--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,45 +483,305 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Small Kitchen Appliances (Food Processors &amp; Choppers)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Breville, Cuisinart, KitchenAid, Braun, Ninja</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Consumer Reports evaluated and ranked the top 7 food processors and choppers for 2026. The review highlights top-performing models from Cuisinart, Breville, KitchenAid, Braun, and Ninja based on lab tests for chopping, slicing, shredding, and noise levels.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The small kitchen appliance market for food processors is currently dominated by specialized brands like Cuisinart and Breville. Samsung and LG are not mentioned in this category, as they primarily focus on major home appliances rather than small countertop food preparation tools.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Since Samsung does not compete in the food processor category, no direct competitive response is needed. However, the high importance placed on 'noise levels' and 'warranty length' in CR's scoring reflects consumer priorities that should be maintained in Samsung's core appliance categories.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kitchen Appliances (Coffee Makers)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bunn, Calphalon, Cuisinart, Haden, Hamilton Beach, Melitta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Consumer Reports released its 2026 rankings for drip coffee makers, testing over 150 models. Top recommendations were categorized by type: traditional drip (Bunn, Calphalon, Cuisinart, Haden, Hamilton Beach), grind-and-brew (Cuisinart, Melitta), and self-serve (Cuisinart). Evaluation criteria included brew performance (temperature and contact time), ease of use, and owner satisfaction.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Cuisinart emerged as a dominant brand across multiple sub-categories, earning high marks for both technical performance and owner satisfaction. Reliability and the ability to maintain optimal brewing temperatures (195°F-205°F) remain the primary differentiators for 'Recommended' status.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>As Samsung does not currently compete in the coffee maker market, this report has no direct competitive impact. However, the high owner satisfaction scores for Cuisinart and Bunn highlight the importance of brand loyalty and reliability in the small kitchen appliance segment.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cooktop, Wall-oven, Range</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Frigidaire, Electrolux</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Electrolux is recalling approximately 174,800 Frigidaire gas ranges due to a delayed ignition defect in the oven's bake burner, which poses a burn hazard. There have been 62 reports of malfunctions and 30 reported injuries. Consequently, Consumer Reports has withdrawn its recommendation for all nine Frigidaire gas range models currently in its ratings.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A major competitor (Frigidaire/Electrolux) has lost its 'Recommended' status across its entire gas range lineup in CR due to a significant safety recall. This creates a temporary vacuum in the 'Recommended' gas range category and potentially damages Frigidaire's brand reliability in the cooking segment.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Samsung should capitalize on this competitor's safety issue by reinforcing the safety and reliability messaging of its own gas and electric range lineups. Marketing efforts could highlight Samsung's rigorous testing protocols to reassure consumers currently wary of gas range safety.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Air Conditioners (Heat Pumps)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Frigidaire, Goodman, Trane, Lennox</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Consumer Reports tested and ranked the best whole-house ducted heat pumps for 2026. The top-performing models identified were the Frigidaire 3T, Goodman 3T R32, Trane 3T, and Lennox 3T, based on heating/cooling efficiency, noise levels, and brand reliability data.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Traditional HVAC-focused brands (Frigidaire, Goodman, Trane, Lennox) continue to dominate the ducted heat pump category in Consumer Reports' rankings. Samsung and LG, despite their strength in ductless systems, were not mentioned or ranked in this specific report for whole-house ducted solutions.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>While Samsung is a leader in the ductless mini-split market, the lack of presence in CR's ducted heat pump rankings—a segment now outselling gas furnaces—indicates a potential brand visibility or product testing gap in the North American whole-house replacement market.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Deals on Headphones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Headphones</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sonos, Apple, Google, Bose, JBL, Ozlo, Anker, Beats, Sony, Dyson, Sennheiser</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Consumer Reports identifies the best current deals on headphones and earbuds, evaluating models from major brands based on sound quality, noise cancellation, and battery life. Featured products include the Sony WF-1000XM5, Bose QuietComfort Ultra, and Apple AirPods 4.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Samsung is completely absent from this list of recommended headphone deals, while key competitors like Apple, Sony, and Google are highlighted for their performance and value. Sony and Bose, in particular, are noted for top-tier noise cancellation and sound quality rankings.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Given the absence of Galaxy Buds in this 'Best Deals' roundup, marketing should evaluate if current promotional pricing for Samsung audio products is being effectively communicated to reviewers or if performance gaps (real or perceived) are excluding them from CR's top-tier recommendations compared to Sony and Apple.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Best Washers for $800 or Less</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Washing Machines</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>LG, Samsung, Electrolux, Maytag, Insignia</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>컨슈머리포트는 800달러 이하의 가성비 세탁기 추천 목록을 발표하며, 봄철 신모델 출시로 인한 가격 상승 트렌드와 구매 적기를 분석했습니다. LG전자는 드럼, 교반식 통돌이, 고효율 통돌이 전 부문에서 다수의 모델이 '추천 제품(CR Recommended)'으로 선정되며 압도적인 성과를 거두었습니다. 반면 삼성전자는 고효율 통돌이 부문에서 1개 모델이 언급되었으나, 에너지 효율은 우수한 반면 사용자 만족도에서 최하위 점수를 기록하며 추천 목록에 포함되지 못했습니다.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>LG전자가 가성비 세탁기 시장의 주요 카테고리를 사실상 독점하며 브랜드 신뢰도와 성능 모두에서 경쟁 우위를 확고히 하고 있습니다. 삼성전자는 기술적 지표(에너지/물 효율)에서는 긍정적인 평가를 받았으나, 실사용자의 낮은 만족도와 신뢰도 문제가 브랜드 추천의 발목을 잡고 있어 이에 대한 품질 개선 및 이미지 회복이 시급한 상황입니다.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>- LG전자는 드럼(WM3400CW), 교반식(WT7005CW, WT7155CW), 고효율 통돌이(WT6100CW, WT8200CW) 등 전 부문에서 추천 제품(Top Pick)으로 선정됨.
 - 삼성전자 모델(WA52DG5500AV)은 에너지 효율, 물 효율, 진동 항목에서 최고 등급을 받았으나, 사용자 만족도(Owner Satisfaction)에서 최하위(Rock bottom) 점수를 기록함.
@@ -529,54 +789,54 @@
 - 달러 이하 보급형 시장에서 LG전자의 추천 모델 비중이 삼성전자를 압도하고 있으며, 삼성은 신뢰도 점수에서 경쟁사 대비 열세임.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Best Deals on Vacuums</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Vacuums</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Samsung, LG, Black+Decker, Shark, Miele, Eufy, iRobot, GorFanty, Tineco, Kenmore, Bissell, Hoover, Dirt Devil, Bosch</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Consumer Reports가 봄맞이 청소를 앞두고 스틱, 로봇, 업라이트, 캐니스터 등 다양한 진공청소기 카테고리의 할인 딜과 성능 평가 결과를 발표했습니다. Shark, Miele, Kenmore 등 주요 브랜드 제품들의 바닥 유형별 청소 성능, 반려동물 털 제거 능력, 사용자 편의성 등을 상세히 다루고 있습니다. 기사 본문은 주로 현재 할인 중인 모델들의 장단점을 분석하여 소비자들에게 구매 가이드를 제공하는 데 중점을 둡니다.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>기사 본문 설명에는 포함되지 않았으나, CR 공식 랭킹 데이터에서 'Samsung Bespoke AI Jet Ultra'가 83점으로 해당 카테고리 최고점 및 Top Pick으로 선정되었습니다. 이는 경쟁사인 LG CordZero(80점) 및 Miele, Bosch 등 프리미엄 브랜드를 제치고 성능 우위를 입증한 결과로, 프리미엄 무선 청소기 시장에서의 강력한 브랜드 위상을 보여줍니다.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>- Samsung Bespoke AI Jet Ultra 모델이 CR 평가 점수 83점으로 'TOP PICK' 및 'RECOMMENDED' 등급 획득.
 - Samsung Jet 85 모델이 79점을 기록하며 상위권 성능 유지 확인.
@@ -584,54 +844,54 @@
 - 기사 본문에서는 Shark, Miele, Kenmore 등 실질적인 할인 혜택이 있는 모델 위주로 상세 리뷰가 진행됨.</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Stick Vacuums</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Samsung, LG, Bosch, Miele, Shark</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>컨슈머리포트가 2026년 최고의 스틱 청소기 9종을 선정하여 발표했습니다. 삼성전자의 '비스포크 AI 제트 울트라'는 강력한 흡입력과 긴 배터리 수명, 자동 먼지 비움 기능을 갖춘 충전 스테이션으로 높은 평가를 받으며 추천 제품(Top Pick)으로 선정되었습니다. LG전자의 '코드제로 올인원' 또한 카페트 청소 성능과 편의 기능에서 우수한 평가를 받았으나, 브랜드 신뢰도 면에서는 삼성이 더 높은 점수를 기록했습니다. 이 외에도 보쉬, 밀레, 샤크 등의 제품이 각 카테고리별 우수 모델로 이름을 올렸습니다.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>삼성전자의 프리미엄 스틱 청소기 라인업이 성능뿐만 아니라 브랜드 신뢰도 및 소유주 만족도 조사에서도 매우 우수한 성적을 거두고 있음을 확인했습니다. 특히 배터리 수명과 신뢰성 측면에서 경쟁사 대비 우위를 점하고 있어, 향후 북미 시장 내 프리미엄 가전 입지를 더욱 공고히 할 수 있을 것으로 분석됩니다.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>- 삼성 Bespoke AI Jet Ultra(VS90F40DMK/AA) 모델이 총점 83점으로 스틱 청소기 부문 'CR 추천 제품(Top Pick)' 선정.
 - 해당 모델은 바닥 및 반려동물 털 청소 성능에서 최고 등급을 받았으며, 테스트 모델 중 가장 긴 평균 작동 시간을 기록함.
@@ -639,54 +899,54 @@
 - 경쟁사인 LG CordZero A949KTMS는 총점 80점을 기록했으나, 브랜드 신뢰도 및 만족도 면에서는 중간 수준(Midlevel)에 머무름.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Washing Machines</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>LG, Samsung, Miele, GE, Speed Queen, Electrolux, Amana, Frigidaire, Maytag, Whirlpool, Asko, Blomberg, Midea</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>컨슈머리포트가 2026년 최고의 세탁기 16종을 선정하여 발표하였으며, LG전자가 드럼, 통돌이(교반식 및 고효율), 소형 드럼 등 거의 모든 주요 카테고리에서 추천 제품(Top Pick)을 휩쓸며 압도적인 성적을 거두었습니다. 삼성전자는 올인원 세탁건조기 부문에서 최고 점수를 기록했으나, 전체적인 추천 제품 리스트에서는 LG에 크게 밀리는 양상을 보였습니다. 특히 LG는 브랜드 신뢰도 조사에서도 드럼 및 고효율 통돌이 부문에서 가장 신뢰할 수 있는 브랜드로 꼽혔습니다.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>LG전자가 북미 세탁기 시장의 전 카테고리에서 성능과 신뢰성을 바탕으로 독보적인 우위를 점하고 있습니다. 삼성전자는 올인원 세탁건조기 시장에서 기술력을 인정받고 있으나, 주력 제품군인 일반 드럼 및 통돌이 세탁기 부문에서 LG의 '추천 제품' 독식을 견제할 수 있는 브랜드 신뢰도 회복 및 성능 차별화가 시급한 상황입니다.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>- LG전자가 드럼, 교반식 통돌이, 고효율 통돌이, 소형 드럼 등 4개 주요 부문에서 총 11개의 추천 제품(Top Pick)을 차지하며 시장 주도권 확인.
 - 삼성 올인원 세탁건조기(WD53DBA900HZ)는 해당 카테고리 최고 점수를 받았으나, 건조 성능 미흡 및 습도 센서 부재가 단점으로 지적됨.
@@ -694,54 +954,54 @@
 - Miele는 소형 드럼 세탁기 부문에서 높은 가격대에도 불구하고 우수한 성능과 사용자 만족도로 추천 제품에 다수 포함됨.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>How an Old-School Flip Phone Changed My Life</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Smartphones</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Samsung, Apple, Nokia, Mint Mobile, Cat, Light Phone, Bigme</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>컨슈머리포트의 한 필자가 디지털 미니멀리즘을 실천하기 위해 아이폰 13 대신 노키아 2780 플립폰(덤폰)을 일주일간 사용한 경험을 공유했습니다. 플립폰 사용을 통해 스크린 타임을 하루 평균 3시간가량 줄이고 삶의 여유를 찾았으나, 앱 부재로 인한 차량 호출, 모바일 결제, 내비게이션 이용의 불편함과 낮은 카메라 성능 등의 한계가 명확히 드러났습니다. 필자는 스마트폰을 완전히 대체하기보다는 필요에 따라 스마트폰을 멀리하고 현재에 집중하기 위한 보조적 수단으로 플립폰 활용을 제안합니다.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>북미 시장 내 '디지털 디톡스'와 '덤폰(Dumb Phone)'에 대한 관심이 존재하지만, 실생활의 필수적인 앱 생태계와 고성능 카메라에 대한 의존도가 높아 스마트폰의 완전한 대체는 어려운 것으로 분석됩니다. 삼성전자는 갤럭시 S25 및 S24 시리즈가 CR 평가에서 최상위권을 유지하며 제품 경쟁력을 인정받고 있는 만큼, 압도적인 하드웨어 성능과 더불어 사용자의 효율적인 디지털 생활을 돕는 소프트웨어적 제어 기능을 강화하여 프리미엄 가치를 공고히 할 필요가 있습니다.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>- 삼성 갤럭시 S25 Ultra 및 S24 Ultra가 CR 스마트폰 평가에서 87점으로 공동 1위(Top Pick) 기록
 - 갤럭시 S25+ 모델 또한 86점으로 애플 아이폰 17 Pro Max와 함께 상위권 및 추천 제품 지위 유지
@@ -749,54 +1009,54 @@
 - 대다수 사용자는 스마트폰의 편리한 기능 때문에 완전한 기기 변경보다는 보조 기기 형태의 사용을 선호하는 경향을 보임</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Worst Vacuums We Tested—and What to Buy Instead</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Vacuums</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Samsung, LG, Shark, Kenmore, Eureka, Bissell, Dirt Devil, Ryobi, Eufy, Roborock, iRobot, Black+Decker</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Consumer Reports는 성능이 미흡한 '최악의 청소기' 목록과 이를 대체할 추천 모델을 발표했습니다. 무선 스틱 청소기 부문에서 Ryobi 모델의 대안으로 LG CordZero Q3가 추천되었으며, 카펫 청소 및 반려동물 털 제거 성능이 우수하다고 평가받았습니다. 한편, 별도 랭킹 데이터에 따르면 삼성전자의 Bespoke AI Jet Ultra가 83점으로 해당 카테고리에서 Top Pick으로 선정되었습니다. 전반적으로 저가형 모델의 흡입력 부족과 배출물 차단 실패가 주요 감점 요인으로 지적되었습니다.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>삼성전자의 Bespoke AI Jet Ultra가 최고점(83점)으로 Top Pick에 선정되어 프리미엄 무선 청소기 시장에서의 경쟁 우위를 확인했습니다. 경쟁사인 LG전자 또한 추천 모델 리스트에 포함되었으나, 삼성 모델이 점수 면에서 앞서고 있습니다. 소비자들이 저가형의 성능 한계를 인지하고 추천 모델로 이동하는 경향이 있으므로, 고성능 및 위생(Clean Emissions) 기능을 강조한 마케팅이 유효할 것으로 보입니다.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>- 삼성 Bespoke AI Jet Ultra 모델이 점수 83점으로 CR Recommended 및 Top Pick으로 선정됨.
 - 삼성 Jet 85 모델은 점수 79점으로 상위권에 랭크됨.
@@ -804,54 +1064,108 @@
 - 무선 스틱 청소기 평가에서 카펫 청소 성능, 반려동물 털 제거, 미세먼지 배출 차단 능력이 핵심 차별화 요소로 작용함.</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Electronics &amp; Appliances</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Laptops, Microwaves</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Consumer Reports의 최신 뉴스레터로, 애플이 599달러의 저가형 노트북인 '맥북 네오(MacBook Neo)'를 포함한 신규 라인업을 출시했다는 소식을 전하고 있습니다. 또한 주방 가전 및 수면 관련 제품에 대한 회원 전용 할인 혜택과 잔디 깎기 기계 관리법, 목재 스테인 내구성 테스트 결과 등을 다루었습니다. 현재 연구소에서는 카운터탑 전자레인지와 세탁 세제 등에 대한 최신 테스트가 진행 중임을 언급했습니다.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>애플이 역대 최저가인 599달러 노트북을 출시하며 컴퓨팅 시장에서의 가격 진입장벽을 대폭 낮추었습니다. 이는 삼성전자의 갤럭시 북 등 보급형 노트북 라인업에 직접적인 경쟁 압박으로 작용할 수 있으며, CR이 전자레인지 부문의 최신 테스트를 진행 중이므로 향후 발표될 평가 결과에 대한 모니터링이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>- 애플, 역대 최저가인 599달러부터 시작하는 '맥북 네오(MacBook Neo)' 및 신규 맥북 에어/프로 라인업 발표
+- CR 연구소에서 카운터탑 전자레인지(Countertop Microwaves)에 대한 신규 테스트 및 평가 업데이트 진행 중
+- 월 17일까지 주방 가전 등 주요 카테고리 제품에 대해 최대 40%의 회원 전용 할인 혜택 제공</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Vacuums, Air Purifiers, Carpet Cleaners</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Blueair, HoMedics, Dirt Devil, Hoover, Shark, iRobot, Dyson, Tineco, Levoit, Persil, Windex, Fabuloso, Method, Mrs. Meyers</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>컨슈머리포트가 봄맞이 대청소 시즌을 맞아 진공청소기, 공기청정기, 카펫 클리너 등 주요 가전제품의 할인 및 추천 목록을 발표했습니다. iRobot Roomba Max 705가 로봇 청소기 중 최고 성능 제품으로 선정되었으며, Blueair의 공기청정기 시리즈가 높은 신뢰도와 성능을 바탕으로 추천 제품(Recommended)에 이름을 올렸습니다. Dyson V15 Detect와 Shark의 스틱 청소기 등 주요 경쟁사 제품들의 성능 테스트 결과와 할인 정보가 상세히 공유되었습니다.</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>기사 내 삼성전자 제품에 대한 직접적인 언급은 없으나, 로봇 청소기 시장에서 iRobot이 압도적인 성능 평가를 받고 있으며 Dyson과 Shark가 프리미엄 및 실용성 시장을 주도하고 있음을 보여줍니다. 특히 공기청정기 분야에서 Blueair가 강력한 브랜드 신뢰도와 추천 등급을 확보하고 있어, 해당 카테고리 내 경쟁사들의 기술적 소구점과 프로모션 전략을 참고할 필요가 있습니다.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>- iRobot Roomba Max 705가 테스트 제품 중 최고 성능을 기록하며 100달러 할인된 가격으로 판매 중임.
 - Blueair 공기청정기 라인업(Mini Restful, 311i+ Max 등)이 CR 추천 제품으로 선정되었으며, 멤버십 대상 최대 40% 할인 코드 제공.
@@ -859,108 +1173,54 @@
 - Shark HydroVac Pro XL 및 Tineco Floor One S5가 스팀 및 세척 성능 부문에서 우수한 평가를 받음.</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Electronics &amp; Appliances</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Laptops, Microwaves</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Consumer Reports의 최신 뉴스레터로, 애플이 599달러의 저가형 노트북인 '맥북 네오(MacBook Neo)'를 포함한 신규 라인업을 출시했다는 소식을 전하고 있습니다. 또한 주방 가전 및 수면 관련 제품에 대한 회원 전용 할인 혜택과 잔디 깎기 기계 관리법, 목재 스테인 내구성 테스트 결과 등을 다루었습니다. 현재 연구소에서는 카운터탑 전자레인지와 세탁 세제 등에 대한 최신 테스트가 진행 중임을 언급했습니다.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>애플이 역대 최저가인 599달러 노트북을 출시하며 컴퓨팅 시장에서의 가격 진입장벽을 대폭 낮추었습니다. 이는 삼성전자의 갤럭시 북 등 보급형 노트북 라인업에 직접적인 경쟁 압박으로 작용할 수 있으며, CR이 전자레인지 부문의 최신 테스트를 진행 중이므로 향후 발표될 평가 결과에 대한 모니터링이 필요합니다.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>- 애플, 역대 최저가인 599달러부터 시작하는 '맥북 네오(MacBook Neo)' 및 신규 맥북 에어/프로 라인업 발표
-- CR 연구소에서 카운터탑 전자레인지(Countertop Microwaves)에 대한 신규 테스트 및 평가 업데이트 진행 중
-- 월 17일까지 주방 가전 등 주요 카테고리 제품에 대해 최대 40%의 회원 전용 할인 혜택 제공</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Air Purifiers</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Coway, Blueair, AirDoctor, Winix, GermGuardian, Vissani, Honeywell</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>컨슈머리포트는 산불 연기로 인한 대기 질 악화에 대비하여 미세 입자 제거 성능이 우수한 공기청정기 5종을 선정하여 발표했습니다. 테스트 결과 HEPA 필터를 장착하고 350평방피트 이상의 대형 공간을 커버하는 모델들이 연기 제거에 가장 효과적인 것으로 나타났습니다. 코웨이(Coway)의 Airmega ProX가 성능과 소음, 브랜드 신뢰도 면에서 최고 평가를 받았으며, 블루에어(Blueair)와 위닉스(Winix) 등의 제품이 추천 목록에 이름을 올렸습니다.</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>북미 시장의 주요 구매 결정 요인 중 하나인 '산불 연기 대응 성능' 평가에서 삼성전자 제품이 추천 목록(Top 5)에 포함되지 않았습니다. 코웨이, 블루에어 등 공기청정기 전문 브랜드들이 성능뿐만 아니라 브랜드 신뢰도와 사용자 만족도에서도 높은 점수를 기록하며 시장 내 입지를 공고히 하고 있는 것으로 분석됩니다.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>- 컨슈머리포트 선정 산불 연기 제거 성능 우수 5대 공기청정기에 삼성 모델 미포함.
 - 코웨이 Airmega ProX가 대형 공간 정화 성능, 저소음, 브랜드 신뢰도에서 최고점(85점)을 받으며 Top Pick으로 선정됨.
@@ -969,54 +1229,54 @@
 - 추천된 모든 제품은 HEPA 필터를 탑재하고 350평방피트 이상의 대형 룸에 적합한 성능을 갖춘 것으로 확인됨.</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Best Deals on Smart Home Devices</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Smart Home Devices</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>TP-Link, Google, SimpliSafe, Amazon, Apple, Samsung</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>컨슈머리포트가 보안 카메라, 스마트 플러그, 온도 조절기 등 주요 스마트 홈 기기의 최신 할인 정보와 테스트 결과를 발표했습니다. TP-Link의 Tapo 및 Kasa 라인업은 구독료 없는 AI 기능과 로컬 저장소 지원으로 높은 가성비를 인정받았으며, Google Nest 제품군은 우수한 비디오 품질과 보안성으로 추천되었습니다. 특히 다수의 추천 제품들이 삼성 SmartThings를 포함한 주요 스마트 홈 플랫폼과의 호환성을 주요 특징으로 내세우고 있습니다.</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>삼성전자의 직접적인 하드웨어 제품은 언급되지 않았으나, TP-Link와 Google 등 주요 스마트 홈 기기 제조사들이 자사 제품의 핵심 경쟁력으로 'Samsung SmartThings' 호환성을 강조하고 있습니다. 이는 스마트 홈 생태계 내에서 SmartThings의 플랫폼 영향력이 견고함을 보여주며, 향후 Matter 표준 확산에 따른 기기 간 연결성 강화가 소비자 선택의 주요 기준이 될 것임을 시사합니다.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>- TP-Link Kasa Smart Wi-Fi Plug Slim EP25는 에너지 모니터링 기능을 제공하며 Samsung SmartThings를 포함한 4대 스마트 홈 시스템과 호환됨.
 - Google Nest Cam with Floodlight는 객체 감지 기능을 무료로 제공하며 Samsung SmartThings 앱 및 음성 제어를 지원함.
@@ -1024,54 +1284,54 @@
 - TP-Link Tapo 보안 카메라 시리즈는 구독료 없이 AI 감지 기능을 제공하며 높은 가성비로 추천됨.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Which iPhone Should You Buy?</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Smartphones</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Apple, Samsung</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>컨슈머리포트가 애플의 최신 아이폰 17 라인업(17, 17e, Air, 17 Pro, 17 Pro Max)에 대한 구매 가이드를 발표했습니다. 각 모델별로 A19 칩셋을 통한 AI 기능 지원, 카메라 성능 차이, 배터리 수명 및 내구성 테스트 결과를 상세히 다루고 있습니다. 특히 새롭게 추가된 초슬림 모델인 '아이폰 Air'와 고성능 'Pro' 시리즈의 사양 및 가격대를 비교 분석했습니다.</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>애플의 최신 아이폰 17 시리즈 출시 및 대대적인 홍보에도 불구하고, 컨슈머리포트의 종합 평가 점수에서는 삼성전자의 갤럭시 S25 울트라와 S24 울트라가 87점으로 공동 1위를 유지하며 아이폰 17 프로 맥스(86점)를 앞서고 있습니다. 이는 삼성전자의 플래그십 스마트폰이 하드웨어 성능과 사용자 경험 측면에서 여전히 시장 최고의 경쟁력을 확보하고 있음을 입증합니다.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>- 컨슈머리포트 스마트폰 부문 평가에서 삼성 갤럭시 S25 Ultra 및 S24 Ultra가 87점으로 전체 공동 1위 및 Top Pick 선정.
 - 애플의 최신 플래그십인 아이폰 17 Pro Max는 86점을 기록하여 삼성전자 상위 모델 대비 낮은 점수 획득.
@@ -1079,54 +1339,54 @@
 - 아이폰 17 시리즈는 전 모델 AI 기능 지원, 120Hz 주사율 확대, 기본 저장용량 증설(256GB) 등 하드웨어 상향 평준화가 진행됨.</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>What's the Best Mac Laptop or Desktop for You?</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Computing (Laptops, Desktops)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Apple, MSI, HP, Acer, Asus, Intel</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>애플이 아이폰 칩을 탑재한 599달러의 초저가형 '맥북 네오'를 포함하여 M5 칩셋 기반의 새로운 맥북 에어 및 프로 라인업을 발표했습니다. 신제품들은 AI 작업 성능이 대폭 향상되었고 WiFi 7을 지원하는 등 하드웨어 사양이 강화되었으나, 모델별로 100달러에서 최대 400달러까지 가격이 인상되었습니다. 컨슈머리포트는 맥북 프로, 에어, 맥 미니 등 애플의 주요 신규 라인업을 '추천 제품(Recommended)'으로 선정하며 높은 평가를 부여했습니다.</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>애플이 저가형 시장(맥북 네오)부터 고성능 프리미엄 시장(M5 Max)까지 라인업을 촘촘히 재편하며 시장 점유율 확대를 꾀하고 있습니다. 특히 AI 성능 강화와 독자 생태계 확장은 삼성 갤럭시 북 시리즈에 위협 요소가 될 수 있으며, 애플의 가격 인상 정책이 시장 전체의 평균 판매 단가(ASP) 및 소비자 선택에 미칠 영향을 모니터링해야 합니다.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>- 애플, 아이폰 A18 Pro 칩을 탑재한 599달러 저가형 '맥북 네오' 출시로 보급형 시장 공략.
 - 신형 맥북 에어(M5) 및 맥북 프로(M5 Pro/Max) 라인업 공개 및 가격 인상(에어 100달러, 프로 16인치 모델 400달러 인상).
@@ -1134,54 +1394,54 @@
 - 컨슈머리포트 평가 결과, 맥북 프로(81점), 맥북 에어(76점), 아이맥(75점) 등 주요 신제품이 추천 제품(Recommended)으로 선정됨.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Computing</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Desktop Computers</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>HP, Apple, Dell, Asus, MSI, Acer</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>컨슈머리포트가 2026년 최고의 데스크탑 컴퓨터 9종을 선정하여 발표했습니다. 올인원, 미니 PC, 타워형의 세 가지 카테고리로 구분하여 성능, 신뢰도, 소비자 만족도를 평가했으며 HP, 애플, 델, 에이수스, MSI, 에이서 제품이 추천 목록에 올랐습니다. 특히 최신 인텔 Ultra, AMD Ryzen AI, 애플 M4 프로세서를 탑재하여 AI 기능을 강화한 모델들이 생산성 측면에서 높은 점수를 받았습니다.</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>데스크탑 시장이 AI PC와 고성능 미니 PC 중심으로 재편되고 있는 가운데, 삼성전자의 제품은 단 한 모델도 추천 목록에 포함되지 못했습니다. 경쟁사들이 전문가용, 게이밍, 사무용 등 세부 시장에서 강력한 성능과 브랜드 신뢰도를 구축하고 있는 반면, 삼성전자의 데스크탑 라인업은 컨슈머리포트의 주요 평가 대상에서 소외되어 있어 브랜드 위상 제고가 시급해 보입니다.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>- 컨슈머리포트 선정 2026년 베스트 데스크탑 9종 목록에 삼성전자 제품 미포함
 - MSI Codex R2 Gaming Desktop이 86점으로 전체 최고점 기록
@@ -1190,54 +1450,54 @@
 - HP와 에이서는 게이밍 및 올인원 부문에서 긴 보증 기간(24~36개월)을 강점으로 내세워 추천됨</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Robot Vacuums</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Samsung, LG, Dyson, Eufy, iRobot, Miele, Shark, Dreame, Eureka, Bosch</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>컨슈머리포트가 반려동물 털 제거 성능이 우수한 2026년 최고의 로봇청소기 6종을 선정했습니다. 삼성전자의 Jet Bot VR7MD96514G 모델은 고가임에도 불구하고 강력한 흡입력과 테스트 제품 중 가장 뛰어난 물걸레 성능을 인정받아 추천 명단에 이름을 올렸습니다. 다이슨, 유피, 아이로봇, 드림, 유레카 등의 경쟁 모델들도 흡입 효율, 가성비, 내비게이션 성능 등을 바탕으로 함께 선정되었습니다.</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>삼성전자의 로봇청소기는 특히 물걸레 성능 면에서 '테스트한 모든 제품 중 최고'라는 압도적인 평가를 받으며 프리미엄 가전으로서의 경쟁력을 입증했습니다. 또한 별도의 랭킹 데이터에서 Bespoke AI Jet Ultra 모델이 83점으로 Top Pick에 선정되는 등 주요 카테고리에서 상위권을 유지하고 있습니다. 다만 다이슨과 유피가 브랜드 신뢰도에서 강세를 보이고 있어, 성능 우위와 더불어 장기적인 신뢰도 관리가 필요할 것으로 보입니다.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>- 삼성 Jet Bot VR7MD96514G 모델이 반려동물 털 제거 및 물걸레 성능 우수로 'Best 6' 제품에 선정됨
 - 해당 모델의 물걸레 기능은 컨슈머리포트가 테스트한 모든 로봇청소기 겸용 모델 중 가장 우수하다고 명시됨
@@ -1246,54 +1506,54 @@
 - 다이슨은 신뢰도 면에서 매우 우수하나 사용자 만족도는 낮게 평가되었으며, 아이로봇은 파산 신청 상태이나 성능 면에서는 여전히 추천됨</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>8 Best Air Purifiers of 2026, Tested by Our Experts</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-of-the-year-a1197763201/</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Air Purifiers</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Coway, AirDoctor, Blueair, Honeywell, Vissani, GermGuardian</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>컨슈머리포트가 2026년 공간 크기별 최고의 공기청정기 8종을 선정하여 발표했습니다. 평가 항목에는 미세먼지 및 연기 제거 성능, 소음 수준, 필터 교체비와 전기료를 합산한 연간 유지비용, 그리고 브랜드 신뢰도가 포함되었습니다. Coway Airmega ProX가 대형 공간용에서 최고점을 받았으며, Blueair와 Honeywell 제품들이 중소형 공간용 추천 제품으로 다수 이름을 올렸습니다.</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>이번 추천 목록에 삼성전자 제품은 포함되지 않았으며, Coway와 Blueair가 성능과 신뢰도 면에서 시장을 주도하고 있는 것으로 나타났습니다. 특히 Coway는 대형 공간용 부문에서 독보적인 성능과 높은 브랜드 신뢰도를 기록하며 Top Pick으로 선정되었습니다. 경쟁사 LG 또한 이번 주요 순위권에는 언급되지 않았습니다.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>- 컨슈머리포트 2026년 공기청정기 부문 추천 제품 발표 (삼성 모델 미포함)
 - Coway Airmega ProX가 총점 85점으로 대형 공간용 부문 Top Pick 선정
@@ -1301,54 +1561,54 @@
 - 주요 평가 지표: 고속/저속 가동 시 입자 제거 효율, 소음, 연간 운영 비용(필터 및 전기료), 브랜드 신뢰도</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Guide to Streaming Video Services</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/electronics-computers/streaming-media/guide-to-streaming-video-services-a4517732799/</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>TVs / Streaming Services</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Amazon, Apple, Disney, Hulu, Netflix, HBO Max, Paramount, Peacock, Sony, AMC, Google, Fubo, DirecTV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>본 기사는 넷플릭스, 디즈니+, 애플 TV+ 등 주요 스트리밍 서비스의 최신 요금제, 콘텐츠 특징 및 스포츠 중계권 현황을 상세히 가이드합니다. 최근 스트리밍 업계의 트렌드인 광고형 요금제 도입, 계정 공유 제한 정책, 그리고 라이브 TV 서비스의 가격 인상 및 번들 결합 상품 정보를 제공합니다. 또한 아마존과 디즈니의 NBA 중계권 확보 등 스포츠 콘텐츠 강화 움직임과 서비스 간 인수합병 소식을 다룹니다.</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>삼성 스마트 TV(Tizen OS) 생태계 내에서 주요 스트리밍 앱의 접근성과 통합 검색 기능이 중요해지고 있습니다. 특히 스포츠 중계권이 여러 플랫폼으로 분산되고 서비스 간 번들링이 가속화됨에 따라, 소비자가 여러 서비스를 편리하게 전환하고 관리할 수 있는 인터페이스 제공이 하드웨어 경쟁력의 핵심 요소가 될 것으로 분석됩니다.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>- 넷플릭스, 디즈니+, 훌루 등 주요 서비스의 요금 인상 및 광고형 요금제 전면 도입.
 - 아마존, 디즈니, NBC유니버설의 NBA 중계권 확보 (2025/2026 시즌부터 11년간).
@@ -1357,54 +1617,54 @@
 - YouTube TV의 스포츠, 뉴스 등 장르별 세분화된 저가형 패키지 출시 계획 (2026년).</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>6 Live TV Streaming Services That Let You Cut Cable TV</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/electronics-computers/streaming-media/video-streaming-services-that-let-you-cut-cable-tv-a9076884300/</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Streaming Services &amp; Devices</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>DirecTV, Fubo, Hulu, Philo, Sling TV, YouTube, Google, Amazon, Apple, Roku, Nvidia</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>케이블 TV를 대체할 수 있는 6가지 주요 라이브 TV 스트리밍 서비스(DirecTV, Fubo, Hulu + Live TV, Philo, Sling TV, YouTube TV)의 요금제와 채널 구성, 주요 특징을 비교 분석한 기사입니다. 각 서비스는 로컬 방송 및 스포츠 채널 제공 여부, 클라우드 DVR 저장 용량 등에서 차이를 보이며 최근 가격 인상 추세를 보이고 있습니다. 또한, 이러한 서비스를 이용하기에 적합한 4K 스트리밍 기기로 Roku, Amazon, Google, Apple, Nvidia의 제품들을 추천하고 있습니다.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>삼성 스마트 TV의 Tizen OS 플랫폼은 기사에서 언급된 Roku, Apple TV, Google TV Streamer 등 외부 스트리밍 기기들과 콘텐츠 허브 주도권을 두고 경쟁 관계에 있습니다. 소비자 리포트가 추천한 'Top Pick' 기기들이 삼성 TV의 내장 플랫폼 기능을 대체할 수 있는 만큼, 삼성 TV 사용자들의 이탈을 막기 위해 주요 스트리밍 서비스와의 파트너십 강화 및 내장 앱의 사용성 개선이 중요합니다.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>- Consumer Reports는 Roku Ultra(2024), Amazon Fire TV Cube(3rd Gen), Google TV Streamer(4K), Apple TV 4K, Nvidia Shield TV Pro를 스트리밍 기기 부문 'Top Pick'으로 선정함.
 - YouTube TV($72/월), Hulu + Live TV($90~100/월), Fubo($85~110/월) 등 주요 라이브 스트리밍 서비스의 요금 인상 및 채널 패키지 변경 사항이 보고됨.
@@ -1412,108 +1672,108 @@
 - 주요 스트리밍 기기들은 4K 해상도 지원, 멀티뷰 기능, 무제한 클라우드 DVR 등을 핵심 경쟁력으로 내세우고 있음.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>3 Reasons to Choose a Hand Mixer Over a Stand Mixer</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/appliances/mixers/reasons-to-choose-a-hand-mixer-over-a-stand-mixer-a5008456414/</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Appliances</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Mixers</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>KitchenAid, Breville, Cuisinart, Toastmaster, Braun, Pioneer Woman, Beautiful by Drew Barrymore, Hamilton Beach</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>컨슈머리포트는 가벼운 반죽 조리, 공간 절약, 저렴한 비용을 이유로 스탠드 믹서보다 핸드 믹서가 효율적일 수 있음을 설명하며 구매 가이드를 제공함. 주요 성능 테스트 항목으로는 혼합 성능, 소음, 편의성 등이 포함되었으며 세척 관리의 중요성을 강조함. Braun, Breville, Cuisinart, KitchenAid의 특정 모델들이 우수한 평가를 받으며 추천 제품으로 선정됨.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>해당 기사는 소형 주방 가전인 핸드 믹서를 다루고 있으며, 삼성전자가 주력으로 하는 가전 카테고리에 해당하지 않아 직접적인 비즈니스 영향은 미미함.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>- 컨슈머리포트의 핸드 믹서 부문 성능 평가 결과 및 추천 제품 리스트 발표.
 - Braun, Breville, Cuisinart, KitchenAid 제품이 'Top Pick' 및 추천 모델로 선정됨.
 - 삼성전자 및 LG전자 관련 언급이나 해당 카테고리 내 경쟁 제품은 포함되지 않음.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Best TV Deals Right Now</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-deals-right-now-a7570913441/</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>TVs, Soundbars, Streaming Devices</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Samsung, LG, Sony, TCL, Hisense, Insignia, Roku, Amazon</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>컨슈머리포트는 3월 스포츠 시즌을 앞두고 현재 할인 중인 주요 TV 모델들의 성능 평가와 추천 순위를 발표했습니다. 삼성전자의 QD-OLED 및 OLED TV 모델들은 화질과 사운드 부문에서 최고 점수인 91점을 기록하며 'Top Pick'으로 선정되었으나, 보급형인 Crystal UHD 라인업은 HDR 성능 미흡이 지적되었습니다. LG전자의 C5 OLED 시리즈 역시 삼성과 동일한 최고점을 기록하며 강력한 경쟁 모델로 평가받았습니다.</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>삼성전자의 프리미엄 라인업(QD-OLED, OLED)은 화질과 사운드에서 업계 최고 수준의 경쟁력을 입증하며 추천 제품 상단을 점유하고 있습니다. 하지만 보급형 시장에서는 HDR 성능 부족이 지속적으로 언급되고 있으며, TCL과 Hisense 등 중국 브랜드들이 미니 LED 기술을 앞세워 가성비 시장을 공략하고 있어 이에 대한 대응이 필요합니다.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>- 삼성 QD-OLED(QN77S90C) 및 OLED(QN65S84FA) 모델이 화질 및 HDR 성능에서 최고 수준의 평가를 받으며 CR 추천 제품(Top Pick)으로 선정됨.
 - 보급형 Crystal UHD 라인업(UN507900F 등)은 일반 화질은 양호하나 HDR 표현력 부족이 주요 단점으로 반복 지적됨.
@@ -1521,7 +1781,7 @@
 - 삼성 9.1.4 채널 사운드바가 무선 돌비 애트모스 및 액티브 보이스 앰플리파이어 기능을 바탕으로 긍정적인 시장 기대를 얻고 있음.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,838 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>중요도</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Frigidaire, Electrolux</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Frigidaire(Electrolux)가 오븐 베이크 버너의 점화 지연으로 인한 화상 위험으로 약 174,800대의 가스 레인지를 리콜했습니다. 소비자 제품 안전 위원회(CPSC)에 따르면 62건의 오작동 보고와 30건의 부상 사례가 발생했으며, Consumer Reports는 해당 브랜드의 가스 레인지 모델 9종에 대한 추천을 모두 철회했습니다.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>주요 경쟁사인 Frigidaire의 대규모 리콜과 CR 추천 제외는 가스 레인지 시장 내 브랜드 신뢰도에 심각한 타격을 줄 것으로 보입니다. 특히 안전과 직결된 결함으로 인해 소비자들이 타 브랜드로 이탈할 가능성이 높으며, 이는 시장 점유율 재편의 기회가 될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>경쟁사의 안전 이슈를 기회로 삼아 삼성 가스 레인지의 점화 안전 장치 및 품질 관리 우수성을 강조하는 마케팅이 필요합니다. 리콜 대상 모델을 보유한 고객들을 대상으로 한 보상 판매나 교체 프로모션을 통해 신규 고객을 확보하는 전략을 검토해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Air Conditioners (Heat Pumps)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Frigidaire, Goodman, Trane, Lennox</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Consumer Reports가 2026년 최고의 전체 주택용 히트펌프(Heat Pumps) 4종을 선정하여 발표했습니다. 테스트 결과 Frigidaire 3T 모델이 종합 87점으로 1위를 차지했으며, Goodman, Trane, Lennox 제품이 그 뒤를 이어 추천 모델로 이름을 올렸습니다. 평가는 가열 및 냉각 효율, 소음, 브랜드 신뢰도 등을 기준으로 진행되었습니다.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>미국 내 히트펌프 판매량이 2024년 처음으로 가스 보일러를 앞지르는 등 시장이 급성장하고 있습니다. 이번 평가에서는 Frigidaire가 성능 면에서 최고점을 받았으나, 전통적인 공조 전문 브랜드인 Trane과 Lennox가 브랜드 신뢰도 및 사용자 만족도에서 여전히 강세를 보이고 있습니다. 삼성과 LG 등 국내 가전 브랜드는 이번 상위 추천 목록에 포함되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>북미 공조 시장이 친환경 히트펌프로 빠르게 재편되고 있는 상황에서, 당사 제품의 인지도와 추천 순위 진입이 시급합니다. 특히 Trane과 Lennox가 선점하고 있는 '신뢰도'와 '설치 품질' 영역에서의 경쟁력을 확보하기 위해 현지 설치 전문가와의 파트너십 강화 및 북미 기후에 최적화된 고효율 모델의 마케팅 확대가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Roku, Sony, Hisense, TCL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>컨슈머리포트의 2026년 TV 브랜드 평가 결과, 삼성이 종합 1위 브랜드로 선정되었으며 LG, Roku, Sony가 그 뒤를 이었습니다. 삼성의 2025년형 QD-OLED 모델인 QN65S90F는 화질, HDR, 사운드 성능에서 극찬을 받으며 종합 점수 91점으로 최고점을 기록했습니다. LG의 OLED65C5PUA는 88점으로 2위를 차지했으며, 소니와 Roku의 주요 모델들도 추천 제품에 포함되었습니다.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>삼성은 실험실 테스트 성능뿐만 아니라 브랜드 신뢰도 및 소유자 만족도 조사에서도 높은 점수를 획득하여 종합 1위를 수성했습니다. 특히 삼성의 QD-OLED 기술이 경쟁사인 LG의 OLED 라인업보다 높은 점수를 기록하며 프리미엄 TV 시장에서의 경쟁 우위를 입증했습니다.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>삼성이 종합 1위를 차지했으나 LG와의 점수 차이가 근소하며, 소니와 Roku 등 경쟁사들도 특정 가격대와 기능에서 강점을 보이고 있습니다. QD-OLED의 화질 우수성과 새로운 AI 프로세서의 성능을 마케팅 포인트로 적극 활용하되, 경쟁사 대비 미지원 기능(Dolby Vision 등)에 대한 소비자 우려를 불식시킬 수 있는 화질 최적화 기술 강조가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Washer</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LG, Electrolux, Maytag, Insignia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>컨슈머리포트(CR)는 800달러 이하의 경제적인 세탁기 중 성능이 우수한 제품들을 선정하여 발표했습니다. LG전자의 드럼 세탁기(WM3400CW)와 교반식(Agitator) 통돌이 세탁기(WT7005CW, WT7155CW)가 각 카테고리에서 최고 점수를 받으며 '추천 제품(CR Recommended)'으로 선정되었습니다. 기사는 봄철 신제품 출시와 프로모션 축소로 가격이 일시적으로 상승하는 경향이 있으므로, 주요 할인 기간을 활용할 것을 권장하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LG전자가 800달러 이하 보급형 세탁기 시장에서 주요 카테고리의 추천 제품(Top Pick)을 사실상 독점하고 있습니다. 특히 드럼 세탁기 부문에서 LG 모델은 87점의 고득점을 기록하며 경쟁사인 일렉트로룩스(79점)와 메이텍(78점)을 크게 앞질렀습니다. 삼성전자는 이번 가성비 추천 목록에 단 하나의 모델도 이름을 올리지 못해, 해당 가격대에서의 제품 경쟁력 및 인지도 강화가 시급한 상황입니다.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>보급형 시장에서 LG의 강력한 지배력이 확인되었습니다. 삼성전자는 800달러 이하 가격대에서 에너지 효율과 세척 성능을 강화한 모델의 마케팅을 확대해야 합니다. 또한, 기사에서 언급된 11월 블랙 프라이데이 등 가격 하락 시점에 맞춘 전략적인 프로모션을 통해 점유율 회복을 도모해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Black+Decker, Shark, Miele, Eufy, iRobot, GorFanty, Tineco, Kenmore, Bissell, Hoover, Dirt Devil</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Consumer Reports에서 발표한 스틱, 로봇, 업라이트, 캐니스터 등 다양한 유형의 진공청소기 및 카페트 클리너에 대한 최신 할인 정보와 성능 평가 요약입니다. Shark, Miele, iRobot, Kenmore 등 주요 브랜드의 제품들이 성능, 신뢰도, 가격 만족도 측면에서 상세히 분석되었습니다.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Shark와 Miele가 여러 카테고리에서 우수한 성능과 높은 브랜드 신뢰도를 바탕으로 강력한 추천을 받고 있습니다. 특히 Shark는 유연한 완드, 먼지 감지 센서, 셀프 클리닝 브러시 롤 등 편의 기능에서 높은 점수를 받았으며, iRobot은 로봇 청소기 부문에서 최고 성능 모델로 평가받았습니다. 이번 목록에 삼성전자 제품은 포함되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>현재 주요 진공청소기 할인 및 추천 목록에서 당사(Samsung) 제품이 언급되지 않았습니다. 경쟁사인 Shark와 Miele가 사용자 편의 기능과 브랜드 만족도를 앞세워 시장을 주도하고 있으므로, 해당 브랜드들의 핵심 기능(센서 기술, 유지보수 편의성 등)에 대응하는 제품 경쟁력 강화 및 프로모션 전략이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Bosch, Miele, Dyson, Shark, Bissell, Tineco, Hoover, Kenmore, Electrolux</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 발표한 2026년 최고의 스틱 청소기 리뷰에서 삼성전자의 'Bespoke AI Jet Ultra'가 종합 점수 83점으로 1위를 차지했습니다. LG전자의 'CordZero All-in-One'은 80점으로 2위를 기록했으며, 삼성의 'Jet 85' 모델도 79점으로 상위권에 올랐습니다. 삼성 제품은 강력한 흡입력뿐만 아니라 배터리 수명과 브랜드 신뢰도 면에서 매우 높은 평가를 받았습니다.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>삼성전자는 프리미엄 모델(Bespoke AI Jet)과 보급형 모델(Jet 85) 모두에서 '추천 제품(Recommended)'으로 선정되며 시장 경쟁력을 입증했습니다. 특히 삼성은 설문조사 결과 브랜드 신뢰도와 소유주 만족도에서 최고 등급을 기록하며, 배터리 결함 문제가 적다는 점이 주요 강점으로 부각되었습니다. 반면 경쟁사인 LG는 성능은 우수하나 브랜드 신뢰도 면에서는 중간 수준에 머물렀습니다.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>삼성 청소기의 압도적인 브랜드 신뢰도(Reliability)와 긴 배터리 수명을 마케팅 포인트로 극대화해야 합니다. 특히 LG 등 경쟁사 대비 배터리 내구성이 뛰어나다는 점을 강조하여 프리미엄 가전으로서의 이미지를 굳히고, 카펫 청소 성능이 다소 낮은 중가형 모델(Jet 85)의 경우 바닥 청소와 반려동물 털 제거 성능을 집중 홍보하여 타겟 고객층을 세분화할 필요가 있습니다.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nokia, Apple, Mint Mobile, Cat, Light Phone, Bigme, Sony</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Consumer Reports의 기자가 스마트폰 중독에서 벗어나기 위해 Nokia 2780 Flip 폰을 일주일간 사용하며 겪은 '디지털 미니멀리즘' 체험기입니다. 앱 생태계 부재와 불편한 내비게이션, 낮은 카메라 성능 등의 한계에도 불구하고, 스크린 타임을 획기적으로 줄이고 삶의 여유를 찾은 긍정적인 변화를 다루고 있습니다.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>최근 스마트폰 과의존에 지친 소비자들 사이에서 '덤폰(Dumb Phone)'으로 불리는 피처폰 회귀 트렌드가 나타나고 있습니다. 이는 단순한 기기 성능의 문제가 아니라, 디지털 디톡스와 개인의 집중력 회복을 원하는 소비자 니즈가 반영된 결과입니다.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>당사(Samsung)는 고성능 하드웨어 경쟁 외에도 사용자의 디지털 웰빙을 지원하는 소프트웨어 기능(예: 모드 및 루틴, 집중 모드)을 더욱 고도화하여 홍보할 필요가 있습니다. 또한, 미니멀한 라이프스타일을 추구하는 고객층을 겨냥한 UI/UX 최적화 전략이 유효할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>LG, Samsung, Shark, Kenmore, Eureka, Bissell, Ryobi, Roborock, iRobot, Black+Decker, Eufy, Atrix, Oreck, Mainstays, Dirt Devil</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 각 카테고리별(업라이트, 캐니스터, 스틱, 로봇, 핸디형)로 성능이 가장 낮은 '최악의 청소기'를 선정하고, 이를 대체할 수 있는 우수한 성능의 추천 제품을 발표했습니다. 특히 무선 스틱 청소기 부문에서 LG전자의 CordZero Q3 모델이 Ryobi 제품의 우수한 대안으로 선정되었습니다.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LG전자의 CordZero Q3 C5323GW 모델은 무선 스틱 청소기 중 약 300달러의 합리적인 가격대에서 카펫 청소, 반려동물 털 제거, 에지 클리닝 성능이 매우 우수한 것으로 평가받아 추천 모델에 이름을 올렸습니다. 반면 로보락(Roborock)은 물걸레 성능 미흡으로 최악의 모델 중 하나로 꼽혔으며, 샤크(Shark)와 켄모어(Kenmore)가 여러 부문에서 가성비 추천 제품으로 선정되었습니다.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>경쟁사인 LG전자가 무선 청소기 부문에서 추천 모델로 선정되어 긍정적인 브랜드 이미지를 구축하고 있습니다. 삼성전자의 청소기 제품군이 이번 리스트에 언급되지 않은 점을 고려할 때, 향후 컨슈머리포트 평가에서 'Top Pick'에 진입할 수 있도록 카펫 청소 성능 및 배터리 편의성 등 핵심 지표에 대한 성능 개선과 마케팅 강화가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vacuums, Air Purifiers, Humidifiers</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blueair, HoMedics, Dirt Devil, Hoover, Shark, iRobot, Dyson, Tineco, Levoit, Persil, Windex, Fabuloso, Mrs. Meyers</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>봄맞이 대청소 시즌을 맞아 컨슈머리포트(CR)가 선정한 청소기, 공기청정기, 가습기 등 주요 가전제품의 할인 정보와 성능 평가 결과입니다. iRobot Roomba Max 705가 역대 최고 성능의 로봇 청소기로 평가받았으며, Dyson, Shark, Blueair 등의 브랜드 제품들이 각 카테고리에서 추천 모델로 선정되었습니다.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>이번 기사에서 삼성과 LG 제품은 언급되지 않았으나, 로봇 청소기 시장에서 iRobot이 독보적인 성능 평가를 받고 있으며 Dyson과 Shark가 스틱 및 멀티 청소기 시장에서 강력한 경쟁력을 유지하고 있습니다. 공기청정기 부문에서는 Blueair가 높은 신뢰도와 성능을 바탕으로 CR 추천(Recommended) 지위를 확보하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>주요 경쟁사들이 봄 시즌을 겨냥해 공격적인 할인과 CR 추천 마크를 활용한 마케팅을 진행 중입니다. 특히 로봇 청소기와 공기청정기는 당사의 주력 카테고리이므로, 경쟁 모델 대비 성능 우위(흡입력, 소음, 유지비 등)를 강조하는 비교 마케팅과 시즌별 프로모션 대응이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Laptops</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Consumer Reports의 최신 소식 요약으로, 애플이 새롭게 출시한 599달러의 저가형 노트북 'MacBook Neo'와 업데이트된 MacBook Air 및 Pro 라인업에 대한 분석을 포함하고 있습니다. 그 외 잔디 깎이 관리, 회원 전용 할인 혜택, 목재 스테인 테스트 및 연료 효율 운전 팁 등을 다룹니다.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>애플이 역대 최저가인 599달러의 MacBook Neo를 출시하며 보급형 노트북 시장 공략을 강화했습니다. 이는 프리미엄 중심의 전략에서 벗어나 가격 민감도가 높은 소비자 층까지 점유율을 확대하려는 움직임으로 해석됩니다.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>애플의 저가형 노트북 시장 진입은 삼성 갤럭시 북의 보급형 라인업에 위협이 될 수 있습니다. 교육용 및 일반 사무용 시장에서 경쟁력을 유지하기 위해 가격 정책을 재점검하고, 갤럭시 에코시스템(스마트폰, 태블릿 연동)의 우수성을 강조하는 마케팅 전략이 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Air Purifier</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Coway, Blueair, AirDoctor, Winix</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 산불 연기로 인한 미세입자 제거에 탁월한 성능을 보인 공기청정기 5종을 선정하여 발표했습니다. 테스트 결과 Coway Airmega ProX가 가장 높은 점수를 받았으며, Blueair(311i+ Max, 211+), AirDoctor 4000 Black, Winix 9800이 추천 모델로 이름을 올렸습니다. 이 제품들은 HEPA 필터를 탑재하고 대형 공간(350평방피트 이상) 정화에 최적화된 성능을 갖춘 것이 특징입니다.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>산불 시즌을 앞두고 공기 질 관리에 대한 관심이 높아지는 가운데, Coway와 Winix 등 아시아 브랜드들이 북미 시장에서 강력한 추천 모델로 자리 잡고 있습니다. 특히 Coway는 성능과 신뢰도 면에서 최고 등급을 받았으며, Winix는 가성비 측면에서 긍정적인 평가를 받았습니다. 이번 추천 목록에 삼성전자 제품은 포함되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>북미 시장의 환경적 특성(산불 등)에 맞춘 대형 공간용 공기청정기 시장에서 경쟁사들이 우위를 점하고 있습니다. 당사 제품의 HEPA 필터 성능 및 대용량 정화 능력을 재점검하고, 컨슈머리포트의 주요 평가 항목인 유지 비용(필터 교체 및 에너지)과 소음 성능을 개선하여 브랜드 인지도를 높일 필요가 있습니다.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 애플의 최신 아이폰 17 라인업(17e, 17, Air, 17 Pro, 17 Pro Max)과 기존 모델을 비교 분석함. 테스트 결과 아이폰 17 Pro가 85점으로 최고점을 기록했으며, 새롭게 도입된 슬림형 모델인 '아이폰 Air'를 포함한 전 모델이 '추천(Recommended)' 등급을 획득함. 모든 모델이 Apple Intelligence를 지원하며 내구성과 카메라 성능에서 우수한 평가를 받음.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>애플은 보급형부터 프리미엄 모델까지 전 라인업에 A19 시리즈 칩을 탑재하여 AI 기능을 표준화했으며, 특히 '아이폰 Air'라는 새로운 폼팩터를 통해 디자인 차별화를 시도함. 경쟁사 대비 높은 브랜드 신뢰도와 함께 전 모델이 80점 이상의 높은 점수를 기록하며 스마트폰 시장에서의 강력한 경쟁력을 입증함.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>경쟁사의 신규 라인업이 컨슈머리포트 추천 모델을 휩쓸고 있어 갤럭시 S 시리즈와의 프리미엄 시장 점유율 경쟁이 심화될 것으로 보임. 삼성은 갤럭시 AI의 실용적 우위와 카메라 줌 성능 등 하드웨어적 차별점을 강조하는 한편, 아이폰 Air에 대응하는 슬림 디자인 및 경량화 전략에 대한 검토가 필요함.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Laptops &amp; Desktops</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Apple, Intel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>애플이 M5 칩을 탑재한 맥북 에어와 프로 라인업을 업데이트하고, 아이폰 칩(A18 Pro)을 사용한 599달러의 초저가형 모델 '맥북 네오(MacBook Neo)'를 출시했습니다. 컨슈머리포트는 맥북 에어 2025 모델(76점)과 맥북 프로(81점)를 '추천 제품(Recommended)'으로 선정하며 성능과 다재다능함을 높게 평가했습니다.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>애플이 저가형 노트북 시장 공략을 위해 모바일 AP를 탑재한 맥북 네오를 도입하며 윈도우 및 크롬북 사용자를 타겟팅하고 있습니다. 또한 M5 칩셋을 통해 AI 성능을 4배 강화하고 WiFi 7을 지원하는 등 하드웨어 사양을 상향 평준화하여 프리미엄 시장에서의 지배력을 공고히 하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>삼성전자는 갤럭시 북 라인업에서 애플의 599달러 저가 공세에 대응할 수 있는 가격 전략이 필요합니다. 특히 애플이 기본 램 용량을 16GB로 상향하고 WiFi 7을 도입함에 따라, 차기 갤럭시 북 모델에서도 통신 규격과 멀티태스킹 성능 우위를 확보하고 갤럭시 생태계와의 연동성을 강조한 마케팅이 요구됩니다.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Microwave</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Commercial Chef, Emerson, Hamilton Beach, Nostalgia Electrics, Proctor Silex, Vissani, Danby, Farberware, Insignia, Panasonic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 공간 효율성이 높은 소형 전자레인지 5종을 선정하여 발표했습니다. 소형 모델은 낮은 와트로 인해 가열 속도가 느리다는 단점이 있으나, 소음 및 해동 균일성 측면에서는 우수한 평가를 받았습니다. 주요 추천 모델로 Commercial Chef, Danby, Farberware, Insignia, Panasonic 제품이 언급되었습니다.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>이번 소형 전자레인지 추천 리스트에 삼성전자와 LG전자의 제품은 포함되지 않았습니다. 소형 가전 시장은 주로 저가형 브랜드와 파나소닉과 같은 특정 브랜드가 강세를 보이고 있으며, 소비자들은 가열 성능의 한계를 인지하면서도 공간 절약과 소음 성능을 주요 구매 요인으로 고려하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>소형 전자레인지 시장에서 삼성의 존재감이 낮은 상황입니다. 1인 가구 및 미니멀 라이프 트렌드에 맞춰, 소형 모델에서도 삼성의 강점인 스마트 기능이나 디자인(비스포크 등)을 접목하고, 소형 모델의 고질적 문제인 가열 속도를 개선한 프리미엄 소형 라인업 검토가 필요해 보입니다.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Desktop Computers</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HP, Apple, Dell, Asus, Intel, AMD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Consumer Reports가 2026년 최고의 데스크탑 컴퓨터 9종을 선정하여 발표했습니다. 올인원, 미니 PC, 타워형 카테고리에서 성능, 신뢰도, 소비자 만족도를 기준으로 평가가 진행되었습니다. HP EliteStudio(올인원), Apple Mac Studio(미니 PC), Asus NUC 14 Pro 등이 각 부문에서 높은 점수를 받으며 추천 제품으로 선정되었습니다.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>데스크탑 시장에서 AI 처리 능력이 핵심 차별화 요소로 부상하고 있습니다. Intel Ultra 및 AMD Ryzen AI 프로세서를 탑재한 모델들이 생산성 측면에서 높은 평가를 받았으며, Apple은 브랜드 신뢰도와 사용자 만족도 부문에서 여전히 독보적인 위치를 차지하고 있습니다. 특히 미니 PC 시장이 로컬 AI 에이전트 활용 등의 수요로 인해 빠르게 성장하고 있는 점이 주목됩니다.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>삼성전자의 데스크탑 제품군이 이번 추천 목록에 포함되지 않았습니다. 경쟁사들이 AI 성능과 폼팩터 혁신(미니 PC 등)을 통해 시장을 선점하고 있는 만큼, 갤럭시 에코시스템과의 연결성 및 온디바이스 AI 강점을 부각한 프리미엄 데스크탑 라인업의 북미 시장 공략 강화가 필요합니다.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Robot Vacuum</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dreame, Dyson, Eufy, Eureka, iRobot, Samsung</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Consumer Reports는 반려동물을 키우는 가정에 적합한 2026년 최고의 로봇청소기 6종을 발표했습니다. 선정된 모델은 삼성 Jet Bot VR7MD96514G를 포함하여 Dreame L40 Ultra, Dyson 360 Vis Nav, Eufy C10 T2292, Eureka NERE10SW, iRobot Roomba Max 705입니다. 삼성 제품은 특히 물걸레 성능에서 역대 최고 수준이라는 평가를 받았습니다.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>삼성 Jet Bot은 고가임에도 불구하고 강력한 반려동물 털 흡입력과 더불어, 테스트된 모든 로봇청소기 중 가장 뛰어난 물걸레 성능을 보유한 것으로 평가되었습니다. 특히 먼지 비움, 물걸레 세척 및 건조가 자동으로 이루어지는 도킹 스테이션의 편의성이 주요 장점으로 꼽혔습니다. 경쟁사인 다이슨은 청소 속도에서, 드리미는 펫 전용 구역 설정 등 소프트웨어 기능에서 강점을 보였습니다.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>삼성 로봇청소기가 '물걸레 성능 부문 역대 최고'라는 평가를 받은 점을 프리미엄 마케팅 포인트로 극대화해야 합니다. 경쟁사들이 가성비(Eufy, Eureka)나 흡입 속도(Dyson)를 내세우는 것에 대응하여, 삼성은 올인원 스테이션을 통한 '완전 무인 관리'와 '위생적인 물걸레 관리'라는 차별화된 가치를 지속적으로 소구할 필요가 있습니다.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -492,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +1344,2046 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4 Best Single-Serve Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-pod-coffee-makers-a3468890273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>What to Expect for Amazon Prime Day 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Deals on Headphones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Talking Carts 11: Couponing 101</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best New SUVs and Cars for Under $30,000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>How to Save Money at the Gas Pump</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Best Deals on Health and Beauty Products</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Battery Platforms for Power Tools</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Deals on Tech Products Right Now</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Best Mattress Sales Right Now</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Our Favorite Deals Right Now</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best Deals on Pet Products</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Best Hot Combs, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>42 Used Cars to Avoid Buying</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>How to Clean Your Lawn Mower Deck</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-clean-your-lawn-mower-deck-a4858405895/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Best Wood Stains of 2026 (and a Few of the Worst)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/best-wood-stains-from-consumer-reports-tests-a4478428531/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>How to Get Your Lawn Mower or Tractor Ready for Mowing Season</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-get-your-lawn-mower-ready-for-spring-a8196766008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Best Time to Fertilize Your Lawn</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-care/dont-bother-fertilizing-your-lawn-twice-a-year-a5780099997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10 Best Deals on Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>How to Stain a Deck</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Best Hybrid Cars for Under $35,000</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Best Deals Under $50</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Best Deals Under $100</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Deals on Healthy-Home Essentials</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Best and Worst Laundry Detergents of 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Most and Least Reliable Coffee Makers</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Worst Deals on New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Best Deals on Smart Home Devices</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Most Discounted New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>How Do Hybrid Cars Work?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Best New-Car Deals</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Best Deals on Kitchen Products</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Best Deals on Home Products</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Best Cars Made in the USA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7 Best E-Bike Covers of 2026, According to Experts</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/electric-bikes/best-e-bike-covers-a5685855846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Are Hybrids a Smart Choice Right Now?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/why-hybrid-vehicles-are-a-smart-choice-right-now-a2736240282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Deals Under $25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-25-a4183478310/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gas vs. Battery Lawn Mower: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/gas-vs-electric-lawn-mower-which-is-better-a1057954260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>How to Check Engine Oil the Right Way</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6 Best Compression Socks, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/underwear-socks/best-compression-socks-a2750797916/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>We Tested 49 More Baby Formulas for Lead and Arsenic</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-formula/liquid-baby-formula-contaminants-test-results-a8639602154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Safest Small SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-small-suvs-a9206654113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ford and Lincoln SUVs Recalled to Fix Windshield Wipers</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/ford-lincoln-suvs-recalled-to-fix-windshield-wiper-motor-a5559013983/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.7 Million More Ford and Lincoln SUVs Recalled to Fix Screens</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/more-ford-and-lincoln-suvs-recalled-to-fix-backup-cameras-a4514261791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Used Cars and SUVs Under $10,000 That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-used-cars-suvs-under-10000-dollars-a8966344858/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Thousands of Halo Magic Sleepsuits Recalled for Choking Risk</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/halo-magic-sleepsuits-recalled-for-choking-risk-a6877096785/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+          <t>What to Expect for Amazon Prime Day 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Best TV Brands of 2026</t>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Best Decking of 2026, Tested by Experts</t>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+          <t>Best Deals on Headphones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What to Expect for Amazon Prime Day 2026</t>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Best Deals on Headphones</t>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+          <t>Best Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+          <t>Best TV Brands of 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Best Nail Clippers for Every Need and Every Nail</t>
+          <t>Best Deals on Health and Beauty Products</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Talking Carts 11: Couponing 101</t>
+          <t>Best Washers for $800 or Less</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Best New SUVs and Cars for Under $30,000</t>
+          <t>Best Deals on Vacuums</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Simple Ways to Organize Your Home's Entryway</t>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>How to Save Money at the Gas Pump</t>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+          <t>How to Save Money at the Gas Pump</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+          <t>Best New SUVs and Cars for Under $30,000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Best Deals on Vacuums</t>
+          <t>Talking Carts 11: Couponing 101</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Best Washers for $800 or Less</t>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Best Deals on Health and Beauty Products</t>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Best Battery Platforms for Power Tools</t>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+          <t>Our Favorite Deals Right Now</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+          <t>Best Deals on Tech Products Right Now</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+          <t>Best Mattress Sales Right Now</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4 Best Glass Cleaners From Our Evaluations</t>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Best Deals on Tech Products Right Now</t>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Battery Platforms for Power Tools</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Best Mattress Sales Right Now</t>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Our Favorite Deals Right Now</t>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Best Deals on Pet Products</t>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+          <t>Best Hot Combs, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Best Hot Combs, Tested and Reviewed</t>
+          <t>42 Used Cars to Avoid Buying</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>42 Used Cars to Avoid Buying</t>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+          <t>How an Old-School Flip Phone Changed My Life</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>How an Old-School Flip Phone Changed My Life</t>
+          <t>Best Deals on Pet Products</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10 Best Deals on Electric Vehicles</t>
+          <t>Best Deals Under $50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>How to Stain a Deck</t>
+          <t>Best Deals Under $100</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Best Hybrid Cars for Under $35,000</t>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Best Deals Under $50</t>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+          <t>How to Stain a Deck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+          <t>10 Best Deals on Electric Vehicles</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Best Deals Under $100</t>
+          <t>Best Hybrid Cars for Under $35,000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Best Used SUVs With Standout Fuel Economy</t>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
         </is>
       </c>
     </row>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+          <t>Most Discounted New Cars Right Now</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Best Deals on Healthy-Home Essentials</t>
+          <t>Worst Deals on New Cars Right Now</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+          <t>Most and Least Reliable Coffee Makers</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best Deals on Fitness Equipment and Accessories</t>
+          <t>Best and Worst Laundry Detergents of 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+          <t>Best Deals on Smart Home Devices</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Best and Worst Laundry Detergents of 2026</t>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Most and Least Reliable Coffee Makers</t>
+          <t>Best Deals on Healthy-Home Essentials</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worst Deals on New Cars Right Now</t>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Best Composite Decking of 2026, Tested by Experts</t>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Best Deals on Smart Home Devices</t>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Most Discounted New Cars Right Now</t>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Best Deals on SUVs You Can Buy Right Now</t>
+          <t>Which iPhone Should You Buy?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+          <t>Best Deals on Home Products</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+          <t>Best Deals on Kitchen Products</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>How Do Hybrid Cars Work?</t>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Best New-Car Deals</t>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which iPhone Should You Buy?</t>
+          <t>Best New-Car Deals</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+          <t>How Do Hybrid Cars Work?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Best Deals on Kitchen Products</t>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Best Deals on Home Products</t>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Best Cars Made in the USA</t>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
         </is>
       </c>
     </row>
@@ -2899,12 +2899,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
         </is>
       </c>
     </row>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5 Best Umbrellas, Tested by Our Experts</t>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What's the Best Mac Laptop or Desktop for You?</t>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
         </is>
       </c>
     </row>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2984,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+          <t>Best Cars Made in the USA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3171,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
+          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
         </is>
       </c>
     </row>
@@ -3188,12 +3188,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
+          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
+          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
         </is>
       </c>
     </row>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,890 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>중요도</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cooking (Gas Range)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Frigidaire, Electrolux</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>- Electrolux가 Frigidaire 브랜드 가스 레인지 약 174,800대(미국) 및 5,300대(캐나다)에 대한 리콜 실시
+- 오븐 베이크 버너의 점화 지연으로 인한 화상 위험 발생(CPSC 발표)
+- 62건의 오작동 보고 및 30건의 화상 부상 사례 확인
+- 2025년 6월부터 2026년 1월 사이 Home Depot, Lowe's 등에서 판매된 23개 모델 대상</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>- Frigidaire 가스 레인지 라인업(Gallery, Professional 포함) 대다수가 리콜 대상에 포함되어 브랜드 신뢰도 하락 우려
+- Consumer Reports(CR) 평가 대상인 Frigidaire 가스 레인지 9개 모델 전량이 리콜 대상에 포함되었으며, 현재 추천(Recommended) 목록에서 모두 제외됨
+- 오븐 기능 사용 중단 권고 및 대규모 무상 수리(In-home repair) 진행에 따른 경쟁사 서비스 비용 부담 가중</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>- 경쟁사(Frigidaire)의 대규모 리콜 및 CR 추천 제외 상황을 활용하여 자사 가스 레인지 제품군의 안전성 및 신뢰도 강조 마케팅 전개
+- 점화 지연 등 유사한 안전 이슈가 자사 제품군에서 발생하지 않도록 품질 관리 및 사전 점검 프로세스 강화
+- 리콜 대상 모델 구매 고객의 교체 수요를 흡수하기 위한 타겟 프로모션 및 유통 채널 협력 검토</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Air Conditioners</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Frigidaire, Goodman, Trane, Lennox</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- 2026년 소비자 리포트(CR) 선정 최고의 전체 주택용 공기 소스 열펌프(Heat Pump) 4종 발표
+- Frigidaire 3T 모델이 종합 점수 87점으로 1위를 차지하며 냉난방 효율 및 소음 부문에서 우수성 입증
+- Goodman(83점), Trane(83점), Lennox(76점) 모델이 각각 정숙성, 가격 경쟁력, 브랜드 신뢰도를 바탕으로 추천 제품에 포함
+- 열펌프가 2024년 미국 시장에서 가스 보일러 판매량을 추월하며 주요 냉난방 솔루션으로 부상</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>- Frigidaire는 성능 테스트에서 최고점을 기록했으나 브랜드 신뢰도 데이터는 부족한 상태임
+- Trane은 매우 높은 사용자 만족도와 신뢰도 등급을 보유하여 실사용자 기반의 강점을 나타냄
+- 열펌프 성능의 70~90%가 설치 품질에 의해 결정되므로 제품 자체의 성능만큼이나 정교한 설치와 덕트 설계가 중요함
+- 연방 세액 공제 혜택 종료 이후에도 주 정부 및 지역 유틸리티 업체의 리베이트가 시장 수요의 주요 동인으로 작용 중</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>- 당사(Samsung) 및 주요 경쟁사(LG) 제품이 이번 추천 목록에 포함되지 않았으므로 북미 HVAC 시장 내 제품 경쟁력 재점검 필요
+- 북미 시장 내 브랜드 신뢰도(Reliability) 및 사용자 만족도 제고를 위한 서비스 및 품질 관리 전략 강화
+- 설치 품질이 제품 수명과 직결되는 제품 특성을 고려하여 설치 전문가 네트워크 교육 및 기술 지원 프로그램 확대 검토</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Roku, Sony, Hisense, TCL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- Consumer Reports(CR)가 발표한 '2026년 최고의 TV 브랜드' 평가에서 삼성전자가 종합 1위를 차지함
+- 삼성전자에 이어 LG, Roku, Sony가 상위권 브랜드로 선정됨
+- 삼성의 2025년형 QD-OLED 모델인 QN65S90F는 종합 점수 91점으로 최고 수준의 평가를 받음
+- LG의 2025년형 OLED 모델인 OLED65C5PUA는 종합 점수 88점으로 가격 대비 성능의 균형이 우수한 제품으로 평가됨</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>- 삼성전자는 실험실 테스트 결과와 소비자 설문 데이터를 결합한 통계 모델에서 가장 높은 브랜드 점수를 획득하며 시장 리더십을 입증함
+- 삼성 QD-OLED 제품군은 화질, HDR 성능, 사운드 및 AI 프로세서를 통한 게이밍 기능(144Hz 지원)에서 경쟁 우위를 확보함
+- LG전자는 OLED 부문에서 강력한 경쟁력을 유지하고 있으며, Sony는 고가 정책에도 불구하고 플래그십 라인업에서 높은 기술력을 인정받고 있음</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>- CR 브랜드 평가 1위 결과를 프리미엄 TV 시장 내 마케팅 소구점으로 적극 활용하여 브랜드 신뢰도를 제고해야 함
+- 경쟁사(LG)가 강조하는 스마트 기능(ThinQ, Alexa 내장) 및 편의 기능에 대응하여 자사 스마트싱스(SmartThings) 생태계의 연결성 우위를 지속 홍보할 필요가 있음
+- Dolby Vision 미지원에 대한 시장의 인식을 상쇄할 수 있도록 HDR10+ 및 자사 AI 화질 개선 기술의 실질적 이점을 지속적으로 교육 및 홍보해야 함</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Washing Machines</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LG, Electrolux, Maytag, Insignia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- 800달러 이하의 가성비 세탁기 중 성능과 효율이 우수한 모델 선정 및 발표
+- 세탁기 가격은 신모델 출시와 프로모션 공백기인 봄철에 상승하며, 블랙 프라이데이 등 주요 세일 기간에 하락하는 계절적 패턴을 보임
+- 드럼(Front-load), 교반식 통돌이(Agitator), 고효율 통돌이(HE Top-load) 등 유형별로 세탁 성능, 에너지 효율, 소음 등을 평가</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>- LG전자가 800달러 이하 보급형 시장에서 드럼 및 통돌이 부문 상위권을 휩쓸며 강력한 경쟁력을 입증함
+- LG WM3400CW 모델은 세탁 성능, 에너지 및 물 효율에서 최고 점수를 받으며 드럼 부문 전체 1위(87점) 및 CR 추천 모델로 선정됨
+- 통돌이 부문에서도 LG WT7005CW, WT7155CW 등이 추천 모델로 선정되며 보급형 라인업의 신뢰도를 확보함
+- 삼성전자 모델은 이번 800달러 이하 우수 제품 리스트에 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>- 보급형 세탁기 시장에서 LG전자의 독주를 견제하기 위해 800달러 이하 가격대의 라인업 강화 및 성능 개선 필요
+- LG가 강점을 보인 에너지/물 효율성 및 세탁 성능 지표를 벤치마킹하여 해당 가격대 제품의 마케팅 소구점으로 활용
+- 가격 민감도가 높은 소비자층을 공략하기 위해 기사에서 언급된 가격 상승기(4~5월) 대비 프로모션 전략 수립 필요</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Black+Decker, Shark, Miele, Eufy, iRobot, GorFanty, Tineco, Kenmore, Bissell, Hoover, Dirt Devil</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트에서 선정한 스틱, 로봇, 업라이트, 캐니스터 등 다양한 유형의 진공청소기 및 바닥 관리 제품 할인 정보 제공
+- Shark, Miele, iRobot 등 주요 브랜드 모델별 성능 테스트 결과, 브랜드 신뢰도, 소유자 만족도 기반의 추천 제품 상세 분석
+- 각 제품의 흡입력, 소음 수준, 반려동물 털 제거 성능, 사용 편의성 및 현재 할인 가격 정보 포함</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>- Shark 브랜드가 스틱, 업라이트, 코드형 등 다수 카테고리에서 우수한 성능과 높은 사용자 만족도를 기록하며 시장 내 강력한 영향력 확인
+- iRobot Roomba Max 705가 로봇 청소기 부문 테스트 모델 중 최고 성능을 기록하며 가격 인하를 통해 경쟁력 강화
+- Miele는 캐니스터 및 스틱 부문에서 높은 브랜드 신뢰도와 정교한 성능을 바탕으로 프리미엄 입지 유지
+- 삼성전자 및 LG전자의 제품은 이번 추천 및 할인 리스트에 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>- 북미 시장 내 Shark와 Miele의 높은 브랜드 신뢰도 및 사용자 만족도 요인(기능적 편의성, 내구성 등)에 대한 벤치마킹 분석 필요
+- 경쟁사들이 강점을 보이는 반려동물 특화 기능(Pet-friendly) 및 다기능성(Lift-away 등)에 대응하는 자사 제품의 기능 차별화 전략 검토
+- 주요 유통 채널(Best Buy, Amazon 등)에서의 경쟁사 가격 정책 및 프로모션 동향 모니터링을 통한 자사 마케팅 대응책 마련</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners (Stick Vacuums)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Bosch, Miele, Dyson, Shark, Bissell, Tineco, Hoover, Kenmore</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트(CR)가 실시한 2026년 스틱 청소기 성능 테스트 결과 발표
+- 삼성전자 'Bespoke AI Jet Ultra' 모델이 종합 점수 83점으로 전체 1위 및 '추천 제품(Recommended)' 선정
+- LG전자 'CordZero All-in-One A949KTMS'가 80점으로 2위 기록
+- 삼성전자 'Jet 85' 모델이 79점으로 3위를 차지하며 상위권 점유</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>- 삼성전자는 바닥, 카펫, 반려동물 털 제거 등 전 부문에서 우수한 성능을 보였으며, 특히 테스트 제품 중 가장 긴 배터리 구동 시간을 기록함
+- 삼성 브랜드는 멤버 설문조사 결과 신뢰도(Reliability)와 소유주 만족도(Owner Satisfaction)에서 매우 높은 점수를 획득, 타사 대비 배터리 문제 발생 가능성이 낮은 것으로 평가됨
+- LG전자는 카펫 청소 및 자동 먼지 비움 기능에서 호평받았으나, 브랜드 신뢰도 및 만족도는 중간 수준(midlevel)에 머무름
+- Bosch와 Miele 등 유럽 브랜드는 특정 편의 기능(90도 굴절 관, 가변형 먼지통)에서 강점을 보였으나 종합 점수에서 삼성에 밀림</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>- 프리미엄 라인업인 Bespoke AI Jet의 성능 우위와 독보적인 브랜드 신뢰도를 마케팅 핵심 소구점으로 활용하여 시장 지배력 강화 필요
+- 경쟁사(LG) 대비 우위에 있는 배터리 수명 및 신뢰성 데이터를 강조하여 장기 사용 안정성을 중시하는 소비자층 공략
+- 보급형 모델(Jet 85)의 가성비와 사용자 교체형 배터리, 디지털 디스플레이 등 편의 사양을 부각하여 중가 시장 점유율 확대 도모</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Washing Machines</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LG, Samsung, Speed Queen, Electrolux, Miele, Amana, Frigidaire, GE, Maytag, Whirlpool, Asko, Blomberg, Midea</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>- Consumer Reports(CR)가 2026년 최우수 세탁기 16종 선정 결과 발표
+- 드럼(Front-load), 교반식(Agitator), 고효율(HE) 통돌이 등 전 부문에서 LG전자 모델이 최상위권 차지
+- 세탁 성능, 에너지 효율, 물 소비량, 진동 및 소음, 브랜드 신뢰도 등을 종합 평가</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>- LG전자가 드럼 세탁기 부문 1~4위 및 통돌이 부문 상위권을 독식하며 압도적인 시장 지배력 확인
+- LG는 브랜드 신뢰도(Predicted Reliability) 조사에서도 드럼 및 고효율 통돌이 부문 최고 등급 획득
+- 삼성전자는 테스트 대상 브랜드에는 포함되었으나, 이번 추천 제품(Top Picks) 목록에서는 제외됨</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>- 경쟁사(LG)가 전 카테고리에서 'Recommended' 및 'Green Choice' 인증을 휩쓸고 있어 북미 시장 내 당사 입지 위축 우려
+- LG의 강점인 세탁 성능과 에너지 효율에 대응하는 기술적 우위 확보 및 브랜드 신뢰도 개선을 위한 품질 관리 강화 필요
+- AI 기능, UV 살균, 반려동물 특화 기능 등 최신 트렌드를 반영한 당사 제품의 차별화 포인트 강조 전략 수립 요망</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nokia, Apple, Google, Cat, Light Phone, Bigme, Sony</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>- 스마트폰 중독 탈피 및 디지털 미니멀리즘 실천을 위해 노키아 2780 플립폰을 일주일간 사용한 체험기
+- 아이폰 13 대비 제한된 기능(앱 부재, 불편한 GPS, 저화질 카메라)으로 인해 스크린 타임이 약 3시간 감소함
+- 현대 사회의 필수 기능(금융, 모빌리티, QR 코드 등) 부재로 인한 실생활의 불편함이 공존함을 확인</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>- 디지털 디톡스 수요 증가로 인해 단순 기능을 선호하는 '덤폰(Dumb Phone)' 시장의 니즈가 존재함
+- 스마트폰의 과도한 편의성이 오히려 사용자의 집중력을 분산시키고 감정적 의존도를 높이는 요인으로 작용함
+- 플립폰 사용자는 부족한 기능을 보완하기 위해 디지털 카메라, MP3 플레이어 등 별도 기기를 구매하는 경향을 보임</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>- 스마트폰 사용 시간을 제어하고자 하는 사용자를 위해 '디지털 웰빙' 기능(앱 제한, 집중 모드 등)의 고도화 및 마케팅 소구점 활용 필요
+- 고성능 카메라 및 앱 생태계가 스마트폰의 핵심 경쟁력임을 재확인하되, 단순함을 추구하는 틈새 시장의 사용자 경험(UX) 연구 가치 있음</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mainstays, Shark, Oreck, Kenmore, Atrix, Eureka, Bissell, Dirt Devil, Ryobi, LG, Lefant, Eufy, Roborock, iRobot, Black+Decker</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트가 각 청소기 카테고리별 최악의 성능을 기록한 모델과 이를 대체할 수 있는 추천 모델을 발표함
+- 무선 스틱 청소기 부문에서 Ryobi 모델(41점)이 카펫 청소 및 모서리 청소 성능 부족으로 최악의 모델 중 하나로 선정됨
+- LG전자의 CordZero Q3 C5323GW 모델이 해당 카테고리의 대체 추천 제품으로 선정됨
+- 기타 유선 스틱, 로봇 청소기, 핸디형 청소기 등 각 부문별 하위 모델과 Shark, Kenmore, Eufy 등의 추천 모델이 명시됨</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>- LG CordZero Q3 C5323GW는 약 300달러의 가격대로 추천 제품 중 가장 저렴한 축에 속하면서도 카펫 먼지 흡입, 반려동물 털 제거, 모서리 청소에서 우수한 성능(76점)을 인정받음
+- 무선 스틱 청소기 평가에서 카펫 청소 성능과 배터리 탈착 편의성이 주요 차별화 요소로 작용함
+- 삼성전자 제품은 이번 최악의 모델 및 대체 추천 모델 리스트에 모두 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>- 경쟁사인 LG전자가 중가형 무선 스틱 청소기 시장에서 '가성비'와 '성능'을 동시에 인정받으며 추천 모델로 등재된 점을 주시해야 함
+- 삼성 제트 등 자사 라인업의 카펫 청소 효율 및 배터리 편의성 등 컨슈머리포트 주요 평가 항목에 대한 경쟁 우위 분석 필요
+- 북미 시장 내 실질적인 구매 전환으로 이어지는 'Recommended' 등급 획득을 위한 중가형 라인업의 성능 최적화 전략 검토 필요</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Air Purifier</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Coway, Blueair, AirDoctor, Winix</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>- 산불 연기 및 미세 입자 제거 성능이 우수한 공기청정기 5종 선정 및 테스트 결과 발표
+- HEPA 필터와 대형 팬을 장착한 대형 공간용(350sq. ft. 이상) 제품을 중심으로 평가
+- 고속 및 저속 가동 시 입자 제거 효율, 소음, 필터 교체 및 에너지 비용을 포함한 연간 운영 비용을 종합적으로 고려</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>- 한국 브랜드인 Coway(Airmega ProX)가 종합 점수 85점으로 전체 1위를 차지하며 성능, 소음, 브랜드 신뢰도 면에서 최고 등급을 획득
+- Winix(9800)는 상대적으로 낮은 연간 운영 비용($164)과 우수한 가성비를 바탕으로 추천 제품에 포함
+- Blueair는 2개 모델이 상위권에 진입하며 강력한 정화 성능을 입증했으나 소음 및 유지 비용이 변수로 작용
+- 삼성전자 및 LG전자 제품은 이번 산불 연기 특화 추천 리스트에 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>- 북미 지역의 정기적인 산불 발생 및 대기질 악화 이슈와 연계하여 HEPA 필터의 미세 입자 제거 성능을 강조한 마케팅 전략 필요
+- 경쟁사(Coway, Winix)가 강점을 보인 대형 공간 정화 능력 및 유지 비용 효율성 측면에서 당사 제품의 경쟁력 재점검 요구
+- 소비자 리포트의 평가 기준인 저속 모드에서의 정화 효율 및 소음 최적화 기술을 차기 모델 개발 및 홍보에 반영 검토</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>- 애플의 최신 iPhone 17 라인업(17, 17e, Air, 17 Pro, 17 Pro Max) 및 이전 모델(16 시리즈)에 대한 소비자 리포트(CR)의 비교 분석
+- 모델별 디스플레이 크기, 칩셋 성능, 카메라 사양, 배터리 수명 및 내구성 테스트 결과 요약
+- iPhone 17 Pro(85점)와 iPhone 17(84점)을 포함한 주요 모델들이 CR '추천 제품(Recommended)'으로 선정됨</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>- iPhone 17 전 라인업에 A19/A19 Pro 칩셋을 탑재하여 생성형 AI(Apple Intelligence) 구동을 위한 하드웨어 기반 강화
+- 신규 슬림 모델인 'iPhone Air' 도입을 통해 5.6mm 두께의 초슬림 디자인과 티타늄 프레임을 강조하며 폼팩터 다변화 시도
+- 보급형 모델(17e) 및 일반 모델의 시작 저장 용량을 256GB로 상향하여 전반적인 제품 경쟁력 제고
+- 전 모델이 CR의 낙하 및 방수 테스트에서 최고 수준의 내구성 등급을 획득하며 하드웨어 신뢰성 입증</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>- 경쟁사의 AI 기능 전면 도입 및 하드웨어 사양 상향(저장 용량 등)에 대응하여 갤럭시 S 시리즈의 소프트웨어 최적화 및 가성비 전략 재점검 필요
+- 'iPhone Air'와 같은 슬림형 폼팩터에 대한 시장 반응을 모니터링하여 갤럭시 라인업의 디자인 차별화 및 경량화 전략에 반영 검토
+- 고성능 카메라 및 배터리 수명 우위를 점하고 있는 Pro Max 라인업에 대응하는 프리미엄 마케팅 강화 필요</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Laptops &amp; Desktops</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>- 애플의 신규 노트북 라인업인 MacBook Neo, MacBook Air(M5), MacBook Pro(M5 Pro/Max) 및 데스크탑 제품군 소개
+- MacBook Neo: $599의 초저가형 모델로 iPhone용 A18 Pro 칩 탑재, 학생 및 입문자 타겟
+- MacBook Air: M5 칩 탑재, WiFi 7 지원, 기본 저장용량 확대(512GB) 및 가격 $100 인상($1,099부터 시작)
+- MacBook Pro: M5 Pro/Max 칩 탑재, Thunderbolt 5 지원, 16인치 M5 Max 모델 기준 $3,899로 가격 대폭 인상
+- Consumer Reports 평가: MacBook Air(76점), MacBook Pro(81점)를 각각 '추천 제품(Recommended)'으로 선정</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>- 애플이 $599 가격대의 MacBook Neo를 통해 기존 윈도우 기반 보급형 노트북 및 크롬북 시장 점유율 탈환 시도
+- 고성능 라인업(Air, Pro)은 최신 규격(WiFi 7, Thunderbolt 5) 도입과 함께 가격을 인상하여 프리미엄 시장의 수익성 극대화 전략 추진
+- 자체 설계 칩셋(M5 시리즈 및 A18 Pro)을 기반으로 한 성능 우위와 전력 효율성을 마케팅 핵심 요소로 활용</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>- 애플의 저가형 노트북 시장 진입에 대응하여 갤럭시 북 시리즈의 보급형 라인업 강화 및 가격 경쟁력 확보 방안 검토 필요
+- 프리미엄 노트북 시장에서 WiFi 7 등 최신 통신 규격의 선제적 적용과 갤럭시 에코시스템 기반의 차별화된 사용자 경험 강조 필요
+- 경쟁사의 가격 인상 기조를 활용하여 고사양 노트북 시장에서의 상대적 가성비 및 프로모션 강화 전략 수립 가능</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Microwave</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Commercial Chef, Emerson, Hamilton Beach, Nostalgia Electrics, Proctor Silex, Vissani, Danby, Farberware, Insignia, Panasonic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트(CR)가 공간 효율성이 높은 소형 전자레인지(0.8 cu.ft. 이하) 5종 및 준중형 2종에 대한 테스트 결과와 추천 모델을 발표함
+- 소형 모델은 낮은 와트수(700W)로 인해 가열 속도가 전반적으로 느리며 용량이 작다는 한계가 있으나, 소음 및 해동 균일성 측면에서는 양호한 성능을 보임
+- 주요 추천 모델로 Commercial Chef(CHM770B, CHM7MB), Danby(DDMW007501G1), Farberware(FMO07ABTBKA), Insignia(NS-MW7BK5) 등이 선정됨</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>- 소형 전자레인지 카테고리에서 삼성전자와 LG전자의 제품은 추천 목록에 포함되지 않았으며, 주로 저가형/PB 브랜드(Commercial Chef, Insignia 등)가 시장을 점유함
+- 브랜드 신뢰도 조사 결과 Commercial Chef, Emerson, Hamilton Beach 등은 우수한 등급을 받았으나, 대다수 소형 모델의 사용자 만족도는 낮게 나타남
+- Panasonic(NN-SD47QS)은 소형에 가까운 크기임에도 1,000W의 출력과 우수한 가열 균일성, 저소음 성능을 바탕으로 높은 종합 점수를 획득함</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>- 당사(Samsung)의 소형/엔트리급 전자레인지 라인업이 CR의 공간 효율성 및 가성비 중심 추천 리스트에서 누락되어 있어 해당 시장 내 인지도 점검이 필요함
+- 소형 모델의 고질적 약점인 가열 속도와 균일성을 개선한 프리미엄 컴팩트 라인업의 특장점을 강화하여 차별화 전략 수립 가능
+- 경쟁사 Panasonic과 같이 저소음 및 사용 편의성(Ease of Use)에서 높은 평가를 받을 수 있도록 엔트리급 모델의 감성 품질 개선 요망</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Desktop Computers</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>HP, Apple, Dell, Asus, Intel, AMD</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>- 2026년 최우수 데스크탑 컴퓨터 9종 선정 및 부문별 순위 발표
+- 올인원(All-in-one), 미니 PC, 타워형의 세 가지 폼팩터로 구분하여 성능, 신뢰도, 소비자 만족도 평가
+- 주요 추천 모델로 HP EliteStudio, Apple iMac M4, Dell 24" All-in-One, Apple Mac Studio, Asus NUC 14 Pro 등 선정</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>- AI 성능 중심의 시장 변화: Intel Ultra, AMD Ryzen AI, Apple M-series 등 AI 처리 역량을 갖춘 프로세서 탑재 모델이 상위권 차지
+- 미니 PC 카테고리 성장: 공간 효율성과 고성능을 동시에 요구하는 원격/하이브리드 근무 환경에 따라 미니 PC 세그먼트 비중 확대
+- 브랜드 평판 격차: Apple은 신뢰도와 만족도에서 최고점을 기록한 반면, HP와 Asus는 해당 지표에서 평균 또는 평균 이하 기록</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>- 당사(Samsung) 제품이 추천 목록 및 주요 언급에서 제외된 상태이므로, 데스크탑/올인원 라인업의 북미 시장 경쟁력 재점검 필요
+- 경쟁사들이 강조하는 로컬 AI 실행 능력 및 AI 어시스턴트 최적화 기능을 당사 컴퓨팅 제품군(Galaxy Book 등)과 연계한 차별화 전략 수립 요망
+- 소비자 리포트의 주요 평가 요소인 브랜드 신뢰도 및 소유자 만족도 제고를 위한 품질 관리 및 사후 서비스 강화 대책 검토</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners (Robot Vacuums)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dreame, Dyson, Eufy, Eureka, iRobot, Samsung</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>- 반려동물 털 제거 성능이 우수한 2026년 최우수 로봇청소기 6종 선정 및 발표
+- 삼성, 다이슨, 아이로봇, 드리미, 유피, 유레카 브랜드의 주요 모델 포함
+- 카펫 내 털 흡입력, 브러시 엉킴 방지, 내비게이션 및 부가 기능(자동 비움 등)을 기준으로 평가
+- 삼성 Jet Bot 모델은 고가이나 청소 및 물걸레 성능의 우수성을 인정받아 추천 목록에 포함</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>- 삼성 Jet Bot VR7MD96514G는 테스트된 모든 제품 중 최고의 물걸레 성능을 보유한 것으로 평가됨
+- 다이슨은 흡입 효율과 브랜드 신뢰도에서 높은 점수를 받았으나 사용자 만족도는 낮게 나타남
+- 드리미(Dreame)는 펫 전용 구역 설정 및 비디오 모니터링 등 반려동물 특화 기능으로 차별화
+- 유피(Eufy)와 유레카(Eureka) 등 저가형 모델도 기본 흡입 성능과 가성비 측면에서 긍정적 평가를 받음</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>- 타사 대비 압도적인 성능을 보인 '물걸레 세척 및 건조' 기능을 포함한 올인원 스테이션의 편의성을 프리미엄 마케팅 핵심 요소로 활용
+- 드리미 등 경쟁사가 도입한 반려동물 특화 소프트웨어 기능(펫 존, 모니터링)에 대응하는 스마트싱스(SmartThings) 기반의 고도화된 기능 개발 검토
+- 고가 제품군에서의 성능 우위를 바탕으로 프리미엄 시장 내 브랜드 입지 강화 전략 수립</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -492,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +1396,2131 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4 Best Single-Serve Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-pod-coffee-makers-a3468890273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>What to Expect for Amazon Prime Day 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Deals on Headphones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Talking Carts 11: Couponing 101</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best New SUVs and Cars for Under $30,000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>How to Save Money at the Gas Pump</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Best Deals on Health and Beauty Products</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Battery Platforms for Power Tools</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Deals on Tech Products Right Now</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Best Mattress Sales Right Now</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Our Favorite Deals Right Now</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best Deals on Pet Products</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Best Hot Combs, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>42 Used Cars to Avoid Buying</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>How to Clean Your Lawn Mower Deck</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-clean-your-lawn-mower-deck-a4858405895/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Best Wood Stains of 2026 (and a Few of the Worst)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/best-wood-stains-from-consumer-reports-tests-a4478428531/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>How to Get Your Lawn Mower or Tractor Ready for Mowing Season</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-get-your-lawn-mower-ready-for-spring-a8196766008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Best Time to Fertilize Your Lawn</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-care/dont-bother-fertilizing-your-lawn-twice-a-year-a5780099997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10 Best Deals on Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>How to Stain a Deck</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Best Hybrid Cars for Under $35,000</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Best Deals Under $50</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Best Deals Under $100</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Deals on Healthy-Home Essentials</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Best and Worst Laundry Detergents of 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Most and Least Reliable Coffee Makers</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Worst Deals on New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Best Deals on Smart Home Devices</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Most Discounted New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>How Do Hybrid Cars Work?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Best New-Car Deals</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Best Deals on Kitchen Products</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Best Deals on Home Products</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Best Cars Made in the USA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7 Best E-Bike Covers of 2026, According to Experts</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/electric-bikes/best-e-bike-covers-a5685855846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Are Hybrids a Smart Choice Right Now?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/why-hybrid-vehicles-are-a-smart-choice-right-now-a2736240282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Deals Under $25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-25-a4183478310/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gas vs. Battery Lawn Mower: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/gas-vs-electric-lawn-mower-which-is-better-a1057954260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>How to Check Engine Oil the Right Way</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6 Best Compression Socks, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/underwear-socks/best-compression-socks-a2750797916/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>We Tested 49 More Baby Formulas for Lead and Arsenic</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-formula/liquid-baby-formula-contaminants-test-results-a8639602154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Safest Small SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-small-suvs-a9206654113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ford and Lincoln SUVs Recalled to Fix Windshield Wipers</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/ford-lincoln-suvs-recalled-to-fix-windshield-wiper-motor-a5559013983/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.7 Million More Ford and Lincoln SUVs Recalled to Fix Screens</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/more-ford-and-lincoln-suvs-recalled-to-fix-backup-cameras-a4514261791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Used Cars and SUVs Under $10,000 That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-used-cars-suvs-under-10000-dollars-a8966344858/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Thousands of Halo Magic Sleepsuits Recalled for Choking Risk</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/halo-magic-sleepsuits-recalled-for-choking-risk-a6877096785/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Baby Product Recalls Parents Should Know About in 2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/baby-product-recalls-parents-caregivers-should-be-aware-of-a5859124070/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Most Reliable 3-Year-Old Cars and SUVs That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/most-reliable-3-year-old-cars-and-suvs-a7361029795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient SUVs</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/the-most-fuel-efficient-suvs-best-mpg-a5599990140/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Talking Carts 10: The Pink Tax</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-10-the-pink-tax-a4218079662/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>More Than 80,000 Babysense Baby Monitors Recalled for Fire Hazard Risk</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/babysense-max-view-baby-monitors-recalled-for-fire-risk-a3285333268/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,2131 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4 Best Single-Serve Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-pod-coffee-makers-a3468890273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>What to Expect for Amazon Prime Day 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Deals on Headphones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Talking Carts 11: Couponing 101</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best New SUVs and Cars for Under $30,000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>How to Save Money at the Gas Pump</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Best Deals on Health and Beauty Products</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Battery Platforms for Power Tools</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Deals on Tech Products Right Now</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Best Mattress Sales Right Now</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Our Favorite Deals Right Now</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best Deals on Pet Products</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Best Hot Combs, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>42 Used Cars to Avoid Buying</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>How to Clean Your Lawn Mower Deck</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-clean-your-lawn-mower-deck-a4858405895/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Best Wood Stains of 2026 (and a Few of the Worst)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/best-wood-stains-from-consumer-reports-tests-a4478428531/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>How to Get Your Lawn Mower or Tractor Ready for Mowing Season</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-get-your-lawn-mower-ready-for-spring-a8196766008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Best Time to Fertilize Your Lawn</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-care/dont-bother-fertilizing-your-lawn-twice-a-year-a5780099997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10 Best Deals on Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>How to Stain a Deck</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Best Hybrid Cars for Under $35,000</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Best Deals Under $50</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Best Deals Under $100</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Deals on Healthy-Home Essentials</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Best and Worst Laundry Detergents of 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Most and Least Reliable Coffee Makers</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Worst Deals on New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Best Deals on Smart Home Devices</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Most Discounted New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>How Do Hybrid Cars Work?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Best New-Car Deals</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Best Deals on Kitchen Products</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Best Deals on Home Products</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Best Cars Made in the USA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7 Best E-Bike Covers of 2026, According to Experts</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/electric-bikes/best-e-bike-covers-a5685855846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Are Hybrids a Smart Choice Right Now?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/why-hybrid-vehicles-are-a-smart-choice-right-now-a2736240282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Deals Under $25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-25-a4183478310/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gas vs. Battery Lawn Mower: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/gas-vs-electric-lawn-mower-which-is-better-a1057954260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>How to Check Engine Oil the Right Way</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6 Best Compression Socks, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/underwear-socks/best-compression-socks-a2750797916/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>We Tested 49 More Baby Formulas for Lead and Arsenic</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-formula/liquid-baby-formula-contaminants-test-results-a8639602154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Safest Small SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-small-suvs-a9206654113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ford and Lincoln SUVs Recalled to Fix Windshield Wipers</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/ford-lincoln-suvs-recalled-to-fix-windshield-wiper-motor-a5559013983/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.7 Million More Ford and Lincoln SUVs Recalled to Fix Screens</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/more-ford-and-lincoln-suvs-recalled-to-fix-backup-cameras-a4514261791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Used Cars and SUVs Under $10,000 That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-used-cars-suvs-under-10000-dollars-a8966344858/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Thousands of Halo Magic Sleepsuits Recalled for Choking Risk</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/halo-magic-sleepsuits-recalled-for-choking-risk-a6877096785/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Baby Product Recalls Parents Should Know About in 2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/baby-product-recalls-parents-caregivers-should-be-aware-of-a5859124070/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Most Reliable 3-Year-Old Cars and SUVs That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/most-reliable-3-year-old-cars-and-suvs-a7361029795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient SUVs</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/the-most-fuel-efficient-suvs-best-mpg-a5599990140/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Talking Carts 10: The Pink Tax</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-10-the-pink-tax-a4218079662/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>More Than 80,000 Babysense Baby Monitors Recalled for Fire Hazard Risk</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/babysense-max-view-baby-monitors-recalled-for-fire-risk-a3285333268/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -537,12 +537,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+          <t>What to Expect for Amazon Prime Day 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
         </is>
       </c>
     </row>
@@ -554,12 +554,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Best TV Brands of 2026</t>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
         </is>
       </c>
     </row>
@@ -588,12 +588,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Best Decking of 2026, Tested by Experts</t>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+          <t>Best Deals on Headphones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
         </is>
       </c>
     </row>
@@ -656,12 +656,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What to Expect for Amazon Prime Day 2026</t>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
         </is>
       </c>
     </row>
@@ -673,12 +673,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Best Deals on Headphones</t>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
         </is>
       </c>
     </row>
@@ -690,12 +690,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+          <t>Best Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
         </is>
       </c>
     </row>
@@ -724,12 +724,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+          <t>Best TV Brands of 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
         </is>
       </c>
     </row>
@@ -792,12 +792,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Best Nail Clippers for Every Need and Every Nail</t>
+          <t>Best Deals on Health and Beauty Products</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Talking Carts 11: Couponing 101</t>
+          <t>Best Washers for $800 or Less</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Best New SUVs and Cars for Under $30,000</t>
+          <t>Best Deals on Vacuums</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Simple Ways to Organize Your Home's Entryway</t>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>How to Save Money at the Gas Pump</t>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+          <t>How to Save Money at the Gas Pump</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+          <t>Best New SUVs and Cars for Under $30,000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Best Deals on Vacuums</t>
+          <t>Talking Carts 11: Couponing 101</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Best Washers for $800 or Less</t>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Best Deals on Health and Beauty Products</t>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Best Battery Platforms for Power Tools</t>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+          <t>Our Favorite Deals Right Now</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+          <t>Best Mattress Sales Right Now</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+          <t>Best Deals on Tech Products Right Now</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4 Best Glass Cleaners From Our Evaluations</t>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Best Deals on Tech Products Right Now</t>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Battery Platforms for Power Tools</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Best Mattress Sales Right Now</t>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Our Favorite Deals Right Now</t>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Best Deals on Pet Products</t>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+          <t>Best Hot Combs, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Best Hot Combs, Tested and Reviewed</t>
+          <t>42 Used Cars to Avoid Buying</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>42 Used Cars to Avoid Buying</t>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+          <t>How an Old-School Flip Phone Changed My Life</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>How an Old-School Flip Phone Changed My Life</t>
+          <t>Best Deals on Pet Products</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10 Best Deals on Electric Vehicles</t>
+          <t>Best Deals Under $50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>How to Stain a Deck</t>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Best Hybrid Cars for Under $35,000</t>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+          <t>Best Deals Under $100</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Best Deals Under $50</t>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
         </is>
       </c>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Best Deals Under $100</t>
+          <t>Best Hybrid Cars for Under $35,000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
         </is>
       </c>
     </row>
@@ -1591,12 +1591,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+          <t>How to Stain a Deck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+          <t>10 Best Deals on Electric Vehicles</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
         </is>
       </c>
     </row>
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Best Used SUVs With Standout Fuel Economy</t>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
         </is>
       </c>
     </row>
@@ -1659,12 +1659,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+          <t>Most Discounted New Cars Right Now</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
         </is>
       </c>
     </row>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
         </is>
       </c>
     </row>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Best Deals on Healthy-Home Essentials</t>
+          <t>Worst Deals on New Cars Right Now</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+          <t>Most and Least Reliable Coffee Makers</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
         </is>
       </c>
     </row>
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best Deals on Fitness Equipment and Accessories</t>
+          <t>Best and Worst Laundry Detergents of 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+          <t>Best Deals on Smart Home Devices</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Best and Worst Laundry Detergents of 2026</t>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
         </is>
       </c>
     </row>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Most and Least Reliable Coffee Makers</t>
+          <t>Best Deals on Healthy-Home Essentials</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worst Deals on New Cars Right Now</t>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
         </is>
       </c>
     </row>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Best Deals on Smart Home Devices</t>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Best Composite Decking of 2026, Tested by Experts</t>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Most Discounted New Cars Right Now</t>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
         </is>
       </c>
     </row>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Best Deals on SUVs You Can Buy Right Now</t>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+          <t>Best Deals on Home Products</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
         </is>
       </c>
     </row>
@@ -1897,12 +1897,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+          <t>Best Deals on Kitchen Products</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
         </is>
       </c>
     </row>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>How Do Hybrid Cars Work?</t>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
         </is>
       </c>
     </row>
@@ -1931,12 +1931,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Best New-Car Deals</t>
+          <t>Which iPhone Should You Buy?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+          <t>How Do Hybrid Cars Work?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which iPhone Should You Buy?</t>
+          <t>Best New-Car Deals</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
         </is>
       </c>
     </row>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Best Deals on Kitchen Products</t>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
         </is>
       </c>
     </row>
@@ -2016,12 +2016,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Best Deals on Home Products</t>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
         </is>
       </c>
     </row>
@@ -2050,12 +2050,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Best Cars Made in the USA</t>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
         </is>
       </c>
     </row>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5 Best Umbrellas, Tested by Our Experts</t>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
         </is>
       </c>
     </row>
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
         </is>
       </c>
     </row>
@@ -2118,12 +2118,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What's the Best Mac Laptop or Desktop for You?</t>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
         </is>
       </c>
     </row>
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+          <t>Best Cars Made in the USA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
         </is>
       </c>
     </row>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
         </is>
       </c>
     </row>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
         </is>
       </c>
     </row>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
         </is>
       </c>
     </row>
@@ -2373,12 +2373,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>How to Check Engine Oil the Right Way</t>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
         </is>
       </c>
     </row>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+          <t>How to Check Engine Oil the Right Way</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
         </is>
       </c>
     </row>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,1058 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>중요도</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cooktop/Range</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Frigidaire, Electrolux</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>- Electrolux가 Frigidaire 브랜드 가스 레인지 약 174,800대(미국 및 캐나다) 리콜 실시
+- 오븐 베이크 버너의 점화 지연으로 인한 화상 위험 발생 및 30건의 부상 사례 보고
+- 2025년 6월부터 2026년 1월까지 판매된 Frigidaire, Gallery, Professional 시리즈 23개 모델 대상
+- Consumer Reports(CR) 평가 대상인 Frigidaire 가스 레인지 9종 전 모델이 리콜에 포함되어 추천(Recommended) 목록에서 제외</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>- 주요 경쟁사인 Frigidaire 가스 레인지 라인업 전반에 걸친 대규모 리콜로 브랜드 신뢰도 및 CR 평가 점수 급락
+- 점화 시스템의 하드웨어적 결함이 실질적인 인명 피해로 이어져 북미 시장 내 가스 조리기기 부문 경쟁 구도 변화 가능성 상존</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>- 리콜 대상 모델과 유사한 점화 방식을 사용하는 당사 가스 레인지 제품군의 안전 메커니즘 및 품질 프로세스 긴급 점검
+- 경쟁사 제품의 CR 추천 제외 상황을 기회로 삼아 당사 조리기기의 안전성 및 신뢰성을 강조하는 북미 시장 마케팅 강화 검토</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Air Conditioners (Heat Pumps)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Frigidaire, Goodman, Trane, Lennox</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>- 2026년 최고의 전체 주택용 공기원(Air-source) 히트펌프 4종 선정 및 성능 테스트 결과 발표
+- Frigidaire 3T 모델이 가열 및 냉각 효율, 저소음 항목에서 최고점(87점)을 기록하며 1위 차지
+- Goodman(83점), Trane(83점), Lennox(76점) 제품이 성능 및 신뢰도를 바탕으로 추천 제품(CR Recommended)에 포함
+- 히트펌프가 2024년 미국 시장에서 가스 보일러 판매량을 처음으로 추월했으며, 에너지 효율 및 탄소 배출 감소의 핵심 대안으로 부상</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>- Frigidaire와 Goodman은 효율성 면에서 우수하나, Trane과 Lennox는 브랜드 신뢰도 및 사용자 만족도 측면에서 강점을 보유
+- 히트펌프 성능의 70~90%가 설치 품질에 좌우됨에 따라, 제품 자체의 성능만큼이나 전문적인 설치 및 덕트 설계의 중요성이 강조됨
+- 삼성 및 LG 등 국내 주요 가전 브랜드는 이번 2026년 상위 추천 리스트에 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>- 북미 HVAC 시장 내 Trane, Lennox 등 전통적 강자들의 브랜드 신뢰도가 견고하므로, 자사 제품의 내구성 및 사용자 만족도 지표 개선을 위한 전략 수립 필요
+- 고효율 및 저소음 경쟁력을 갖춘 히트펌프 라인업의 CR 평가 모니터링을 강화하고, 북미 현지 설치 품질 보증을 위한 파트너십 및 서비스 네트워크 점검 요구됨</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Roku, Sony</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>- Consumer Reports(CR)가 실험실 테스트, 설문 데이터, 가격을 종합하여 2026년 최고의 TV 브랜드로 삼성(Samsung)을 선정
+- 삼성은 종합 브랜드 점수에서 1위를 차지했으며 LG, Roku, Sony가 그 뒤를 이음
+- 삼성의 2025년형 QD-OLED 모델인 QN65S90F는 종합 점수 91점으로 최고 수준의 평가를 받음
+- LG의 OLED65C5PUA(88점), 소니의 K65XR80M2(81점) 등 경쟁사 주요 모델 대비 높은 점수 기록</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>- 삼성은 화질, 사운드 등 성능 지표뿐만 아니라 가격 경쟁력과 사용자 만족도를 결합한 종합 평가에서 경쟁사(LG, Sony)를 제치고 최상위 브랜드 지위 확보
+- 특히 QD-OLED 라인업이 LG의 OLED 라인업보다 높은 점수를 획득하며 차세대 디스플레이 시장에서의 기술적 우위 입증
+- 게이밍 특화 기능(144Hz 지원) 및 AI 프로세서 성능이 주요 차별화 요소로 작용</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>- CR의 '2026년 최고 TV 브랜드 1위' 선정 결과를 북미 시장 프리미엄 마케팅 및 프로모션의 핵심 소재로 활용 권고
+- 경쟁사 대비 우위에 있는 종합 점수(91점 vs 88점)를 강조하여 OLED TV 시장 내 점유율 확대 전략 추진
+- Dolby Vision 미지원 등 기술적 사양 차이에 대한 소비자 인식을 HDR10+ 및 AI 화질 최적화 성능 강조를 통해 방어할 필요 있음</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Washer</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LG, Electrolux, Maytag, Insignia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>- 800달러 이하의 경제적인 세탁기 중 성능과 효율성이 우수한 모델 선정 결과 발표
+- 봄철 신제품 출시 및 프로모션 감소로 인한 세탁기 가격 상승 추세 분석 및 구매 적기 안내
+- 드럼, 교반식(Agitator), 고효율(HE) 통돌이 세탁기 부문별 주요 추천 제품 정보 제공</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>- 경쟁사 LG전자가 드럼 및 교반식 통돌이 세탁기 부문에서 'CR 추천(Recommended)' 모델을 휩쓸며 가성비 시장 내 강력한 우위 점함
+- LG WM3400CW 모델은 세탁 성능, 에너지 및 물 효율성에서 최고점을 기록하며 드럼 세탁기 부문 종합 1위(87점) 차지
+- LG WT7005CW 및 WT7155CW 모델 또한 통돌이 부문에서 세탁 성능과 효율성을 인정받아 상위권 랭크
+- 본 기사 내 800달러 이하 추천 리스트에 삼성전자 모델은 단 하나도 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>- 보급형 세탁기 시장($800 이하)에서 LG전자의 CR 추천 모델 독식에 따른 브랜드 이미지 및 점유율 잠식 우려
+- 해당 가격대 삼성 모델의 CR 평가 결과 및 가격 경쟁력 재점검 필요
+- 북미 소비자의 고물가 상황을 고려하여, 성능과 효율성을 겸비한 보급형 라인업의 마케팅 강화 및 프로모션 전략 수립 권고</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Black+Decker, Shark, Miele, Eufy, iRobot, GorFanty, Tineco, Kenmore, Bissell, Hoover, Dirt Devil</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트(CR)가 봄맞이 청소 시즌을 대비하여 성능, 브랜드 신뢰도, 고객 만족도 및 할인율을 종합 평가한 유형별 최적의 진공청소기 추천 목록을 발표함
+- 스틱형, 로봇형, 직립형(Upright), 캐니스터형, 카펫 클리너 등 전 카테고리에 걸쳐 주요 할인 모델과 성능 특징을 상세히 기술함
+- Shark, Miele, Kenmore 등 주요 가전 브랜드들이 각 부문에서 우수한 평가를 받으며 추천 제품으로 선정됨</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>- Shark 브랜드는 스틱형부터 직립형까지 다수의 모델이 추천되었으며, 특히 브랜드 신뢰도와 소유주 만족도에서 높은 점수를 기록하며 시장 내 강력한 영향력을 입증함
+- Miele는 프리미엄 캐니스터 및 스틱형 부문에서 높은 신뢰도를 바탕으로 상위권을 유지하고 있으며, iRobot은 로봇 청소기 부문에서 최고 성능 모델로 평가됨
+- 삼성전자 및 LG전자의 제품은 이번 추천 및 할인 리스트에 포함되지 않아, 해당 카테고리 내 북미 시장 경쟁력 및 인지도 점검이 필요함</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>- Shark의 'PowerDetect'와 같은 자동 바닥 감지 기술 및 양방향 흡입 기능 등 경쟁사의 차별화된 기능에 대응하는 당사 제품의 기술적 소구점 강화 필요
+- 컨슈머리포트의 브랜드 신뢰도 및 만족도 조사에서 상위권을 차지한 경쟁사들의 전략을 분석하여 당사 제품의 서비스 및 품질 신뢰도 제고 방안 마련 권고
+- 주요 시즌별 프로모션 시기에 맞춰 CR 추천 목록에 진입할 수 있도록 제품 성능 개선 및 전략적 마케팅 노출 확대 필요</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners (Stick Vacuums)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Bosch, Miele, Dyson, Bissell, Shark, Tineco</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트가 2026년 최우수 스틱 청소기 9종을 선정하여 발표함.
+- 삼성전자의 'Bespoke AI Jet Ultra'가 총점 83점으로 전체 1위를 차지하며 '추천 제품(Recommended)'으로 선정됨.
+- LG전자의 'CordZero All-in-One'이 총점 80점으로 2위를 기록함.
+- 삼성전자의 'Jet 85' 모델이 총점 79점으로 3위에 올라 상위권을 점유함.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>- 삼성전자는 청소 성능(마룻바닥, 반려동물 털, 카펫)뿐만 아니라 배터리 구동 시간 및 브랜드 신뢰도에서 최고 수준의 평가를 받음.
+- 특히 삼성 무선 청소기는 타 브랜드 대비 배터리 문제가 발생할 가능성이 낮아 브랜드 신뢰도와 소유주 만족도에서 높은 점수를 획득함.
+- LG전자는 청소 성능 면에서는 우수하나, 브랜드 신뢰도 및 만족도 부문에서 삼성보다 낮은 '중간 수준(midlevel)'에 머무름.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>- 삼성 프리미엄 모델(Bespoke AI Jet)의 압도적인 성능과 배터리 신뢰도를 경쟁사(LG, Dyson 등) 대비 차별화된 마케팅 포인트로 강화해야 함.
+- 중가형 모델(Jet 85)의 우수한 가성비와 사용자 교체형 배터리 등 편의성을 강조하여 실속형 소비자 층의 점유율 확대 필요.
+- 자동 먼지 비움 스테이션과 AI 기반 바닥 감지 기능 등 기술적 우위 요소를 지속적으로 노출하여 프리미엄 이미지를 공고히 할 것.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Washing Machines</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LG, Samsung, Speed Queen, Electrolux, Miele, GE, Whirlpool, Maytag, Amana, Frigidaire</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>- 2026년 소비자 리포트(CR) 선정 최고의 세탁기 16선 발표
+- LG전자가 드럼(Front-load), 고효율 통돌이(HE Top-load), 교반식(Agitator) 등 전 카테고리에서 추천 제품(CR Recommended) 및 상위권 독점
+- 주요 평가 항목은 세탁 성능, 에너지 및 물 효율성, 진동/소음, 브랜드 신뢰도 등임
+- LG전자는 브랜드 신뢰도 조사에서도 드럼 및 고효율 통돌이 부문 가장 신뢰할 수 있는 브랜드로 선정</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>- 경쟁사(LG)가 성능, 효율성, 신뢰도 전 지표에서 압도적인 평가를 받으며 시장 내 강력한 추천 순위 점유
+- 특히 LG는 'Green Choice' 인증을 다수 획득하며 친환경 및 고효율 이미지 선점
+- 삼성전자는 테스트 대상 브랜드에는 포함되었으나, 이번 주요 추천 모델 리스트에는 단 한 개의 제품도 이름을 올리지 못함</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>- 북미 세탁기 시장 내 LG전자의 독주 체제에 대응하기 위한 제품 성능 및 에너지 효율성 재검토 필요
+- 소비자 리포트의 주요 평가 지표인 '브랜드 신뢰도(Reliability)' 및 '사용자 만족도' 제고를 위한 품질 관리 강화 전략 수립 요구됨
+- 삼성 세탁기만의 차별화된 AI 기능 및 디자인 요소를 강조한 비교 우위 마케팅 및 제품 노출 확대 방안 마련 필요</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nokia, Apple, Google</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>- 스마트폰 중독 및 스크린 타임 감소를 위해 노키아 2780 플립폰(Dumb Phone)을 일주일간 사용한 체험 사례
+- 기존 아이폰 13 사용자가 디지털 미니멀리즘을 목적으로 기능을 제한한 피처폰으로 기기 변경 시도
+- 앱 스토어 부재로 인한 모빌리티 호출, 간편 결제, QR 코드 메뉴 확인 등 현대적 편의 기능 사용의 한계 노출
+- T9 방식의 문자 입력, 저해상도 카메라, 내비게이션의 불편함 등 기술적 제약 사항 확인</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>- 소비자들 사이에서 과도한 연결성과 스크린 타임에 대한 피로감으로 인해 의도적으로 기능을 제한한 '덤폰(Dumb Phone)' 트렌드 확산
+- 스마트폰의 핵심 편의 기능(금융, 교통, 지도)은 유지하면서도 소셜 미디어 등 중독성 요소만 배제하고자 하는 니즈 존재
+- 디지털 디톡스를 위해 세컨드 기기를 운용하거나 특정 시간대 기기 사용을 제한하는 사용자 층 확인</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>- 갤럭시 기기 내 '모드 및 루틴' 기능을 고도화하여 별도의 기기 구매 없이도 강력한 디지털 디톡스 환경(앱 차단, 흑백 모드 등)을 제공하는 마케팅 강화 필요
+- 덤폰 사용자가 겪는 핵심 불편 사항인 내비게이션과 결제 기능을 유지하면서도 중독성을 낮춘 '미니멀 모드' UI 개발 검토
+- 시니어 및 키즈 시장 외에 디지털 피로도를 느끼는 MZ세대를 타겟으로 한 단순화된 기기 또는 소프트웨어 솔루션 제안</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mainstays, Shark, Oreck, Kenmore, Atrix, Eureka, Bissell, Dirt Devil, Ryobi, LG, Lefant, Eufy, Roborock, iRobot, Black+Decker</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트가 각 청소기 카테고리별 성능 미달 제품(Worst)과 이를 대체할 추천 제품(What to Buy Instead) 목록을 발표함
+- 무선 스틱 청소기 부문에서 Ryobi 모델이 최하위권으로 선정된 반면, LG CordZero Q3 C5323GW가 우수한 대안으로 추천됨
+- 로봇 청소기, 유선 스틱, 업라이트, 캐니스터 등 주요 카테고리별로 흡입력, 소음, 미세먼지 배출 등을 기준으로 평가함</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>- LG CordZero Q3 C5323GW 모델은 약 300달러의 가격대에서 가성비가 뛰어난 무선 스틱 청소기로 평가받으며 추천 제품에 포함됨
+- 해당 모델은 타 스틱 청소기가 고전하는 카펫 청소 성능에서 우수한 성적을 거두었으며, 반려동물 털 제거 및 모서리 청소 능력이 강점으로 부각됨
+- 컨슈머리포트는 저가형 모델의 고질적 문제로 미세먼지 재배출, 약한 흡입력, 소음 문제를 지적하며 이를 해결한 모델들을 추천함</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>- 경쟁사(LG)의 보급형 무선 스틱 청소기가 성능과 가격 경쟁력을 동시에 인정받고 있으므로, 해당 가격대(300달러 내외) 자사 라인업의 성능 지표 재점검 필요
+- 컨슈머리포트의 주요 평가 항목인 카펫 청소 효율 및 미세먼지 배출 차단 성능(Clean Emissions)에 대한 자사 제품의 우위성을 마케팅에 적극 활용 권고
+- 워스트 제품으로 선정된 모델들의 단점(흡입력 저하, 배터리 호환성 위주의 마케팅 등)을 반면교사 삼아 실질적 청소 성능 중심의 소구점 강화</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Vacuums &amp; Air Purifiers</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>iRobot, Dyson, Shark, Blueair, HoMedics, Tineco, Dirt Devil, Hoover, Levoit, Persil, Windex, Fabuloso, Mrs. Meyers</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>- 봄맞이 대청소 시즌을 맞아 진공청소기, 로봇청소기, 공기청정기 등 주요 가전제품의 할인 혜택 및 CR 테스트 결과 발표
+- iRobot, Dyson, Shark 등 주요 경쟁사 제품의 성능 평가와 함께 CR 추천(Recommended) 모델 선정
+- 공기청정기, 가습기, 스팀 몹 등 계절성 가전의 가격 변동 추이 및 구매 적기 정보 제공</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>- 로봇청소기 부문에서 iRobot Roomba Max 705가 역대 최저가 수준의 할인을 기록하며 성능 및 장애물 회피 능력에서 최고점 획득
+- Dyson V15 Detect는 레이저 먼지 감지 기술을 통해 프리미엄 무선 청소기 시장 내 기술적 차별성 강조
+- Shark와 Tineco는 습식 청소 및 다기능성(10-in-1 등)을 앞세워 실용성을 중시하는 소비자 층에서 높은 평가를 받음
+- Blueair 공기청정기는 CR 멤버십 전용 추가 할인을 통해 가격 경쟁력을 확보하고 신뢰도 부문에서 우수한 성적 유지</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>- 삼성전자의 제트(Jet) 및 비스포크 제트 봇(Bespoke Jet Bot) 라인업이 이번 추천 목록에서 제외되었으므로, 경쟁사(iRobot, Dyson)의 할인 공세에 대응하는 프로모션 강화 필요
+- Shark와 Tineco가 주도하는 습식/건식 겸용 청소기 시장의 성장세에 대응하여 자사 제품의 다기능성 및 편의성 소구점 재정비 요망
+- 공기청정기 카테고리에서 Blueair와 같은 경쟁사의 멤버십 연계 할인 전략을 벤치마킹하여 충성 고객 대상 혜택 확대 검토 필요</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Air Purifier</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Coway, Blueair, AirDoctor, Winix</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>- 산불 연기로 인한 미세입자 및 오염 물질 제거에 효과적인 공기청정기 5종 선정 및 테스트 결과 발표
+- HEPA 필터와 대형 팬을 장착하여 350평방피트 이상의 대형 공간에서 성능이 우수한 제품 위주로 추천
+- 선정된 주요 모델은 Coway Airmega ProX, Blueair Blue Pure 311i+ Max, Blueair Blue Pure 211+, AirDoctor 4000 Black, Winix 9800임</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>- Coway Airmega ProX가 종합 점수 85점으로 1위를 차지하며 대형 공간 정화 능력, 저소음, 브랜드 신뢰도 면에서 최고 등급을 받음
+- Blueair는 휴대성과 가성비(311i+ Max) 및 강력한 정화 성능(211+)으로 복수의 제품이 추천됨
+- Winix 9800은 낮은 연간 유지비용과 우수한 입자 제거 성능으로 가성비 부문에서 긍정적인 평가를 받음
+- 삼성전자 제품은 이번 산불 연기 특화 추천 리스트에 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>- 북미 지역의 산불 시즌 정례화에 따른 공기질 관리 수요 증가에 맞춰, 미세입자 및 연기 제거 성능을 강조한 마케팅 전략 필요
+- 경쟁사(Coway, Winix 등)가 강점을 보인 대형 공간용 고성능 라인업 및 유지비용 경쟁력에 대응하는 당사 제품의 특장점(스마트 기능, 필터 수명 등) 부각 검토
+- Consumer Reports의 성능 테스트 항목(고속/저속 입자 제거, 소음, 연간 유지비)에 최적화된 제품 성능 개선 및 홍보 데이터 확보 필요</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Best Deals on Smart Home Devices</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Smart Home</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Samsung, TP-Link (Tapo, Kasa), Google (Nest), SimpliSafe, Apple, Amazon</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>- 주요 스마트 홈 기기(보안 카메라, 스마트 플러그, 온도 조절기 등)의 최신 할인 정보 및 성능 평가 결과 요약
+- TP-Link Tapo/Kasa, Google Nest 등 주요 브랜드 제품의 기능적 장점과 가격 경쟁력 분석
+- 삼성 SmartThings를 포함한 주요 스마트 홈 플랫폼과의 호환성 정보 제공</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>- TP-Link와 Google Nest 제품군이 비디오 품질, 데이터 보안, 응답 속도 면에서 우수한 평가를 받으며 시장 내 주요 추천 모델로 선정됨
+- 구독료 없이 AI 감지(사람, 반려동물, 차량 등) 및 로컬 저장 기능을 제공하는 제품들이 소비자 가성비 측면에서 높은 점수를 받음
+- 삼성 SmartThings는 타사 스마트 플러그 및 보안 카메라와의 연동성을 통해 개방형 생태계의 핵심 플랫폼으로 언급됨</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>- SmartThings 생태계 내에서 TP-Link 및 Google Nest 기기들의 연동 비중이 높으므로, 해당 제품들과의 연결 안정성 및 사용자 경험(UX) 최적화 지속 필요
+- 경쟁사 및 서드파티 기기들이 '구독료 없는 AI 기능'을 차별화 포인트로 내세우고 있는 바, 당사 스마트 홈 서비스의 유료화 및 무료 기능 범위 설정 시 벤치마킹 필요</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>- Consumer Reports(CR)가 아이폰 17 시리즈(17, 17e, Air, 17 Pro, 17 Pro Max) 및 이전 모델에 대한 평가 및 구매 가이드 발표
+- 아이폰 17 Pro(85점)가 가장 높은 점수를 기록했으며, 17 Pro Max와 함께 카메라 및 내구성 부문에서 최상위 평가를 받음
+- 신규 라인업인 '아이폰 Air'는 5.6mm의 초슬림 디자인을 특징으로 하며, Plus 모델을 대체하는 포지션으로 출시
+- 보급형 모델인 17e는 A19 칩셋을 탑재하고 기본 저장 용량을 256GB로 상향하여 $599에 판매</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>- 애플은 전 라인업에 A19/A19 Pro 칩을 탑재하여 'Apple Intelligence(AI)' 기능을 표준화함
+- '아이폰 Air' 모델을 통해 배터리 성능의 소폭 희생(29.5시간)에도 불구하고 초슬림/경량화라는 새로운 폼팩터 전략을 제시함
+- Pro 라인업은 트리플 48MP 카메라 시스템을 통해 하위 모델과 성능 차별화를 명확히 함
+- 전 모델이 CR의 내구성 테스트(낙하 및 방수)에서 높은 점수를 획득하며 하드웨어 신뢰성을 확보함</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>- 경쟁사의 초슬림 모델(Air)에 대한 시장 반응을 모니터링하고 갤럭시 시리즈의 슬림화 및 경량화 대응 전략 검토 필요
+- 보급형 라인업의 기본 저장 용량 확대(256GB) 추세에 따른 당사 보급형 모델의 사양 경쟁력 재점검
+- 전 모델 AI 기능 지원에 대응하여 갤럭시 AI만의 실질적 사용성 우위 및 차별화 포인트 강조 필요</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Laptops &amp; Desktops</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Apple, Intel</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>- 애플이 초저가형 노트북 'MacBook Neo'($599)를 포함한 신규 PC 라인업을 발표함
+- MacBook Air는 M5 칩 탑재, WiFi 7 지원 등 성능이 강화되었으나 시작 가격이 $1,099로 $100 인상됨
+- MacBook Pro는 M5 Pro 및 M5 Max 칩을 탑재하고 전송 속도가 빠른 Thunderbolt 5를 지원하며 가격은 모델별로 최대 $400 인상됨
+- 데스크탑 부문에서는 M4 칩을 탑재한 Mac Mini($599)와 iMac($1,299)이 주요 선택지로 제시됨</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>- 애플이 아이폰용 A18 Pro 칩을 탑재한 $599 저가형 노트북을 출시하여 학생 및 크롬북/윈도우 사용자층 흡수를 시도함
+- 전반적인 하드웨어 가격 인상에도 불구하고 기본 메모리(16GB) 및 저장용량 상향을 통해 제품 경쟁력을 유지하려는 전략임
+- Consumer Reports는 기존 MacBook Air와 Pro 모델에 대해 'Recommended(추천)' 등급을 부여하며 브랜드 신뢰도와 만족도에서 높은 점수를 유지 중임</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>- 애플의 $500대 시장 진입은 갤럭시 북 등 당사 보급형 라인업에 위협이 될 수 있으므로, 교육용 시장 및 입문자용 제품의 가격/성능 대응 전략 수립 필요
+- 경쟁사의 WiFi 7 도입 및 무선 연결성 강화 추세에 맞춰 차세대 갤럭시 북의 통신 스펙 우위 확보 검토 필요
+- 경쟁사의 가격 인상 기조를 기회로 삼아 당사 제품의 가격 대비 성능(가성비) 및 갤럭시 생태계 연동성을 강조한 마케팅 강화 필요</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Service/Warranty</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Samsung, Apple</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>- 신규 출시 예정인 삼성 갤럭시 S26 시리즈 대상 삼성 케어 플러스(Samsung Care+) 가입 가이드 및 비용 분석
+- 일반 Care+와 도난/분실 보장 포함 플랜 두 가지 옵션 제공
+- 기기 가액에 따른 4단계 가격 티어 적용 (S26은 티어 2, S26 Ultra는 티어 4 예상)
+- 액정 수리비 $29, 기타 사고 수리/교체 $99 등 고정 비용 및 24/7 기술 지원 포함</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>- 고가 플래그십 및 폴더블 모델의 경우 파손 시 교체 비용 대비 서비스 가입의 경제적 실익이 큼
+- 소비자 리포트 조사 결과 연장 보증 가입자의 20%만이 실제 서비스를 이용하며, 기기 내구성 향상으로 인해 가입 필요성에 대한 논란 존재
+- 신용카드 제공 보험이나 주택 보험 등 대체 보상 수단과의 비교가 가입 결정의 주요 변수임</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>- S26 시리즈 마케팅 시 자사 수리 서비스의 접근성(700개 이상 uBreakiFix 매장) 및 정품 부품 사용의 신뢰성 강조 필요
+- 경쟁사(Apple Care+) 대비 수리 비용의 우위 및 24/7 전담 기술 지원(Servify)의 편의성을 핵심 소구점으로 활용
+- 실사용률이 낮은 점을 고려하여 초기 가입 프로모션이나 번들 혜택을 통한 서비스 침투율 확대 전략 검토</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Microwave</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Commercial Chef, Emerson, Hamilton Beach, Nostalgia Electrics, Proctor Silex, Vissani, Danby, Farberware, Insignia, Panasonic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>- 소형 전자레인지(0.8 cubic feet 이하) 5종 및 일부 중형 모델에 대한 Consumer Reports의 성능 테스트 결과 발표
+- 소형 모델은 낮은 와트수(700W)로 인해 가열 속도가 전반적으로 느리며 가용 용량이 제조사 표기보다 적은 경향이 있음
+- 가열 균일성, 해동 성능, 소음 수준을 기준으로 Commercial Chef, Danby, Farberware, Insignia, Panasonic 제품을 추천 모델로 선정</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>- 소형 전자레인지 카테고리에서 가열 속도는 공통적인 성능 한계로 지적되나, 해동 균일성과 저소음 부문에서는 제품별 차별화가 나타남
+- 브랜드 신뢰도 조사에서 Commercial Chef, Emerson, Hamilton Beach 등이 우수 등급을 획득했으나, 실제 성능 테스트에서 고득점을 받은 소형 모델은 소수에 불과함
+- Panasonic 모델(NN-SD47QS)은 가열 속도 부족에도 불구하고 가열 균일성, 해동, 저소음, 브랜드 신뢰도에서 고루 높은 평가를 받음</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>- 본 기사에서 삼성 및 LG 제품은 소형 전자레인지 추천 목록에 포함되지 않았으며, 주로 저가형 브랜드와 Panasonic이 시장을 점유 중임
+- 1인 가구 및 좁은 공간을 타겟으로 하는 소형 가전 시장에서 경쟁사가 강조하는 '가열 균일성'과 '저소음' 성능에 대한 벤치마킹 및 대응 전략 검토 필요</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Desktop Computers</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>HP, Apple, Dell, Asus, Intel, AMD</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>- Consumer Reports가 선정한 2026년 최우수 데스크탑 컴퓨터 9종 및 테스트 결과 발표
+- 올인원(All-in-one), 미니 PC, 타워형 카테고리로 분류하여 성능, 브랜드 신뢰도, 소유자 만족도 평가
+- 주요 추천 모델로 HP EliteStudio, Apple iMac(M4), Dell 24" All-in-One, Apple Mac Studio, Asus NUC 14 Pro 등이 선정</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>- Apple이 브랜드 신뢰도 및 소유자 만족도에서 최고 등급을 기록하며 Mac Studio 모델이 전체 평가 대상 중 최고점(81점) 획득
+- Intel Core Ultra 및 AMD Ryzen AI 프로세서를 탑재한 AI 특화 미니 PC 제품군(Asus 등)이 생산성 부문에서 높은 평가를 받으며 부상
+- 삼성전자 및 LG전자의 데스크탑 제품은 이번 최우수 추천 목록(Top Picks)에 포함되지 않음</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>- 북미 컴퓨팅 시장 내 Apple의 높은 브랜드 신뢰도와 만족도 지표에 대한 원인 분석 및 벤치마킹 필요
+- 경쟁사들의 AI 가속 프로세서 채용 및 미니 PC 폼팩터 다변화 전략에 대응하는 당사 PC 제품군(노트북/모니터 연계 등)의 차별화 포인트 발굴 필요
+- 소비자 리포트 내 당사 브랜드 인지도 및 신뢰도 제고를 위한 품질 관리 및 서비스 전략 점검</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Robot Vacuums</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Samsung, Dyson, Eufy, Eureka, iRobot, Dreame, Shark, Miele</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>- 컨슈머리포트(CR)가 반려동물 털 제거 성능이 우수한 2026년 최고의 로봇청소기 6종을 선정함
+- 선정된 모델은 Samsung Jet Bot VR7MD96514G, Dyson 360 Vis Nav, Eufy C10 T2292, Eureka NERE10SW, iRobot Roomba Max 705, Dreame L40 Ultra임
+- 삼성 Jet Bot은 고가의 모델임에도 불구하고 강력한 흡입력과 뛰어난 물걸레 성능으로 추천 목록에 포함됨</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>- 삼성 Jet Bot VR7MD96514G는 테스트된 모든 로봇청소기 겸용 모델 중 물걸레 성능이 가장 우수한 것으로 평가됨
+- 삼성의 도킹 스테이션은 먼지통 비움, 걸레 세척 및 건조, 물 보충 등 자동화된 편의 기능에서 강점을 보임
+- 경쟁사 다이슨은 신뢰도는 높으나 만족도가 낮고, iRobot은 파산 신청 상태임에도 성능 면에서 추천됨
+- Dreame L40 Ultra는 반려동물 구역 설정 및 비디오 모니터링 등 특화 기능을 제공함</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>- 타사 대비 압도적인 물걸레 성능과 올인원 스테이션의 자동화 편의성을 프리미엄 시장의 핵심 차별화 포인트로 지속 강조해야 함
+- 고가 제품군인 만큼 성능 우위와 더불어 브랜드 신뢰도 및 사용자 만족도 지표를 경쟁사(다이슨 등) 이상으로 유지하기 위한 관리가 필요함</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -492,7 +1544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +1564,2131 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4 Best Single-Serve Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-pod-coffee-makers-a3468890273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>What to Expect for Amazon Prime Day 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Deals on Headphones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Talking Carts 11: Couponing 101</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best New SUVs and Cars for Under $30,000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>How to Save Money at the Gas Pump</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Best Deals on Health and Beauty Products</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Battery Platforms for Power Tools</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Deals on Tech Products Right Now</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Best Mattress Sales Right Now</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Our Favorite Deals Right Now</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best Deals on Pet Products</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Best Hot Combs, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>42 Used Cars to Avoid Buying</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>How to Clean Your Lawn Mower Deck</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-clean-your-lawn-mower-deck-a4858405895/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Best Wood Stains of 2026 (and a Few of the Worst)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/best-wood-stains-from-consumer-reports-tests-a4478428531/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>How to Get Your Lawn Mower or Tractor Ready for Mowing Season</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-get-your-lawn-mower-ready-for-spring-a8196766008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Best Time to Fertilize Your Lawn</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-care/dont-bother-fertilizing-your-lawn-twice-a-year-a5780099997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10 Best Deals on Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>How to Stain a Deck</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Best Hybrid Cars for Under $35,000</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Best Deals Under $50</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Best Deals Under $100</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Deals on Healthy-Home Essentials</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Best and Worst Laundry Detergents of 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Most and Least Reliable Coffee Makers</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Worst Deals on New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Best Deals on Smart Home Devices</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Most Discounted New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>How Do Hybrid Cars Work?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Best New-Car Deals</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Best Deals on Kitchen Products</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Best Deals on Home Products</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Best Cars Made in the USA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7 Best E-Bike Covers of 2026, According to Experts</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/electric-bikes/best-e-bike-covers-a5685855846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Are Hybrids a Smart Choice Right Now?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/why-hybrid-vehicles-are-a-smart-choice-right-now-a2736240282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Deals Under $25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-25-a4183478310/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gas vs. Battery Lawn Mower: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/gas-vs-electric-lawn-mower-which-is-better-a1057954260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>How to Check Engine Oil the Right Way</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6 Best Compression Socks, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/underwear-socks/best-compression-socks-a2750797916/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>We Tested 49 More Baby Formulas for Lead and Arsenic</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-formula/liquid-baby-formula-contaminants-test-results-a8639602154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Safest Small SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-small-suvs-a9206654113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ford and Lincoln SUVs Recalled to Fix Windshield Wipers</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/ford-lincoln-suvs-recalled-to-fix-windshield-wiper-motor-a5559013983/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.7 Million More Ford and Lincoln SUVs Recalled to Fix Screens</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/more-ford-and-lincoln-suvs-recalled-to-fix-backup-cameras-a4514261791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Used Cars and SUVs Under $10,000 That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-used-cars-suvs-under-10000-dollars-a8966344858/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Thousands of Halo Magic Sleepsuits Recalled for Choking Risk</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/halo-magic-sleepsuits-recalled-for-choking-risk-a6877096785/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Baby Product Recalls Parents Should Know About in 2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/baby-product-recalls-parents-caregivers-should-be-aware-of-a5859124070/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Most Reliable 3-Year-Old Cars and SUVs That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/most-reliable-3-year-old-cars-and-suvs-a7361029795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient SUVs</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/the-most-fuel-efficient-suvs-best-mpg-a5599990140/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Talking Carts 10: The Pink Tax</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-10-the-pink-tax-a4218079662/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>More Than 80,000 Babysense Baby Monitors Recalled for Fire Hazard Risk</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/babysense-max-view-baby-monitors-recalled-for-fire-risk-a3285333268/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Target_Articles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_Articles_History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,895 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>중요도</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Frigidaire, Electrolux</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Electrolux가 화상 위험으로 인해 미국 내 Frigidaire 브랜드 가스 레인지 약 174,800대를 리콜함. 오븐 베이크 버너의 점화 지연 문제로 30건의 부상 사례를 포함한 62건의 사고가 보고되었으며, CR은 평가 대상이었던 Frigidaire 가스 레인지 9개 모델 전체에 대해 추천(Recommended) 지위를 취소함.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>주요 경쟁사인 Frigidaire의 가스 레인지 라인업 대다수가 안전 결함으로 인해 CR 추천 목록에서 제외됨에 따라 해당 카테고리의 경쟁 구도 변화가 예상됨.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>- Electrolux가 화상 위험을 이유로 Frigidaire 가스 레인지 약 174,800대(미국) 및 5,300대(캐나다)를 리콜함.
+- 리콜 대상은 2025년 6월부터 2026년 1월까지 판매된 Frigidaire, Gallery, Professional 브랜드의 23개 가스 레인지 모델임.
+- Consumer Reports는 리콜 대상에 포함된 Frigidaire 가스 레인지 9개 모델 전체에 대해 '추천(Recommended)' 등급 부여를 중단함.
+- 오븐 베이크 버너의 점화 지연으로 인해 발생한 62건의 오작동 및 30건의 화상 부상 사례가 접수됨.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Air Conditioners (Heat Pumps)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Frigidaire, Goodman, Trane, Lennox</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Consumer Reports가 2026년 최고의 전체 주택용 히트펌프(Whole-House Heat Pumps) 4종을 선정하여 발표함. Frigidaire, Goodman, Trane, Lennox 제품이 추천 제품(CR Recommended)으로 선정되었으며, 가열 및 냉각 효율, 소음, 브랜드 신뢰도 등을 기준으로 평가됨.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>미국 내 히트펌프 판매량이 가스 가열로(Furnace)를 추월하며 시장이 확대되는 가운데, Frigidaire가 총점 87점으로 1위를 차지함. 이번 덕트형 히트펌프 추천 목록에 삼성전자와 LG전자의 제품은 포함되지 않음.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>- Frigidaire 3T 모델이 총점 87점을 획득하며 가열 및 냉각 효율 부문 최고점으로 전체 1위에 선정됨.
+- Goodman 3T R32 모델은 소음 테스트에서 추천 제품 중 가장 우수한 성적을 기록하며 총점 83점으로 공동 2위를 차지함.
+- Trane 3T 모델은 브랜드 신뢰도 'Very Good' 및 소유자 만족도 'Excellent' 등급을 받으며 총점 83점을 기록함.
+- Lennox 3T 모델은 가열 효율과 소음에서 우수한 평가를 받았으나, 조사 대상 중 최고가인 5,000달러를 기록하며 총점 76점으로 4위에 위치함.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Roku, Sony, Hisense, TCL</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 발표한 '2026년 최고의 TV 브랜드' 평가에서 삼성전자가 1위를 차지했습니다. 삼성의 2025년형 QD-OLED TV(QN65S90F)는 총점 91점을 기록하며 주요 추천 제품 중 가장 높은 점수를 받았으며, LG전자가 브랜드 순위 2위로 그 뒤를 이었습니다.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>삼성전자가 화질, 음향, 신뢰도, 소비자 만족도 및 가격을 종합한 브랜드 평가에서 1위를 달성하며 경쟁력을 입증했습니다. 특히 2025년형 QD-OLED 신제품이 LG전자의 OLED 모델(88점)보다 높은 91점을 획득하며 기술적 우위를 확보한 것으로 나타났습니다.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>- 삼성전자가 컨슈머리포트 선정 '2026년 최고의 TV 브랜드' 부문에서 1위 기록.
+- 삼성 QN65S90F(QD-OLED) 모델이 총점 91점을 획득하며 '추천 제품(Recommended)' 및 '그린 초이스(Green Choice)'로 선정됨.
+- LG전자는 브랜드 평가 2위를 차지했으며, 주요 모델인 OLED65C5PUA는 총점 88점으로 추천 제품에 포함됨.
+- 소니(Sony)의 K65XR80M2 모델은 총점 81점, 로쿠(Roku)의 75R8C5 모델은 총점 72점을 기록함.
+- 삼성 TV는 HDR10+와 돌비 애트모스를 지원하나 돌비 비전(Dolby Vision)은 미지원하는 것으로 명시됨.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Washer</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LG, Electrolux, Maytag, Insignia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Consumer Reports(CR)가 800달러 이하의 가성비 세탁기 추천 제품을 발표함. LG전자가 드럼 세탁기 및 통돌이(교반식) 세탁기 부문에서 높은 점수를 획득하며 주요 추천 모델로 선정되었으나, 삼성전자 모델은 해당 리스트에 포함되지 않음.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>800달러 이하 보급형 세탁기 시장에서 LG전자가 세탁 성능, 에너지 효율, 수자원 효율성 등 주요 평가 항목에서 경쟁사(Electrolux, Maytag 등) 대비 우위를 점하며 추천 제품(CR Recommended) 목록을 주도함.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>- LG 드럼 세탁기(WM3400CW)가 총점 87점을 기록하며 해당 가격대 드럼 부문 1위 및 CR 추천 제품으로 선정됨.
+- LG 통돌이(교반식) 세탁기 WT7005CW(80점)와 WT7155CW(79점)가 해당 부문 상위권 및 추천 제품에 포함됨.
+- LG WT8205CW 모델은 4.8큐빅피트 용량과 우수한 세탁 성능으로 추가 언급됨.
+- 800달러 이하 추천 제품 리스트 내 삼성전자 세탁기 모델은 선정되지 않음.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Black+Decker, Shark, Miele, Eufy, iRobot, GorFanty, Tineco, Kenmore, Bissell, Hoover, Dirt Devil</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Consumer Reports가 스틱, 로봇, 업라이트, 캐니스터 청소기 및 카페트 클리너 등 다양한 바닥 관리 제품군의 최신 할인 정보와 주요 성능 테스트 결과를 발표함.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Shark, Miele, Kenmore 등 주요 가전 브랜드 제품들이 성능 및 신뢰도 평가를 바탕으로 추천 할인 모델에 선정되었으나, 이번 리스트에 삼성전자와 LG전자 제품은 포함되지 않음.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>- Shark 브랜드의 다수 모델(Vertex Pro, Stratos, Navigator 등)이 바닥 청소 성능 및 사용자 만족도 점수를 바탕으로 주요 할인 품목에 선정됨.
+- iRobot Roomba Max 705가 테스트된 로봇 청소기 중 최고 성능 모델로 평가받으며 전년 대비 최저가 수준으로 하락함.
+- Miele 브랜드는 스틱 및 캐니스터 부문에서 브랜드 예측 신뢰도와 사용자 만족도 부문 최고 등급을 획득함.
+- Kenmore Elite Pet Friendly 31150 모델이 업라이트 부문에서 가장 강력한 흡입력을 기록한 것으로 보고됨.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vacuum Cleaners</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Samsung, LG, Bosch, Miele</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 발표한 '2026년 최고의 스틱 청소기' 평가 결과, 삼성전자의 Bespoke AI Jet Ultra가 총점 83점으로 1위를 차지했습니다. LG전자의 CordZero All-in-One 모델이 80점으로 2위를 기록했으며, 삼성전자의 Jet 85 모델이 79점으로 그 뒤를 이었습니다.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>삼성전자는 제품의 청소 성능뿐만 아니라 브랜드 신뢰도와 사용자 만족도 조사에서 경쟁사 대비 높은 평가를 받으며 무선 청소기 시장에서의 우위를 확인했습니다. 특히 배터리 효율성과 자동 먼지 비움 기능이 주요 강점으로 분석되었습니다.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>- 삼성 Bespoke AI Jet Ultra(VS90F40DMK/AA)가 총점 83점을 획득하며 무선 스틱 청소기 부문 1위에 선정됨.
+- 해당 모델은 나대지 바닥 청소 및 반려동물 털 제거 성능에서 최고 등급을 기록했으며, 테스트 제품 중 가장 긴 평균 실행 시간을 보유함.
+- 삼성 브랜드는 멤버 설문조사 결과 신뢰도(Reliability) 및 소유주 만족도(Owner Satisfaction)에서 '매우 우수(Very Good)' 등급을 획득함.
+- LG CordZero All-in-One(A949KTMS)은 총점 80점으로 2위를 기록했으며, 카펫 청소 성능과 물걸레 노즐 등 부가 기능에서 우수한 평가를 받음.
+- 삼성 Jet 85(VS20C8522TW)는 총점 79점으로 3위를 차지했으며, 나대지 바닥 청소와 반려동물 털 제거 성능에서 우수함을 인정받음.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Washing Machine</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>LG, Samsung, Speed Queen, Electrolux, Miele, Amana, Frigidaire, GE, Maytag, Whirlpool, Asko, Blomberg, Midea</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Consumer Reports가 2026년 최고의 세탁기 16종을 선정하여 발표했습니다. LG전자가 드럼(Front-load), 통돌이(Top-load Agitator), 고효율 통돌이(HE Top-load) 등 주요 전 카테고리에서 상위권을 독점하며 강력한 추천 제품(Top Picks)으로 선정되었습니다. 또한 LG는 브랜드 신뢰도 조사에서도 드럼 및 고효율 통돌이 부문에서 가장 신뢰할 수 있는 브랜드로 꼽혔습니다.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>경쟁사인 LG전자가 세탁기 전 부문에서 압도적인 성능 점수와 브랜드 신뢰도 등급을 획득하며 시장 내 추천 지위를 선점했습니다. 삼성전자는 테스트 대상 브랜드로는 언급되었으나, 이번 2026년 베스트 모델 목록 및 주요 부문별 상위권에는 포함되지 않았습니다.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>- LG전자가 드럼 세탁기 부문에서 WM4000HWA, WM9900HSA, WM3400CW 모델로 최고점 87점을 기록하며 상위권을 점유함.
+- LG WT8405CW 모델이 통돌이(Agitator) 부문에서 총점 82점으로 해당 카테고리 1위에 선정됨.
+- 고효율 통돌이(HE Top-load) 부문에서 LG WT8600CB(86점)와 WT8400CW(84점)가 추천 제품으로 등재됨.
+- CR 멤버 설문 조사 결과, LG전자가 드럼 및 고효율 통돌이 세탁기 부문에서 가장 신뢰할 수 있는 브랜드(Most Reliable Brand)로 발표됨.
+- 삼성전자는 브랜드 신뢰도 및 추천 제품 목록 내 구체적인 순위권에 진입하지 못함.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nokia, Apple, Cat, Light Phone, Bigme</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>컨슈머리포트 기자가 아이폰 13에서 노키아 2780 플립폰으로 기기를 변경하여 일주일간 사용한 경험을 바탕으로 '디지털 미니멀리즘' 트렌드와 덤폰(Dumb Phone)의 사용성을 분석함. 스크린 타임 감소와 집중력 향상이라는 긍정적 효과가 있었으나, 앱 생태계 부재, 불편한 내비게이션, 낮은 카메라 품질 등의 실질적인 한계가 확인됨.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>스마트폰 과의존에서 벗어나려는 '디지털 미니멀리즘' 수요가 존재하며, 이는 기능이 제한된 플립폰(덤폰) 시장의 유지와 별도 전용 기기(GPS, MP3 등)를 휴대하는 사용자 문화로 이어지고 있음.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>- 노키아 2780 플립폰 사용을 통해 일일 스크린 타임이 기존 대비 약 3시간 감소함.
+- 플립폰의 주요 기능적 제약으로 금융 앱(Venmo), 모빌리티(Uber), QR 코드 인식, 모바일 티켓팅 접근 불가 등이 보고됨.
+- 탑재된 500만 화소 카메라는 최신 스마트폰 대비 해상도와 화질이 현저히 낮은 것으로 평가됨.
+- 카이오에스(KaiOS)를 통한 구글 맵 이용은 가능하나, 터치스크린 부재 및 턴바이턴(Turn-by-turn) 안내 미지원으로 사용성이 제한됨.
+- 덤폰 사용 시 부족한 기능을 보완하기 위해 전용 GPS, 디지털 카메라, 음악 플레이어를 별도 휴대하는 사용자 사례가 확인됨.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Vacuum</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>LG, Shark, Kenmore, Eureka, iRobot, Black+Decker, Ryobi, Roborock, Bissell, Oreck, Atrix, Dirt Devil, Mainstays, Lefant</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 주요 청소기 카테고리별로 성능이 가장 낮은 모델과 이를 대체할 수 있는 우수 추천 제품을 발표함. LG전자의 CordZero Q3 모델이 무선 스틱 청소기 부문에서 가성비가 뛰어난 추천 제품으로 선정됨.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LG CordZero Q3 C5323GW 모델은 무선 스틱 청소기 부문에서 Ryobi 제품의 대안으로 추천되었으며, 특히 카펫 청소와 반려동물 털 제거 성능에서 우수한 평가를 받음. 삼성전자 제품은 이번 최악 및 추천 리스트에 언급되지 않음.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>- LG CordZero Q3 C5323GW 모델이 총점 76점을 기록하며 무선 스틱 청소기 부문 추천 제품(What to buy instead)에 선정됨.
+- 해당 모델은 카펫 먼지 추출, 반려동물 털 제거, 벽면 모서리 청소 항목에서 우수한 성능을 기록함.
+- 약 300달러의 가격으로 추천 제품군 중 가격 경쟁력이 높은 모델로 분류됨.
+- 삼성전자 청소기 제품은 이번 보도 내용의 최악 또는 추천 리스트에 포함되지 않음.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Vacuums, Air Purifiers, Humidifiers</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blueair, HoMedics, Dirt Devil, Hoover, Shark, iRobot, Dyson, Tineco, Levoit</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Consumer Reports(CR)가 봄맞이 청소 시즌을 맞아 공기청정기, 가습기, 로봇청소기, 무선청소기 등 주요 가전 제품의 성능 테스트 결과와 할인 정보를 발표함. iRobot, Dyson, Shark 등 주요 경쟁사 제품들이 추천 모델 및 할인 대상으로 포함됨.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>로봇청소기 및 무선청소기 카테고리에서 iRobot과 Dyson이 기술적 우위와 높은 성능 점수를 바탕으로 추천되었으며, 삼성전자와 LG전자 제품은 이번 할인 및 추천 목록에 언급되지 않음.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>- iRobot Roomba Max 705가 CR 테스트 결과 역대 최고 성능 로봇청소기로 평가받으며 100달러 할인된 가격에 판매 중임.
+- Dyson V15 Detect 무선청소기가 레이저 먼지 감지 기능 및 입자 분석 센서 성능을 바탕으로 추천 제품에 포함됨.
+- Blueair 공기청정기(Mini Restful, 311i+ Max 등)가 CR 회원 대상 최대 40% 할인 혜택과 함께 높은 브랜드 신뢰도를 기록함.
+- Tineco Floor One S5 스팀맙이 세라믹 타일 얼룩 제거 및 스팀 생성 부문에서 우수(Exemplary) 등급을 획득함.
+- Shark HydroVac Pro XL 무선맙이 세척 성능 테스트에서 높은 점수를 기록하였으나, 사용 후 세척 편의성 면에서는 낮은 평가를 받음.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Air Purifier</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Coway, Blueair, AirDoctor, Winix</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 산불 연기 입자 제거에 특화된 고성능 공기청정기 5종을 선정하여 발표함. HEPA 필터를 탑재하고 350평방피트 이상의 대형 공간에서 미세 입자 제거 성능이 우수한 제품들이 상위권에 오름.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>코웨이(Coway)가 소음 및 정화 성능에서 최고점을 받으며 1위를 차지함. 블루에어, 에어닥터, 위닉스 등 주요 공기청정기 브랜드들이 추천 명단에 포함되었으나, 삼성전자와 LG전자 제품은 이번 추천 목록에서 제외됨.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>- 코웨이 Airmega ProX가 총점 85점을 기록하며 전체 1위 및 추천 제품(CR Recommended)으로 선정됨.
+- 블루에어 Blue Pure 311i+ Max와 211+가 각각 총점 80점으로 공동 2위를 차지함.
+- 에어닥터 4000 Black은 총점 77점, 위닉스 9800은 총점 74점으로 추천 명단에 포함됨.
+- 평가 항목은 고속 및 저속 운전 시의 먼지·꽃가루·연기 제거 성능, 소음 수준, 연간 유지 비용(필터 및 에너지) 등을 포함함.
+- 삼성전자 및 LG전자 공기청정기 제품은 이번 산불 연기 특화 추천 5종에 포함되지 않음.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>컨슈머리포트(CR)가 애플의 최신 아이폰 17 라인업(17, 17 Pro, 17 Pro Max, 17 Air, 17e)과 기존 모델인 16 시리즈에 대한 성능 평가 및 구매 가이드를 발표함. 각 모델의 배터리 수명, 카메라 성능, 내구성 및 가격을 비교 분석하여 추천 제품을 선정함.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>아이폰 17 시리즈 전 모델이 CR 추천(Recommended) 등급을 획득했으며, 특히 아이폰 17 Pro가 총점 85점으로 라인업 중 가장 높은 점수를 기록함. 새롭게 도입된 초슬림 모델인 아이폰 17 Air는 디자인 면에서 우수하나 배터리 성능은 시리즈 중 가장 낮은 것으로 나타남.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>- 아이폰 17 Pro가 총점 85점을 기록하며 평가 대상 중 최고점을 획득함.
+- 아이폰 17 Pro Max는 1회 충전 시 43시간의 배터리 수명을 기록하여 라인업 내 최장 시간을 달성함.
+- 신규 폼팩터인 아이폰 17 Air는 5.6mm 두께를 구현했으나, 배터리 지속 시간은 29.5시간으로 아이폰 17 시리즈 중 가장 짧음.
+- 아이폰 17 시리즈 전 모델이 CR의 낙하 테스트(100회) 및 방수 테스트를 통과하여 내구성 부문 최고 등급을 획득함.
+- 보급형 모델인 아이폰 16e는 총점 81점을 기록했으며, 후속 모델인 17e는 현재 테스트 진행 중임.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Laptop/Desktop</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>애플이 599달러부터 시작하는 저가형 노트북 '맥북 네오(MacBook Neo)'를 포함하여 M5 칩을 탑재한 맥북 에어 및 맥북 프로 신제품 라인업을 공개함. 맥북 네오는 아이폰용 A18 Pro 칩을 탑재한 보급형 모델이며, 맥북 에어와 프로는 성능 향상과 함께 가격이 인상됨. Consumer Reports는 기존 맥북 에어와 프로 모델에 대해 각각 76점과 81점을 부여하며 '추천 제품'으로 선정함.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>애플이 저가형 시장 공략을 위해 500달러대 라인업을 신설하고, 고성능 라인업에는 M5 칩과 WiFi 7 등 최신 기술을 적용하여 제품군을 재편함. CR은 애플 브랜드의 신뢰도와 소유주 만족도를 높게 평가하며 주요 모델을 추천 제품 리스트에 유지함.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>- 애플이 599달러의 저가형 노트북 '맥북 네오(MacBook Neo)'를 출시하며 보급형 컴퓨팅 시장 라인업을 확장함.
+- 맥북 에어 M5 모델의 시작 가격이 1,099달러로 이전 세대 대비 100달러 인상됨.
+- 맥북 프로 M5 Pro 및 M5 Max 모델에 WiFi 7 및 썬더볼트 5 규격이 도입됨.
+- Consumer Reports 평가 결과, 맥북 프로(MX2X3LL/A)가 총점 81점으로 '추천 제품(CR Recommended)' 등급을 획득함.
+- 맥북 에어 2025 모델이 총점 76점으로 '추천 제품(CR Recommended)' 등급을 유지함.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Microwave</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Commercial Chef, Emerson, Hamilton Beach, Nostalgia Electrics, Proctor Silex, Vissani, Danby, Farberware, Insignia, Panasonic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Consumer Reports가 공간 제약이 있는 소비자를 위한 소형 전자레인지(0.8 cubic feet 이하) 및 일부 중형 모델의 성능 테스트 결과를 발표함. 소형 모델은 가열 속도가 전반적으로 느리지만, 소음 및 해동 균일성에서 우수한 특정 모델들이 추천됨.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>소형 전자레인지는 낮은 소비전력(700W)으로 인해 가열 속도 면에서 취약점을 보이나, Commercial Chef와 Panasonic 등은 신뢰도와 성능 균형에서 긍정적인 평가를 받음. 삼성과 LG 제품은 이번 소형/저가형 추천 목록에 포함되지 않음.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>- Consumer Reports가 소형 전자레인지 추천 모델로 Commercial Chef(CHM770B, CHM7MB), Danby(DDMW007501G1), Farberware(FMO07ABTBKA), Insignia(NS-MW7BK5)를 선정함.
+- 중형급(0.9~1.2 cu. ft.)에서는 Commercial Chef(CHM990B)와 Panasonic(NN-SD47QS)이 우수한 평가를 받음.
+- Commercial Chef, Emerson, Hamilton Beach, Nostalgia Electrics, Proctor Silex, Vissani 6개 브랜드가 브랜드 신뢰도(Predicted Reliability)에서 최고 등급(Excellent)을 기록함.
+- 삼성전자 및 LG전자 제품은 이번 소형 전자레인지 부문 테스트 결과 및 추천 목록에 언급되지 않음.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Computing</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Desktop Computers</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>HP, Apple, Dell, Asus, Intel, AMD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 성능, 신뢰도, 소유자 만족도를 기준으로 선정한 '2026년 최우수 데스크탑 컴퓨터' 평가 결과를 발표함. 올인원(All-in-One), 미니 PC, 타워형 부문에서 HP, Apple, Dell, Asus의 주요 모델들이 추천 제품(CR Recommended)으로 선정되었으며, 특히 AI 기능을 강화한 최신 프로세서 탑재 모델들이 주목받음.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>이번 데스크탑 부문 추천 목록에 삼성전자와 LG전자의 제품은 포함되지 않음. Apple은 브랜드 신뢰도와 소유자 만족도에서 최고 등급을 유지하며 미니 PC와 올인원 부문 상위권을 차지했고, HP와 Asus는 고성능 작업 및 AI 가속 성능을 앞세워 높은 총점을 획득함.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - 컨슈머리포트의 2026년 최우수 데스크탑 선정 결과, 삼성 및 LG 브랜드 제품은 순위권에 포함되지 않음.
+ - HP EliteStudio All-in-One이 총점 83점으로 올인원 부문 최고점을 기록함.
+ - Apple Mac Studio(81점)가 미니 데스크탑 부문 전체 1위를 차지했으며, 브랜드 신뢰도 및 소유자 만족도에서 최고 등급을 획득함.
+ - Asus NUC 14 Pro(82점)와 ExpertCenter PN54(77점)가 Intel 및 AMD의 AI 프로세서를 탑재한 미니 PC 부문 추천 제품으로 선정됨.
+ - Dell 24" All-in-One(66점)은 사무용 성능과 디스플레이 품질을 인정받아 추천 제품에 포함됨.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Home Appliances</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Vacuum</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Samsung, Dyson, Eufy, iRobot, Dreame, Eureka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>컨슈머리포트가 반려동물을 키우는 가정에 적합한 2026년 최고의 로봇청소기 6종을 선정하여 발표함. 삼성전자의 제트 봇(Jet Bot VR7MD96514G)은 흡입력과 물걸레 성능 모두에서 우수한 평가를 받으며 추천 제품에 포함됨.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>삼성전자의 로봇청소기 겸용 모델이 반려동물 털 제거 성능뿐만 아니라, 테스트된 모든 제품 중 물걸레 청소 성능에서 가장 높은 평가를 받으며 제품 경쟁력을 입증함.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>- 삼성 Jet Bot VR7MD96514G 모델이 반려동물 털 제거 성능 우수 제품(Top Pick)으로 선정됨.
+- 해당 모델은 컨슈머리포트가 테스트한 로봇청소기 겸용 모델 중 물걸레 성능 부문에서 최고점을 기록함.
+- 먼지통 자동 비움, 물걸레 세척·건조, 물탱크 자동 리필 기능을 포함한 도킹 스테이션의 편의성이 주요 특징으로 기술됨.
+- 경쟁사 제품으로는 Dreame L40 Ultra, Dyson 360 Vis Nav, iRobot Roomba Max 705 등이 함께 추천 목록에 포함됨.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -492,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +1401,2131 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4 Best Single-Serve Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-pod-coffee-makers-a3468890273/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best TV Brands of 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>What to Expect for Amazon Prime Day 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Best Deals on Headphones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Talking Carts 11: Couponing 101</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Best New SUVs and Cars for Under $30,000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>How to Save Money at the Gas Pump</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Best Deals on Vacuums</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Best Washers for $800 or Less</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Best Deals on Health and Beauty Products</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Best Battery Platforms for Power Tools</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Best Deals on Tech Products Right Now</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Best Mattress Sales Right Now</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Our Favorite Deals Right Now</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Best Deals on Pet Products</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Best Hot Combs, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>42 Used Cars to Avoid Buying</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>How an Old-School Flip Phone Changed My Life</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>How to Clean Your Lawn Mower Deck</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-clean-your-lawn-mower-deck-a4858405895/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Best Wood Stains of 2026 (and a Few of the Worst)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/best-wood-stains-from-consumer-reports-tests-a4478428531/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>How to Get Your Lawn Mower or Tractor Ready for Mowing Season</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-get-your-lawn-mower-ready-for-spring-a8196766008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Best Time to Fertilize Your Lawn</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-care/dont-bother-fertilizing-your-lawn-twice-a-year-a5780099997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>10 Best Deals on Electric Vehicles</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>How to Stain a Deck</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Best Hybrid Cars for Under $35,000</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Best Deals Under $50</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Best Deals Under $100</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Best Deals on Healthy-Home Essentials</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Best and Worst Laundry Detergents of 2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Most and Least Reliable Coffee Makers</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Worst Deals on New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Best Deals on Smart Home Devices</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Most Discounted New Cars Right Now</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>How Do Hybrid Cars Work?</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Best New-Car Deals</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Which iPhone Should You Buy?</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Best Deals on Kitchen Products</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Best Deals on Home Products</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Best Cars Made in the USA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7 Best E-Bike Covers of 2026, According to Experts</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/electric-bikes/best-e-bike-covers-a5685855846/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Are Hybrids a Smart Choice Right Now?</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/why-hybrid-vehicles-are-a-smart-choice-right-now-a2736240282/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Best Deals Under $25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-25-a4183478310/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gas vs. Battery Lawn Mower: Which Is Better?</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/gas-vs-electric-lawn-mower-which-is-better-a1057954260/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>How to Check Engine Oil the Right Way</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6 Best Compression Socks, Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/apparel-accessories/underwear-socks/best-compression-socks-a2750797916/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>We Tested 49 More Baby Formulas for Lead and Arsenic</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-formula/liquid-baby-formula-contaminants-test-results-a8639602154/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Safest Small SUVs of 2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-small-suvs-a9206654113/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ford and Lincoln SUVs Recalled to Fix Windshield Wipers</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/ford-lincoln-suvs-recalled-to-fix-windshield-wiper-motor-a5559013983/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1.7 Million More Ford and Lincoln SUVs Recalled to Fix Screens</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/more-ford-and-lincoln-suvs-recalled-to-fix-backup-cameras-a4514261791/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Best Used Cars and SUVs Under $10,000 That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/best-used-cars-suvs-under-10000-dollars-a8966344858/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Thousands of Halo Magic Sleepsuits Recalled for Choking Risk</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/halo-magic-sleepsuits-recalled-for-choking-risk-a6877096785/</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Baby Product Recalls Parents Should Know About in 2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/baby-product-recalls-parents-caregivers-should-be-aware-of-a5859124070/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Most Reliable 3-Year-Old Cars and SUVs That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/most-reliable-3-year-old-cars-and-suvs-a7361029795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient SUVs</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/the-most-fuel-efficient-suvs-best-mpg-a5599990140/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Talking Carts 10: The Pink Tax</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-10-the-pink-tax-a4218079662/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>More Than 80,000 Babysense Baby Monitors Recalled for Fire Hazard Risk</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/babysense-max-view-baby-monitors-recalled-for-fire-risk-a3285333268/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+          <t>What to Expect for Amazon Prime Day 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Best TV Brands of 2026</t>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Best Decking of 2026, Tested by Experts</t>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+          <t>Best Deals on Headphones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What to Expect for Amazon Prime Day 2026</t>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Best Deals on Headphones</t>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+          <t>Best Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+          <t>Best TV Brands of 2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Best Nail Clippers for Every Need and Every Nail</t>
+          <t>Best Deals on Health and Beauty Products</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Talking Carts 11: Couponing 101</t>
+          <t>Best Washers for $800 or Less</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Best New SUVs and Cars for Under $30,000</t>
+          <t>Best Deals on Vacuums</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Simple Ways to Organize Your Home's Entryway</t>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>How to Save Money at the Gas Pump</t>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+          <t>How to Save Money at the Gas Pump</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+          <t>Best New SUVs and Cars for Under $30,000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Best Deals on Vacuums</t>
+          <t>Talking Carts 11: Couponing 101</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Best Washers for $800 or Less</t>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Best Deals on Health and Beauty Products</t>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Best Battery Platforms for Power Tools</t>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+          <t>Our Favorite Deals Right Now</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+          <t>Best Mattress Sales Right Now</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+          <t>Best Deals on Tech Products Right Now</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4 Best Glass Cleaners From Our Evaluations</t>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Best Deals on Tech Products Right Now</t>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Battery Platforms for Power Tools</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Best Mattress Sales Right Now</t>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Our Favorite Deals Right Now</t>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Best Deals on Pet Products</t>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+          <t>Best Hot Combs, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Best Hot Combs, Tested and Reviewed</t>
+          <t>42 Used Cars to Avoid Buying</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>42 Used Cars to Avoid Buying</t>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+          <t>How an Old-School Flip Phone Changed My Life</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>How an Old-School Flip Phone Changed My Life</t>
+          <t>Best Deals on Pet Products</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10 Best Deals on Electric Vehicles</t>
+          <t>Best Deals Under $50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>How to Stain a Deck</t>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Best Hybrid Cars for Under $35,000</t>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
         </is>
       </c>
     </row>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+          <t>Best Deals Under $100</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Best Deals Under $50</t>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Best Deals Under $100</t>
+          <t>Best Hybrid Cars for Under $35,000</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+          <t>How to Stain a Deck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+          <t>10 Best Deals on Electric Vehicles</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Best Used SUVs With Standout Fuel Economy</t>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+          <t>Most Discounted New Cars Right Now</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Best Deals on Healthy-Home Essentials</t>
+          <t>Worst Deals on New Cars Right Now</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
         </is>
       </c>
     </row>
@@ -2599,12 +2599,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+          <t>Most and Least Reliable Coffee Makers</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best Deals on Fitness Equipment and Accessories</t>
+          <t>Best and Worst Laundry Detergents of 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+          <t>Best Deals on Smart Home Devices</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Best and Worst Laundry Detergents of 2026</t>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Most and Least Reliable Coffee Makers</t>
+          <t>Best Deals on Healthy-Home Essentials</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worst Deals on New Cars Right Now</t>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Best Deals on Smart Home Devices</t>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Best Composite Decking of 2026, Tested by Experts</t>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Most Discounted New Cars Right Now</t>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Best Deals on SUVs You Can Buy Right Now</t>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+          <t>Best Deals on Home Products</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+          <t>Best Deals on Kitchen Products</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>How Do Hybrid Cars Work?</t>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Best New-Car Deals</t>
+          <t>Which iPhone Should You Buy?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+          <t>How Do Hybrid Cars Work?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which iPhone Should You Buy?</t>
+          <t>Best New-Car Deals</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Best Deals on Kitchen Products</t>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Best Deals on Home Products</t>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
         </is>
       </c>
     </row>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Best Cars Made in the USA</t>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5 Best Umbrellas, Tested by Our Experts</t>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What's the Best Mac Laptop or Desktop for You?</t>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+          <t>Best Cars Made in the USA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
         </is>
       </c>
     </row>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>How to Check Engine Oil the Right Way</t>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+          <t>How to Check Engine Oil the Right Way</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
         </is>
       </c>
     </row>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What to Expect for Amazon Prime Day 2026</t>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+          <t>Best TV Brands of 2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+          <t>Best Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Deals on Headphones</t>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+          <t>What to Expect for Amazon Prime Day 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+          <t>Best Deals on Headphones</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Best Decking of 2026, Tested by Experts</t>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Best TV Brands of 2026</t>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+          <t>How to Save Money at the Gas Pump</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Best Deals on Health and Beauty Products</t>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Best Washers for $800 or Less</t>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Best Deals on Vacuums</t>
+          <t>Talking Carts 11: Couponing 101</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+          <t>Best New SUVs and Cars for Under $30,000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>How to Save Money at the Gas Pump</t>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Simple Ways to Organize Your Home's Entryway</t>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Best New SUVs and Cars for Under $30,000</t>
+          <t>Best Deals on Vacuums</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Talking Carts 11: Couponing 101</t>
+          <t>Best Washers for $800 or Less</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Best Nail Clippers for Every Need and Every Nail</t>
+          <t>Best Deals on Health and Beauty Products</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4 Best Glass Cleaners From Our Evaluations</t>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Our Favorite Deals Right Now</t>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Best Mattress Sales Right Now</t>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Best Deals on Tech Products Right Now</t>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Battery Platforms for Power Tools</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+          <t>Our Favorite Deals Right Now</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Best Battery Platforms for Power Tools</t>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+          <t>Best Deals on Tech Products Right Now</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+          <t>Best Mattress Sales Right Now</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+          <t>Best Hot Combs, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Best Hot Combs, Tested and Reviewed</t>
+          <t>42 Used Cars to Avoid Buying</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>42 Used Cars to Avoid Buying</t>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+          <t>How an Old-School Flip Phone Changed My Life</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>How an Old-School Flip Phone Changed My Life</t>
+          <t>Best Deals on Pet Products</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Best Deals on Pet Products</t>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Best Deals Under $50</t>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+          <t>10 Best Deals on Electric Vehicles</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
         </is>
       </c>
     </row>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+          <t>How to Stain a Deck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Best Deals Under $100</t>
+          <t>Best Hybrid Cars for Under $35,000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+          <t>Best Deals Under $100</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Best Hybrid Cars for Under $35,000</t>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>How to Stain a Deck</t>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10 Best Deals on Electric Vehicles</t>
+          <t>Best Deals Under $50</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+          <t>Best Deals on Smart Home Devices</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Most Discounted New Cars Right Now</t>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Best Composite Decking of 2026, Tested by Experts</t>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Worst Deals on New Cars Right Now</t>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
         </is>
       </c>
     </row>
@@ -2599,12 +2599,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Most and Least Reliable Coffee Makers</t>
+          <t>Best Deals on Healthy-Home Essentials</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best and Worst Laundry Detergents of 2026</t>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Best Deals on Smart Home Devices</t>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Best Deals on Fitness Equipment and Accessories</t>
+          <t>Best and Worst Laundry Detergents of 2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Best Deals on Healthy-Home Essentials</t>
+          <t>Worst Deals on New Cars Right Now</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+          <t>Most Discounted New Cars Right Now</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Best Used SUVs With Standout Fuel Economy</t>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+          <t>Most and Least Reliable Coffee Makers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+          <t>How Do Hybrid Cars Work?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Best Deals on Home Products</t>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Best Deals on Kitchen Products</t>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which iPhone Should You Buy?</t>
+          <t>Best New-Car Deals</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>How Do Hybrid Cars Work?</t>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Best New-Car Deals</t>
+          <t>Which iPhone Should You Buy?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+          <t>Best Deals on Kitchen Products</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+          <t>Best Deals on Home Products</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Best Deals on SUVs You Can Buy Right Now</t>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
         </is>
       </c>
     </row>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+          <t>Best Cars Made in the USA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What's the Best Mac Laptop or Desktop for You?</t>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5 Best Umbrellas, Tested by Our Experts</t>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Best Cars Made in the USA</t>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
         </is>
       </c>
     </row>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+          <t>How to Check Engine Oil the Right Way</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>How to Check Engine Oil the Right Way</t>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
         </is>
       </c>
     </row>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+          <t>What to Expect for Amazon Prime Day 2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Best TV Brands of 2026</t>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Best Decking of 2026, Tested by Experts</t>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+          <t>Best Deals on Headphones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What to Expect for Amazon Prime Day 2026</t>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Best Deals on Headphones</t>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+          <t>Best Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+          <t>Best TV Brands of 2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>How to Save Money at the Gas Pump</t>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
         </is>
       </c>
     </row>
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Best Nail Clippers for Every Need and Every Nail</t>
+          <t>Best Deals on Health and Beauty Products</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
         </is>
       </c>
     </row>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Talking Carts 11: Couponing 101</t>
+          <t>Best Washers for $800 or Less</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Best New SUVs and Cars for Under $30,000</t>
+          <t>Best Deals on Vacuums</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Simple Ways to Organize Your Home's Entryway</t>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+          <t>Best New SUVs and Cars for Under $30,000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Best Deals on Vacuums</t>
+          <t>Talking Carts 11: Couponing 101</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Best Washers for $800 or Less</t>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Best Deals on Health and Beauty Products</t>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+          <t>How to Save Money at the Gas Pump</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+          <t>Best Mattress Sales Right Now</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+          <t>Best Deals on Tech Products Right Now</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
         </is>
       </c>
     </row>
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+          <t>Our Favorite Deals Right Now</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Best Battery Platforms for Power Tools</t>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Battery Platforms for Power Tools</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Our Favorite Deals Right Now</t>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4 Best Glass Cleaners From Our Evaluations</t>
+          <t>8 Midsized Three-Row Sport-Utility Vehicles With the Best Tested Gas Mileage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-used-three-row-suvs-a7976679803/</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Best Deals on Tech Products Right Now</t>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Best Mattress Sales Right Now</t>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
         </is>
       </c>
     </row>
@@ -2038,12 +2038,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+          <t>Best Hot Combs, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
         </is>
       </c>
     </row>
@@ -2072,12 +2072,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Best Hot Combs, Tested and Reviewed</t>
+          <t>42 Used Cars to Avoid Buying</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>42 Used Cars to Avoid Buying</t>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+          <t>How an Old-School Flip Phone Changed My Life</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>How an Old-School Flip Phone Changed My Life</t>
+          <t>Best Deals on Pet Products</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Best Deals on Pet Products</t>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
         </is>
       </c>
     </row>
@@ -2225,12 +2225,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
         </is>
       </c>
     </row>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+          <t>7 Expert Steps to Buy a Used Car Without Costly Regrets</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/how-to-protect-yourself-when-buying-a-used-car-a7040550851/</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+          <t>Best Deals Under $100</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
         </is>
       </c>
     </row>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10 Best Deals on Electric Vehicles</t>
+          <t>Best Deals Under $50</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
         </is>
       </c>
     </row>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>How to Stain a Deck</t>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Best Hybrid Cars for Under $35,000</t>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Best Deals Under $100</t>
+          <t>Best Hybrid Cars for Under $35,000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/best-hybrid-cars-from-consumer-reports-tests-a5841270718/</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+          <t>10 Best Deals on Electric Vehicles</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Best Deals Under $50</t>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+          <t>How to Stain a Deck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
         </is>
       </c>
     </row>
@@ -2531,12 +2531,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Best Deals on Smart Home Devices</t>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+          <t>Most and Least Reliable Coffee Makers</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
         </is>
       </c>
     </row>
@@ -2565,12 +2565,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Best Used SUVs With Standout Fuel Economy</t>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
         </is>
       </c>
     </row>
@@ -2599,12 +2599,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Best Deals on Healthy-Home Essentials</t>
+          <t>Worst Deals on New Cars Right Now</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best Deals on Fitness Equipment and Accessories</t>
+          <t>Best and Worst Laundry Detergents of 2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+          <t>Most Discounted New Cars Right Now</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Best and Worst Laundry Detergents of 2026</t>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Worst Deals on New Cars Right Now</t>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Best Composite Decking of 2026, Tested by Experts</t>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Most Discounted New Cars Right Now</t>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
         </is>
       </c>
     </row>
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+          <t>Best Deals on Smart Home Devices</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+          <t>https://www.consumerreports.org/home-garden/smart-home/best-smart-home-deals-a3525616797/</t>
         </is>
       </c>
     </row>
@@ -2735,12 +2735,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Most and Least Reliable Coffee Makers</t>
+          <t>Best Deals on Healthy-Home Essentials</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
         </is>
       </c>
     </row>
@@ -2752,12 +2752,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>How Do Hybrid Cars Work?</t>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Best Deals on SUVs You Can Buy Right Now</t>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2786,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+          <t>Best Deals on Home Products</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
+          <t>Best Deals on Kitchen Products</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Best New-Car Deals</t>
+          <t>Which iPhone Should You Buy?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
         </is>
       </c>
     </row>
@@ -2837,12 +2837,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+          <t>Popular Small Cars to Avoid and What to Buy Instead</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/popular-compact-cars-to-avoid-what-to-buy-instead-a1188453224/</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which iPhone Should You Buy?</t>
+          <t>Best New-Car Deals</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Best Deals on Kitchen Products</t>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Best Deals on Home Products</t>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
         </is>
       </c>
     </row>
@@ -2905,12 +2905,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+          <t>How Do Hybrid Cars Work?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
         </is>
       </c>
     </row>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Best Cars Made in the USA</t>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
         </is>
       </c>
     </row>
@@ -2939,12 +2939,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5 Best Umbrellas, Tested by Our Experts</t>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
         </is>
       </c>
     </row>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
         </is>
       </c>
     </row>
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+          <t>Best Cars Made in the USA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+          <t>14 Exclusive Savings for CR's Member Appreciation Week</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/member-exclusive-savings-a4229795581/</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What's the Best Mac Laptop or Desktop for You?</t>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
         </is>
       </c>
     </row>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
         </is>
       </c>
     </row>
@@ -3262,12 +3262,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>How to Check Engine Oil the Right Way</t>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3279,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+          <t>How to Check Engine Oil the Right Way</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
         </is>
       </c>
     </row>

--- a/CR_News_Report_Master.xlsx
+++ b/CR_News_Report_Master.xlsx
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1404,85 +1404,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4 Best Single-Serve Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+          <t>Most Satisfying New Midsized SUVs According to Consumer Reports' Experts</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-pod-coffee-makers-a3468890273/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-satisfying-new-midsized-suvs-a8737769761/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What to Expect for Amazon Prime Day 2026</t>
+          <t>5 Expert Bicycle Maintenance Basics Every Rider Should Know to Avoid Costly Repairs</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
+          <t>https://www.consumerreports.org/health/bikes/bike-maintenance-tips-a1082340932/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
+          <t>How to Stay Steady on Your Feet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
+          <t>https://www.consumerreports.org/health/seniors-health/how-to-stay-steady-on-your-feet-a7592140588/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Electric and Battery Pressure Washers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
+          <t>https://www.consumerreports.org/home-garden/pressure-washers/best-electric-pressure-washers-of-the-year-a7705441243/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Pressure Washers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
+          <t>https://www.consumerreports.org/home-garden/pressure-washers/best-pressure-washers-of-the-year-a1182532607/</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
+          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
+          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
+          <t>4 Best Single-Serve Coffee Makers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-pod-coffee-makers-a3468890273/</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Best Deals on Headphones</t>
+          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
+          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AI Data Centers: Big Tech's Impact on Electric Bills, Water, and More</t>
+          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/data-centers/ai-data-centers-impact-on-electric-bills-water-and-more-a1040338678/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
+          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
+          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Best Decking of 2026, Tested by Experts</t>
+          <t>Best TV Brands of 2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
+          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Best TV Brands of 2026</t>
+          <t>Best Used Small Cars for Gas Mileage: Standout Picks From Consumer Reports' Fuel-Economy Tests</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/tvs/best-tv-brands-a7582471181/</t>
+          <t>https://www.consumerreports.org/cars/used-compact-cars-with-best-fuel-economy-a7463598571/</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4 Best Toilet Brushes of 2026 From Our Evaluations</t>
+          <t>Best Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/toilets/best-toilet-brushes-a6509646029/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-decking-materials-from-consumer-reports-tests-a6751297873/</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11 Best Cordless Drills of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Deals on Headphones</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-cordless-drills-of-the-year-a1168250583/</t>
+          <t>https://www.consumerreports.org/electronics-computers/headphones/best-headphone-deals-a9608506602/</t>
         </is>
       </c>
     </row>
@@ -1647,97 +1647,97 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Used Car Checklist to Avoid Costly Repairs</t>
+          <t>Best Drip Coffee Makers of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/how-to-inspect-a-used-car-a1377126659/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-drip-coffee-makers-consumer-reports-tests-a1869713908/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
+          <t>Consumer Safety Agency Finalizes New Regulations on Water Beads and Infant Neck Floats</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
+          <t>https://www.consumerreports.org/babies-kids/toys/consumer-safety-agency-new-rules-water-beads-neck-floats-a2051187866/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
+          <t>7 Best Food Processors and Choppers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
+          <t>https://www.consumerreports.org/appliances/food-processors-choppers/best-food-processors-of-the-year-a7878155198/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Best Deals on Health and Beauty Products</t>
+          <t>4 Best Whole-House Heat Pumps of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
+          <t>https://www.consumerreports.org/appliances/heat-pumps/best-whole-house-heat-pumps-a1157154177/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Best Washers for $800 or Less</t>
+          <t>174,800 Frigidaire Gas Ranges Recalled Due to Burn Hazard</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
+          <t>https://www.consumerreports.org/appliances/appliance-recalls/frigidaire-gas-ranges-recalled-burn-hazard-a1065367849/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Best Deals on Vacuums</t>
+          <t>What to Expect for Amazon Prime Day 2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/amazon-prime-day-what-to-expect-a9781954357/</t>
         </is>
       </c>
     </row>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
+          <t>Simple Ways to Organize Your Home's Entryway</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
+          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
         </is>
       </c>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Simple Ways to Organize Your Home's Entryway</t>
+          <t>How to Save Money at the Gas Pump</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/home-organization/easy-tips-to-organize-home-entryway-a1146889912/</t>
+          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
         </is>
       </c>
     </row>
@@ -1783,12 +1783,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Best New SUVs and Cars for Under $30,000</t>
+          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Talking Carts 11: Couponing 101</t>
+          <t>Best Nail Clippers for Every Need and Every Nail</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
+          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Best Nail Clippers for Every Need and Every Nail</t>
+          <t>Talking Carts 11: Couponing 101</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/personal-care/best-nail-clippers-a6951655841/</t>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-11-couponing-101-a9760148597/</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10 Tips to Get the Most Out of a Tank of Gas</t>
+          <t>Best New SUVs and Cars for Under $30,000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/10-tips-to-get-the-most-out-of-a-tank-of-gas-a2642110189/</t>
+          <t>https://www.consumerreports.org/cars/best-new-cars-under-30000-dollars-a6574737993/</t>
         </is>
       </c>
     </row>
@@ -1851,97 +1851,97 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>How to Save Money at the Gas Pump</t>
+          <t>Popular Cars and SUVs to Avoid and Safer Choices to Buy Instead</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/saving-money/how-to-save-money-at-the-gas-pump-a8520505361/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/popular-cars-suvs-to-avoid-safer-choices-to-buy-instead-a7755684192/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
+          <t>Buying or Leasing a Car in 2026: Which Makes the Best Financial Sense for You?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/leasing-vs-buying-a-new-car-a9135602164/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Best Mattress Sales Right Now</t>
+          <t>Best Deals on Vacuums</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-vacuum-deals-right-now-a5043984151/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Best Deals on Tech Products Right Now</t>
+          <t>Best Washers for $800 or Less</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washers-for-800-dollars-or-less-a3982320572/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Our Favorite Deals Right Now</t>
+          <t>Best Deals on Health and Beauty Products</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-health-and-beauty-products-a1654821936/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4 Best Glass Cleaners From Our Evaluations</t>
+          <t>9 Best Stick Vacuums of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-stick-vacuums-of-the-year-a1113185163/</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Best Battery Platforms for Power Tools</t>
+          <t>Best Cleaning Products From Our Tests and Evaluations</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
         </is>
       </c>
     </row>
@@ -1970,12 +1970,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
+          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2004,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Preview: 2027 BMW i3 Returns as an All-Electric Sedan</t>
+          <t>Best Battery Platforms for Power Tools</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/2027-bmw-i3-review-a6401226776/</t>
+          <t>https://www.consumerreports.org/home-garden/battery-platforms/best-battery-platforms-for-power-tools-a1200820570/</t>
         </is>
       </c>
     </row>
@@ -2021,97 +2021,97 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Best Cleaning Products From Our Tests and Evaluations</t>
+          <t>Talking Cars 498: Discussing the Latest Electric Car Range Test Results</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cleaning/best-cleaning-products-a3675714062/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-498-latest-electric-car-range-test-results-a4872039008/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
+          <t>Our Favorite Deals Right Now</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/our-favorite-deals-a4347518393/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Best Hot Combs, Tested and Reviewed</t>
+          <t>4 Best Glass Cleaners From Our Evaluations</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
+          <t>https://www.consumerreports.org/home-garden/cleaning/best-glass-cleaners-a9011399777/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>42 Used Cars to Avoid Buying</t>
+          <t>16 Best Washing Machines of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
+          <t>https://www.consumerreports.org/appliances/washing-machines/best-washing-machines-of-the-year-a7327583525/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
+          <t>Best Deals on Tech Products Right Now</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-electronics-deals-right-now-a3598707304/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
+          <t>Best Mattress Sales Right Now</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
+          <t>https://www.consumerreports.org/home-garden/mattresses/best-mattress-deals-a6347099135/</t>
         </is>
       </c>
     </row>
@@ -2123,12 +2123,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>How an Old-School Flip Phone Changed My Life</t>
+          <t>Worst Vacuums We Tested—and What to Buy Instead</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/worst-vacuums-we-tested-and-what-to-buy-instead-a4744433209/</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Best Deals on Pet Products</t>
+          <t>Best Hot Combs, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
+          <t>https://www.consumerreports.org/health/hair-styling-tools/best-hot-combs-a1155859440/</t>
         </is>
       </c>
     </row>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Best Cars, SUVs, and Trucks from American Brands</t>
+          <t>42 Used Cars to Avoid Buying</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
+          <t>https://www.consumerreports.org/cars/used-cars-to-avoid-buying-a4034931071/</t>
         </is>
       </c>
     </row>
@@ -2174,97 +2174,97 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
+          <t>Most Fuel-Efficient Used Hybrid Cars and Hatchbacks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/used-hybrid-sedans-and-hatchbacks-with-best-fuel-economy-a2840918797/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
+          <t>Least Durable Nonstick Frying Pans and What to Buy Instead</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
+          <t>https://www.consumerreports.org/home-garden/cookware/least-durable-nonstick-frying-pans-what-to-buy-instead-a4466494459/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
+          <t>How an Old-School Flip Phone Changed My Life</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/pros-and-cons-of-using-a-flip-phone-a8412704280/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
+          <t>Best Deals on Pet Products</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
+          <t>https://www.consumerreports.org/money/discounts-rebates/best-deals-on-pet-products-a5737541283/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
+          <t>Best Cars, SUVs, and Trucks from American Brands</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
+          <t>https://www.consumerreports.org/cars/cars-best-american-cars-suvs-trucks-a1034107548/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
+          <t>Raw Farm Raw Milk Cheddar Cheese Linked to an E. Coli Outbreak</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/raw-farm-raw-milk-cheddar-cheese-e-coli-outbreak-a1754162551/</t>
         </is>
       </c>
     </row>
@@ -2288,153 +2288,153 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>How to Clean Your Lawn Mower Deck</t>
+          <t>Hyundai Recalls Palisade and Issues Stop-Sale After Child’s Death</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-clean-your-lawn-mower-deck-a4858405895/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/hyundai-palisade-recall-folding-seats-stop-sale-child-death-a6861032164/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Best Wood Stains of 2026 (and a Few of the Worst)</t>
+          <t>ICYMI: Spring Yard Prep, Exclusive Member Savings, Apple's New MacBook Neo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/wood-stains/best-wood-stains-from-consumer-reports-tests-a4478428531/</t>
+          <t>https://www.consumerreports.org/home-garden/spring-yard-prep-exclusive-member-savings-apple-macbook-neo-a6548509942/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>How to Get Your Lawn Mower or Tractor Ready for Mowing Season</t>
+          <t>Consumer Reports’ Real-World Electric Car Range Comparison</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-get-your-lawn-mower-ready-for-spring-a8196766008/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/real-world-ev-range-tests-models-that-beat-epa-estimates-a1103288135/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Best Time to Fertilize Your Lawn</t>
+          <t>Best Spring Cleaning Deals on Vacuums, Carpet Cleaners, and More</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/lawn-care/dont-bother-fertilizing-your-lawn-twice-a-year-a5780099997/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-spring-cleaning-deals-a6459257616/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Best Deals Under $100</t>
+          <t>Best Baby Food Companies for Reporting Lead, Arsenic, and Other Toxic Elements</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-food/baby-food-labels-heavy-metals-california-ab899-a5779555429/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
+          <t>How to Clean Your Lawn Mower Deck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-clean-your-lawn-mower-deck-a4858405895/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Best Deals Under $50</t>
+          <t>Best Wood Stains of 2026 (and a Few of the Worst)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/best-wood-stains-from-consumer-reports-tests-a4478428531/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
+          <t>How to Get Your Lawn Mower or Tractor Ready for Mowing Season</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/how-to-get-your-lawn-mower-ready-for-spring-a8196766008/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
+          <t>Best Time to Fertilize Your Lawn</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
+          <t>https://www.consumerreports.org/home-garden/lawn-care/dont-bother-fertilizing-your-lawn-twice-a-year-a5780099997/</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2463,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10 Best Deals on Electric Vehicles</t>
+          <t>How to Stain a Deck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
+          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
         </is>
       </c>
     </row>
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
+          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Toyota Highlander Recalled to Fix Second-Row Seat Latches</t>
+          <t>20 Most Reliable and Fuel-Efficient 2026 Compact SUVs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/toyota-highlander-recalled-to-fix-second-row-seat-latches-a1110263947/</t>
+          <t>https://www.consumerreports.org/cars/suvs/reliable-and-fuel-efficient-compact-suvs-a6901123061/</t>
         </is>
       </c>
     </row>
@@ -2514,97 +2514,97 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>How to Stain a Deck</t>
+          <t>10 Best Deals on Electric Vehicles</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/wood-stains/how-to-stain-your-deck-a1462288683/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/best-deals-on-electric-vehicles-a1198228201/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
+          <t>4 Best K-Cup Coffee Makers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-keurig-k-cup-coffee-makers-a2682700597/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Most and Least Reliable Coffee Makers</t>
+          <t>Does an ‘Eco-Friendly’ Diaper Really Exist?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
+          <t>https://www.consumerreports.org/babies-kids/diapers/does-an-eco-friendly-diaper-really-exist-a6768931967/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
+          <t>5 Best Air Purifiers for Wildfire Smoke, According to Our Testing</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
+          <t>https://www.consumerreports.org/appliances/air-purifiers/best-air-purifiers-for-wildfire-smoke-a1153295134/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Best Composite Decking of 2026, Tested by Experts</t>
+          <t>Best Deals Under $100</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-100-dollars-a1055650279/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Worst Deals on New Cars Right Now</t>
+          <t>Best Deals Under $50</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-50-dollars-a2569975133/</t>
         </is>
       </c>
     </row>
@@ -2616,12 +2616,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best and Worst Laundry Detergents of 2026</t>
+          <t>Most Discounted New Cars Right Now</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
         </is>
       </c>
     </row>
@@ -2633,12 +2633,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Most Discounted New Cars Right Now</t>
+          <t>Best Deals on Healthy-Home Essentials</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/new-cars-with-biggest-savings-off-msrp-right-now-a1002706451/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Best Deals on Fitness Equipment and Accessories</t>
+          <t>12 Products That Help Us Get a Good Night's Sleep</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
+          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10 Cheap Cars That Consumer Reports Recommends</t>
+          <t>Best Used SUVs With Standout Fuel Economy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
+          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
         </is>
       </c>
     </row>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Best Used SUVs With Standout Fuel Economy</t>
+          <t>10 Cheap Cars That Consumer Reports Recommends</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/most-fuel-efficient-5-year-old-compact-suvs-a1110308216/</t>
+          <t>https://www.consumerreports.org/cars/cheap-cars-recommended-by-consumer-reports-a1059266229/</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12 Products That Help Us Get a Good Night's Sleep</t>
+          <t>Best Deals on Fitness Equipment and Accessories</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/sleeping/products-that-help-us-get-a-good-nights-sleep-a8894453489/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-fitness-equipment-and-accessories-a9859972001/</t>
         </is>
       </c>
     </row>
@@ -2735,97 +2735,97 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Best Deals on Healthy-Home Essentials</t>
+          <t>Best and Worst Laundry Detergents of 2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-healthy-home-essentials-a5487006019/</t>
+          <t>https://www.consumerreports.org/appliances/laundry-detergents/best-and-worst-laundry-detergents-from-consumer-reports-tests-a9342715268/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
+          <t>Best Composite Decking of 2026, Tested by Experts</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
+          <t>https://www.consumerreports.org/home-garden/decking/best-composite-decking-from-consumer-reports-tests-a6753939440/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
+          <t>Preview: 2026 Porsche Cayenne Electric Doesn’t Need to Plug In to Charge</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
+          <t>https://www.consumerreports.org/cars/suvs/2026-porsche-cayenne-electric-review-a1008258321/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Best Deals on Home Products</t>
+          <t>Most and Least Reliable Coffee Makers</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/most-and-least-reliable-coffee-makers-a4935369168/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Best Deals on Kitchen Products</t>
+          <t>Consumer Reports' Best Used Midsized SUVs With Excellent Fuel Economy</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
+          <t>https://www.consumerreports.org/cars/suvs/used-two-row-midsized-suvs-with-best-fuel-economy-a1177062626/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which iPhone Should You Buy?</t>
+          <t>Worst Deals on New Cars Right Now</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/worst-deals-on-new-cars-a3991316773/</t>
         </is>
       </c>
     </row>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Best New-Car Deals</t>
+          <t>How Do Hybrid Cars Work?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
+          <t>Best Deals on SUVs You Can Buy Right Now</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
+          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Best Deals on SUVs You Can Buy Right Now</t>
+          <t>Talking Cars 497: Should You Drive 55 to Save Gas?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/best-deals-on-new-suvs-a3535956359/</t>
+          <t>https://www.consumerreports.org/cars/cars-driving/talking-cars-497-should-you-drive-55-to-save-gas-a3968521620/</t>
         </is>
       </c>
     </row>
@@ -2905,97 +2905,97 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>How Do Hybrid Cars Work?</t>
+          <t>Best New-Car Deals</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/how-do-hybrid-cars-work-a1034181509/</t>
+          <t>https://www.consumerreports.org/cars/best-new-car-deals-a1060496430/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What's the Best Mac Laptop or Desktop for You?</t>
+          <t>Best Deals on Kitchen Products</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-kitchen-products-a3665220041/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
+          <t>Which iPhone Should You Buy?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
+          <t>https://www.consumerreports.org/electronics-computers/cell-phones/which-iphone-should-you-buy-a7028071026/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
+          <t>Best Deals on Home Products</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-home-products-a1464868801/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
+          <t>Best Deals on Fuel-Efficient Cars and SUVs</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
+          <t>https://www.consumerreports.org/cars/buying-a-car/best-deals-on-fuel-efficient-cars-a4329802409/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
+          <t>8 Best Coffee Makers of 2026, Lab Tested and Reviewed</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
+          <t>https://www.consumerreports.org/appliances/coffee-makers/best-coffee-makers-of-the-year-a9612622702/</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Best Cars Made in the USA</t>
+          <t>5 Best Umbrellas, Tested by Our Experts</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
+          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
         </is>
       </c>
     </row>
@@ -3041,97 +3041,97 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5 Best Umbrellas, Tested by Our Experts</t>
+          <t>Best Cars Made in the USA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/apparel-accessories/best-umbrellas-a5725351696/</t>
+          <t>https://www.consumerreports.org/cars/best-cars-made-in-the-usa-a7966845571/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7 Best E-Bike Covers of 2026, According to Experts</t>
+          <t>Safest Midsized, Large, and Three-Row SUVs of 2026</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/electric-bikes/best-e-bike-covers-a5685855846/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-midsized-large-three-row-suvs-a4483160846/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Are Hybrids a Smart Choice Right Now?</t>
+          <t>Trader Joe's Chicken Fried Rice Recall Expanded. Packages May Contain Glass Fragments.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/hybrids-evs/why-hybrid-vehicles-are-a-smart-choice-right-now-a2736240282/</t>
+          <t>https://www.consumerreports.org/health/food-recalls/fried-rice-ramen-dumpling-recall-glass-trader-joes-ajinomoto-a1204133892/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Best Deals Under $25</t>
+          <t>What's the Best Mac Laptop or Desktop for You?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-25-a4183478310/</t>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-mac-desktop-or-laptop-for-you-a1085516654/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Gas vs. Battery Lawn Mower: Which Is Better?</t>
+          <t>Best Sales on Pillows, Duvets, and More Sleep Essentials</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/lawn-mowers/gas-vs-electric-lawn-mower-which-is-better-a1057954260/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-on-pillows-sheets-and-other-sleep-accessories-a9893546733/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
+          <t>Consumer Reports' Cars With the Best Gas Mileage</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
+          <t>https://www.consumerreports.org/cars/fuel-economy-efficiency/the-most-fuel-efficient-cars-best-mpg-a1198903400/</t>
         </is>
       </c>
     </row>
@@ -3143,12 +3143,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
+          <t>7 Best E-Bike Covers of 2026, According to Experts</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
+          <t>https://www.consumerreports.org/health/electric-bikes/best-e-bike-covers-a5685855846/</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
+          <t>Are Hybrids a Smart Choice Right Now?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
+          <t>https://www.consumerreports.org/cars/hybrids-evs/why-hybrid-vehicles-are-a-smart-choice-right-now-a2736240282/</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
+          <t>Best Deals Under $25</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
+          <t>https://www.consumerreports.org/money/sales-promotions/best-deals-under-25-a4183478310/</t>
         </is>
       </c>
     </row>
@@ -3194,12 +3194,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
+          <t>Gas vs. Battery Lawn Mower: Which Is Better?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
+          <t>https://www.consumerreports.org/home-garden/lawn-mowers/gas-vs-electric-lawn-mower-which-is-better-a1057954260/</t>
         </is>
       </c>
     </row>
@@ -3211,165 +3211,165 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
+          <t>ICYMI: Heavy Metals in Baby Formula, New Materials in Our Sheets Ratings, Best Tire Retailers</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
+          <t>https://www.consumerreports.org/home-garden/heavy-metals-in-baby-formula-sheet-materials-tire-retailers-a3381367383/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
+          <t>4 Best OTC Orthotics of 2026, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
+          <t>https://www.consumerreports.org/health/foot-care-products/best-orthotics-shoe-inserts-a9704600797/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
+          <t>Should You Buy Samsung Care+ for Your New Galaxy S26 Phone?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
+          <t>https://www.consumerreports.org/money/extended-warranties/should-you-buy-samsung-care-plus-a5246602825/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>How to Make Sure Your Packages Don't Get Stolen</t>
+          <t>5 Best Small Microwaves, Lab-Tested by Experts</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
+          <t>https://www.consumerreports.org/appliances/microwave-ovens/best-small-microwaves-a9271841322/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>How to Check Engine Oil the Right Way</t>
+          <t>3 Best Hardwood Floor Cleaners, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
+          <t>https://www.consumerreports.org/appliances/floor-cleaners/best-hardwood-floor-cleaners-a1178709301/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6 Best Compression Socks, Tested and Reviewed</t>
+          <t>Best Midsized SUVs That Are Reliable and Fuel-Efficient</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/apparel-accessories/underwear-socks/best-compression-socks-a2750797916/</t>
+          <t>https://www.consumerreports.org/cars/car-reliability-owner-satisfaction/new-midsized-suvs-most-reliable-fuel-efficient-a2811867777/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>We Tested 49 More Baby Formulas for Lead and Arsenic</t>
+          <t>6 Best Impact Drivers of 2026, Lab-Tested and Reviewed</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-formula/liquid-baby-formula-contaminants-test-results-a8639602154/</t>
+          <t>https://www.consumerreports.org/home-garden/cordless-drills-impact-drivers/best-impact-drivers-of-the-year-a2626906980/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
+          <t>How Do You Maintain a Car That Isn’t Driven Much?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
+          <t>https://www.consumerreports.org/cars/car-maintenance/how-to-maintain-a-car-that-isnt-driven-much-a6412749580/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Safest Small SUVs of 2026</t>
+          <t>How to Check Engine Oil the Right Way</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-safety/safest-small-suvs-a9206654113/</t>
+          <t>https://www.consumerreports.org/cars/car-repair-maintenance/how-to-check-car-engine-oil-a7618306432/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ford and Lincoln SUVs Recalled to Fix Windshield Wipers</t>
+          <t>How to Make Sure Your Packages Don't Get Stolen</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/ford-lincoln-suvs-recalled-to-fix-windshield-wiper-motor-a5559013983/</t>
+          <t>https://www.consumerreports.org/money/theft/how-to-keep-holiday-packages-being-stolen-a5439792808/</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1.7 Million More Ford and Lincoln SUVs Recalled to Fix Screens</t>
+          <t>6 Best Compression Socks, Tested and Reviewed</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/car-recalls-defects/more-ford-and-lincoln-suvs-recalled-to-fix-backup-cameras-a4514261791/</t>
+          <t>https://www.consumerreports.org/apparel-accessories/underwear-socks/best-compression-socks-a2750797916/</t>
         </is>
       </c>
     </row>
@@ -3398,97 +3398,97 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Best Used Cars and SUVs Under $10,000 That You Can Buy Right Now</t>
+          <t>We Tested 49 More Baby Formulas for Lead and Arsenic</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/best-used-cars-suvs-under-10000-dollars-a8966344858/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-formula/liquid-baby-formula-contaminants-test-results-a8639602154/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Thousands of Halo Magic Sleepsuits Recalled for Choking Risk</t>
+          <t>9 Best Desktop Computers of 2026, Tested by Our Experts</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/halo-magic-sleepsuits-recalled-for-choking-risk-a6877096785/</t>
+          <t>https://www.consumerreports.org/electronics-computers/computers/best-desktop-computers-of-the-year-a7188203360/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+          <t>Safest Small SUVs of 2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+          <t>https://www.consumerreports.org/cars/car-safety/safest-small-suvs-a9206654113/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Baby Product Recalls Parents Should Know About in 2026</t>
+          <t>Ford and Lincoln SUVs Recalled to Fix Windshield Wipers</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/baby-product-recalls-parents-caregivers-should-be-aware-of-a5859124070/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/ford-lincoln-suvs-recalled-to-fix-windshield-wiper-motor-a5559013983/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Most Reliable 3-Year-Old Cars and SUVs That You Can Buy Right Now</t>
+          <t>1.7 Million More Ford and Lincoln SUVs Recalled to Fix Screens</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/most-reliable-3-year-old-cars-and-suvs-a7361029795/</t>
+          <t>https://www.consumerreports.org/cars/car-recalls-defects/more-ford-and-lincoln-suvs-recalled-to-fix-backup-cameras-a4514261791/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Most Fuel-Efficient SUVs</t>
+          <t>Best Used Cars and SUVs Under $10,000 That You Can Buy Right Now</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/cars/suvs/the-most-fuel-efficient-suvs-best-mpg-a5599990140/</t>
+          <t>https://www.consumerreports.org/cars/best-used-cars-suvs-under-10000-dollars-a8966344858/</t>
         </is>
       </c>
     </row>
@@ -3500,27 +3500,112 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Talking Carts 10: The Pink Tax</t>
+          <t>Thousands of Halo Magic Sleepsuits Recalled for Choking Risk</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-10-the-pink-tax-a4218079662/</t>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/halo-magic-sleepsuits-recalled-for-choking-risk-a6877096785/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>6 Best Robot Vacuums of 2026 for Pet Hair, Lab-Tested and Reviewed</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/appliances/vacuum-cleaners/best-robotic-vacuums-for-pet-hair-a6341573082/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Baby Product Recalls Parents Should Know About in 2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/baby-product-recalls-parents-caregivers-should-be-aware-of-a5859124070/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Most Reliable 3-Year-Old Cars and SUVs That You Can Buy Right Now</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/most-reliable-3-year-old-cars-and-suvs-a7361029795/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Most Fuel-Efficient SUVs</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/cars/suvs/the-most-fuel-efficient-suvs-best-mpg-a5599990140/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Talking Carts 10: The Pink Tax</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>https://www.consumerreports.org/money/shopping-retail/talking-carts-10-the-pink-tax-a4218079662/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>More Than 80,000 Babysense Baby Monitors Recalled for Fire Hazard Risk</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>https://www.consumerreports.org/babies-kids/baby-product-recalls/babysense-max-view-baby-monitors-recalled-for-fire-risk-a3285333268/</t>
         </is>
